--- a/data/EM.MI.xlsx
+++ b/data/EM.MI.xlsx
@@ -62874,7 +62874,7 @@
         <v>0.83899998664856</v>
       </c>
       <c r="D2718" t="n">
-        <v>0.828999996185303</v>
+        <v>0.819999992847443</v>
       </c>
       <c r="E2718" t="n">
         <v>0.833999991416931</v>
@@ -62883,6 +62883,29 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G2718" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>51896</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>0.824999988079071</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>0.815999984741211</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>0.819999992847443</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>0.824999988079071</v>
+      </c>
+      <c r="G2719" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EM.MI.xlsx
+++ b/data/EM.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>82051</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>0.819000005722046</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>0.806999981403351</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>0.819000005722046</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>0.809000015258789</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EM.MI.xlsx
+++ b/data/EM.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>34523</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>0.824000000953674</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>0.808000028133392</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>0.814000010490417</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>0.810999989509583</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EM.MI.xlsx
+++ b/data/EM.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>99562</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>0.829999983310699</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>0.810000002384186</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>0.814999997615814</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>0.819999992847443</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EM.MI.xlsx
+++ b/data/EM.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>37466</v>
+        <v>15174</v>
       </c>
       <c r="C2715" t="n">
-        <v>0.837999999523163</v>
+        <v>0.847000002861023</v>
       </c>
       <c r="D2715" t="n">
-        <v>0.828999996185303</v>
+        <v>0.818000018596649</v>
       </c>
       <c r="E2715" t="n">
-        <v>0.837999999523163</v>
+        <v>0.818000018596649</v>
       </c>
       <c r="F2715" t="n">
-        <v>0.832000017166138</v>
+        <v>0.83899998664856</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>195724</v>
+        <v>37466</v>
       </c>
       <c r="C2716" t="n">
-        <v>0.85699999332428</v>
+        <v>0.837999999523163</v>
       </c>
       <c r="D2716" t="n">
-        <v>0.833000004291534</v>
+        <v>0.828999996185303</v>
       </c>
       <c r="E2716" t="n">
-        <v>0.834999978542328</v>
+        <v>0.837999999523163</v>
       </c>
       <c r="F2716" t="n">
-        <v>0.856000006198883</v>
+        <v>0.832000017166138</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>186700</v>
+        <v>195724</v>
       </c>
       <c r="C2717" t="n">
-        <v>0.852999985218048</v>
+        <v>0.85699999332428</v>
       </c>
       <c r="D2717" t="n">
-        <v>0.824999988079071</v>
+        <v>0.833000004291534</v>
       </c>
       <c r="E2717" t="n">
-        <v>0.84799998998642</v>
+        <v>0.834999978542328</v>
       </c>
       <c r="F2717" t="n">
-        <v>0.824999988079071</v>
+        <v>0.856000006198883</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>105147</v>
+        <v>186700</v>
       </c>
       <c r="C2718" t="n">
-        <v>0.83899998664856</v>
+        <v>0.852999985218048</v>
       </c>
       <c r="D2718" t="n">
-        <v>0.819999992847443</v>
+        <v>0.824999988079071</v>
       </c>
       <c r="E2718" t="n">
-        <v>0.833999991416931</v>
+        <v>0.84799998998642</v>
       </c>
       <c r="F2718" t="n">
-        <v>0.819999992847443</v>
+        <v>0.824999988079071</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>51896</v>
+        <v>105147</v>
       </c>
       <c r="C2719" t="n">
-        <v>0.824999988079071</v>
+        <v>0.83899998664856</v>
       </c>
       <c r="D2719" t="n">
-        <v>0.815999984741211</v>
+        <v>0.819999992847443</v>
       </c>
       <c r="E2719" t="n">
+        <v>0.833999991416931</v>
+      </c>
+      <c r="F2719" t="n">
         <v>0.819999992847443</v>
-      </c>
-      <c r="F2719" t="n">
-        <v>0.824999988079071</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>82051</v>
+        <v>51896</v>
       </c>
       <c r="C2720" t="n">
-        <v>0.819000005722046</v>
+        <v>0.824999988079071</v>
       </c>
       <c r="D2720" t="n">
-        <v>0.806999981403351</v>
+        <v>0.815999984741211</v>
       </c>
       <c r="E2720" t="n">
-        <v>0.819000005722046</v>
+        <v>0.819999992847443</v>
       </c>
       <c r="F2720" t="n">
-        <v>0.809000015258789</v>
+        <v>0.824999988079071</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>34523</v>
+        <v>82051</v>
       </c>
       <c r="C2721" t="n">
-        <v>0.824000000953674</v>
+        <v>0.819000005722046</v>
       </c>
       <c r="D2721" t="n">
-        <v>0.808000028133392</v>
+        <v>0.806999981403351</v>
       </c>
       <c r="E2721" t="n">
-        <v>0.814000010490417</v>
+        <v>0.819000005722046</v>
       </c>
       <c r="F2721" t="n">
-        <v>0.810999989509583</v>
+        <v>0.809000015258789</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>99562</v>
+        <v>34523</v>
       </c>
       <c r="C2722" t="n">
-        <v>0.829999983310699</v>
+        <v>0.824000000953674</v>
       </c>
       <c r="D2722" t="n">
-        <v>0.810000002384186</v>
+        <v>0.808000028133392</v>
       </c>
       <c r="E2722" t="n">
-        <v>0.814999997615814</v>
+        <v>0.814000010490417</v>
       </c>
       <c r="F2722" t="n">
-        <v>0.819999992847443</v>
+        <v>0.810999989509583</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>59360</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>0.823000013828278</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>0.808000028133392</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>0.816999971866608</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>0.820999979972839</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EM.MI.xlsx
+++ b/data/EM.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>0.808000028133392</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>0.78600001335144</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>190043</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>0.805999994277954</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>0.788999974727631</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>0.805999994277954</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EM.MI.xlsx
+++ b/data/EM.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>0.805999994277954</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>0.790000021457672</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>57341</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>0.795000016689301</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>0.782999992370605</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>0.791999995708466</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EM.MI.xlsx
+++ b/data/EM.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>0.791999995708466</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>0.790000021457672</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>108504</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>0.791000008583069</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>0.769999980926514</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>0.773000001907349</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EM.MI.xlsx
+++ b/data/EM.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>0.773000001907349</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>0.78600001335144</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>16664</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>0.788999974727631</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>0.77700001001358</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>0.782000005245209</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EM.MI.xlsx
+++ b/data/EM.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>82696</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>0.796999990940094</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>0.776000022888184</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>0.787999987602234</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>0.776000022888184</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EM.MI.xlsx
+++ b/data/EM.MI.xlsx
@@ -421,7 +421,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G2" t="n">
-        <v>0.533523917198181</v>
+        <v>0.533523857593536</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G3" t="n">
-        <v>0.518079817295074</v>
+        <v>0.518079698085785</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G5" t="n">
-        <v>0.502635717391968</v>
+        <v>0.502635657787323</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>0.721000015735626</v>
       </c>
       <c r="G6" t="n">
-        <v>0.506145775318146</v>
+        <v>0.506145715713501</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>0.716499984264374</v>
       </c>
       <c r="G10" t="n">
-        <v>0.50298660993576</v>
+        <v>0.50298672914505</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>0.685000002384186</v>
       </c>
       <c r="G11" t="n">
-        <v>0.480873584747314</v>
+        <v>0.480873465538025</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>0.674499988555908</v>
       </c>
       <c r="G12" t="n">
-        <v>0.473502457141876</v>
+        <v>0.473502486944199</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>0.639500021934509</v>
       </c>
       <c r="G15" t="n">
-        <v>0.448932290077209</v>
+        <v>0.448932349681854</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G17" t="n">
-        <v>0.470343410968781</v>
+        <v>0.470343470573425</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G18" t="n">
-        <v>0.463323384523392</v>
+        <v>0.463323414325714</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G21" t="n">
-        <v>0.485787481069565</v>
+        <v>0.48578754067421</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>0.689000010490417</v>
       </c>
       <c r="G22" t="n">
-        <v>0.483681559562683</v>
+        <v>0.483681440353394</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>0.693000018596649</v>
       </c>
       <c r="G23" t="n">
-        <v>0.486489534378052</v>
+        <v>0.486489564180374</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>0.672999978065491</v>
       </c>
       <c r="G24" t="n">
-        <v>0.472449421882629</v>
+        <v>0.472449451684952</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G25" t="n">
-        <v>0.463323384523392</v>
+        <v>0.463323414325714</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G26" t="n">
-        <v>0.470343410968781</v>
+        <v>0.470343470573425</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>0.641499996185303</v>
       </c>
       <c r="G27" t="n">
-        <v>0.450336366891861</v>
+        <v>0.450336247682571</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>0.604499995708466</v>
       </c>
       <c r="G28" t="n">
-        <v>0.424362123012543</v>
+        <v>0.42436209321022</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G29" t="n">
-        <v>0.473151475191116</v>
+        <v>0.473151504993439</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>0.634999990463257</v>
       </c>
       <c r="G30" t="n">
-        <v>0.445773214101791</v>
+        <v>0.445773273706436</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G31" t="n">
-        <v>0.449283331632614</v>
+        <v>0.449283301830292</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G32" t="n">
-        <v>0.470343410968781</v>
+        <v>0.470343470573425</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G33" t="n">
-        <v>0.470343410968781</v>
+        <v>0.470343470573425</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>0.710500001907349</v>
       </c>
       <c r="G34" t="n">
-        <v>0.49877455830574</v>
+        <v>0.49877467751503</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>0.699500024318695</v>
       </c>
       <c r="G36" t="n">
-        <v>0.491052627563477</v>
+        <v>0.491052538156509</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G37" t="n">
-        <v>0.495615601539612</v>
+        <v>0.495615571737289</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G38" t="n">
-        <v>0.491403609514236</v>
+        <v>0.491403579711914</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G39" t="n">
-        <v>0.491403609514236</v>
+        <v>0.491403579711914</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G42" t="n">
-        <v>0.499827712774277</v>
+        <v>0.499827653169632</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G43" t="n">
-        <v>0.519483864307404</v>
+        <v>0.519483804702759</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G44" t="n">
-        <v>0.519483864307404</v>
+        <v>0.519483804702759</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>0.753499984741211</v>
       </c>
       <c r="G45" t="n">
-        <v>0.528960883617401</v>
+        <v>0.528960824012756</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>0.785000026226044</v>
       </c>
       <c r="G46" t="n">
-        <v>0.551074087619781</v>
+        <v>0.551074147224426</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G47" t="n">
-        <v>0.561604082584381</v>
+        <v>0.561604142189026</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G49" t="n">
-        <v>0.570028126239777</v>
+        <v>0.570028185844421</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G51" t="n">
-        <v>0.565816044807434</v>
+        <v>0.565816104412079</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>0.772499978542328</v>
       </c>
       <c r="G52" t="n">
-        <v>0.542299032211304</v>
+        <v>0.542298972606659</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>0.773000001907349</v>
       </c>
       <c r="G53" t="n">
-        <v>0.542650043964386</v>
+        <v>0.542649865150452</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G55" t="n">
-        <v>0.536331951618195</v>
+        <v>0.53633189201355</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>0.533523917198181</v>
+        <v>0.533523857593536</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>0.773500025272369</v>
       </c>
       <c r="G57" t="n">
-        <v>0.543000996112823</v>
+        <v>0.543001055717468</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G58" t="n">
-        <v>0.561604082584381</v>
+        <v>0.561604142189026</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>0.766499996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>0.538087010383606</v>
+        <v>0.538086831569672</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>0.766499996185303</v>
       </c>
       <c r="G60" t="n">
-        <v>0.538087010383606</v>
+        <v>0.538086831569672</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>0.760999977588654</v>
       </c>
       <c r="G64" t="n">
-        <v>0.534225940704346</v>
+        <v>0.534225881099701</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G65" t="n">
-        <v>0.533523917198181</v>
+        <v>0.533523857593536</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>0.75</v>
       </c>
       <c r="G68" t="n">
-        <v>0.526503920555115</v>
+        <v>0.52650386095047</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>0.765500009059906</v>
       </c>
       <c r="G69" t="n">
-        <v>0.537384927272797</v>
+        <v>0.537384867668152</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>0.787000000476837</v>
       </c>
       <c r="G71" t="n">
-        <v>0.552478015422821</v>
+        <v>0.552477955818176</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>0.795000016689301</v>
       </c>
       <c r="G72" t="n">
-        <v>0.558094084262848</v>
+        <v>0.558094143867493</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G73" t="n">
-        <v>0.558796107769012</v>
+        <v>0.558795988559723</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>0.795000016689301</v>
       </c>
       <c r="G76" t="n">
-        <v>0.558094084262848</v>
+        <v>0.558094143867493</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G77" t="n">
-        <v>0.57283616065979</v>
+        <v>0.572836101055145</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>0.817499995231628</v>
       </c>
       <c r="G80" t="n">
-        <v>0.573889195919037</v>
+        <v>0.573889255523682</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>0.790499985218048</v>
       </c>
       <c r="G81" t="n">
-        <v>0.554935038089752</v>
+        <v>0.554935097694397</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>0.790499985218048</v>
       </c>
       <c r="G82" t="n">
-        <v>0.554935038089752</v>
+        <v>0.554935097694397</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G83" t="n">
-        <v>0.548967957496643</v>
+        <v>0.548968017101288</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>0.766499996185303</v>
       </c>
       <c r="G84" t="n">
-        <v>0.538087010383606</v>
+        <v>0.538086831569672</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G85" t="n">
-        <v>0.540543913841248</v>
+        <v>0.540543973445892</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G88" t="n">
-        <v>0.537735939025879</v>
+        <v>0.537735879421234</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G89" t="n">
-        <v>0.540543913841248</v>
+        <v>0.540543973445892</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G90" t="n">
-        <v>0.53703385591507</v>
+        <v>0.537033915519714</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>0.751500010490417</v>
       </c>
       <c r="G91" t="n">
-        <v>0.527556777000427</v>
+        <v>0.527556836605072</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G92" t="n">
-        <v>0.519483864307404</v>
+        <v>0.519483804702759</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G94" t="n">
-        <v>0.53703385591507</v>
+        <v>0.537033915519714</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>0.745000004768372</v>
       </c>
       <c r="G96" t="n">
-        <v>0.522993803024292</v>
+        <v>0.522993862628937</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G97" t="n">
-        <v>0.519483864307404</v>
+        <v>0.519483804702759</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>0.710500001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>0.49877455830574</v>
+        <v>0.49877467751503</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>0.715499997138977</v>
       </c>
       <c r="G100" t="n">
-        <v>0.502284646034241</v>
+        <v>0.502284705638885</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>0.736500024795532</v>
       </c>
       <c r="G107" t="n">
-        <v>0.517026782035828</v>
+        <v>0.517026841640472</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>0.746500015258789</v>
       </c>
       <c r="G108" t="n">
-        <v>0.524046838283539</v>
+        <v>0.524046897888184</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G111" t="n">
-        <v>0.520064175128937</v>
+        <v>0.520064115524292</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G115" t="n">
-        <v>0.511347889900208</v>
+        <v>0.511347949504852</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>0.700500011444092</v>
       </c>
       <c r="G116" t="n">
-        <v>0.508805692195892</v>
+        <v>0.508805811405182</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>0.689000010490417</v>
       </c>
       <c r="G117" t="n">
-        <v>0.500452756881714</v>
+        <v>0.500452637672424</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>0.700500011444092</v>
       </c>
       <c r="G118" t="n">
-        <v>0.508805692195892</v>
+        <v>0.508805811405182</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>0.700500011444092</v>
       </c>
       <c r="G121" t="n">
-        <v>0.508805692195892</v>
+        <v>0.508805811405182</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>0.720499992370605</v>
       </c>
       <c r="G123" t="n">
-        <v>0.523332715034485</v>
+        <v>0.52333265542984</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>0.683000028133392</v>
       </c>
       <c r="G124" t="n">
-        <v>0.496094703674316</v>
+        <v>0.496094733476639</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G125" t="n">
-        <v>0.501179099082947</v>
+        <v>0.501179039478302</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>0.70550000667572</v>
       </c>
       <c r="G126" t="n">
-        <v>0.512437462806702</v>
+        <v>0.512437403202057</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G128" t="n">
-        <v>0.509895324707031</v>
+        <v>0.509895265102386</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G129" t="n">
-        <v>0.517158806324005</v>
+        <v>0.517158687114716</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G130" t="n">
-        <v>0.504810810089111</v>
+        <v>0.504810750484467</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G131" t="n">
-        <v>0.496820956468582</v>
+        <v>0.49682092666626</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G133" t="n">
-        <v>0.476483345031738</v>
+        <v>0.476483285427094</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>0.661499977111816</v>
       </c>
       <c r="G134" t="n">
-        <v>0.480478167533875</v>
+        <v>0.480478227138519</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G139" t="n">
-        <v>0.492462903261185</v>
+        <v>0.492462933063507</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>0.697499990463257</v>
       </c>
       <c r="G142" t="n">
-        <v>0.506626665592194</v>
+        <v>0.506626725196838</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>0.680999994277954</v>
       </c>
       <c r="G143" t="n">
-        <v>0.494641989469528</v>
+        <v>0.494642078876495</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G144" t="n">
-        <v>0.493915617465973</v>
+        <v>0.493915528059006</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>0.690500020980835</v>
       </c>
       <c r="G146" t="n">
-        <v>0.501542210578918</v>
+        <v>0.501542270183563</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>0.666999995708466</v>
       </c>
       <c r="G148" t="n">
-        <v>0.484473049640656</v>
+        <v>0.4844731092453</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>0.665499985218048</v>
       </c>
       <c r="G149" t="n">
-        <v>0.483383536338806</v>
+        <v>0.483383566141129</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>0.673500001430511</v>
       </c>
       <c r="G151" t="n">
-        <v>0.489194363355637</v>
+        <v>0.489194422960281</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>0.677500009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>0.492099702358246</v>
+        <v>0.492099761962891</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>0.677500009536743</v>
       </c>
       <c r="G157" t="n">
-        <v>0.492099702358246</v>
+        <v>0.492099761962891</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>0.685000002384186</v>
       </c>
       <c r="G158" t="n">
-        <v>0.497547328472137</v>
+        <v>0.497547298669815</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>0.694500029087067</v>
       </c>
       <c r="G159" t="n">
-        <v>0.504447638988495</v>
+        <v>0.50444757938385</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G162" t="n">
-        <v>0.531685531139374</v>
+        <v>0.531685650348663</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G163" t="n">
-        <v>0.538949072360992</v>
+        <v>0.538949012756348</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>0.746500015258789</v>
       </c>
       <c r="G167" t="n">
-        <v>0.542217671871185</v>
+        <v>0.54221773147583</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>0.746500015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>0.542217671871185</v>
+        <v>0.54221773147583</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>0.771499991416931</v>
       </c>
       <c r="G172" t="n">
-        <v>0.560376286506653</v>
+        <v>0.560376346111298</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G173" t="n">
-        <v>0.566550254821777</v>
+        <v>0.566550195217133</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G174" t="n">
-        <v>0.559286713600159</v>
+        <v>0.559286832809448</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>0.767499983310699</v>
       </c>
       <c r="G175" t="n">
-        <v>0.557470977306366</v>
+        <v>0.557470738887787</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>0.778999984264374</v>
       </c>
       <c r="G176" t="n">
-        <v>0.565823972225189</v>
+        <v>0.565823912620544</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>0.773000001907349</v>
       </c>
       <c r="G177" t="n">
-        <v>0.561465859413147</v>
+        <v>0.561465740203857</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>0.773000001907349</v>
       </c>
       <c r="G178" t="n">
-        <v>0.561465859413147</v>
+        <v>0.561465740203857</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>0.771000027656555</v>
       </c>
       <c r="G179" t="n">
-        <v>0.560013115406036</v>
+        <v>0.560013175010681</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G180" t="n">
-        <v>0.559286713600159</v>
+        <v>0.559286832809448</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>0.757499992847443</v>
       </c>
       <c r="G182" t="n">
-        <v>0.550207555294037</v>
+        <v>0.550207436084747</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G185" t="n">
-        <v>0.565097630023956</v>
+        <v>0.565097510814667</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>0.796999990940094</v>
       </c>
       <c r="G186" t="n">
-        <v>0.578898191452026</v>
+        <v>0.578898131847382</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>0.805000007152557</v>
       </c>
       <c r="G187" t="n">
-        <v>0.58470892906189</v>
+        <v>0.584708988666534</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>0.792500019073486</v>
       </c>
       <c r="G188" t="n">
-        <v>0.575629591941833</v>
+        <v>0.575629651546478</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G189" t="n">
-        <v>0.573813736438751</v>
+        <v>0.573813796043396</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G190" t="n">
-        <v>0.566550254821777</v>
+        <v>0.566550195217133</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G191" t="n">
-        <v>0.572361052036285</v>
+        <v>0.572360992431641</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>0.792999982833862</v>
       </c>
       <c r="G192" t="n">
-        <v>0.57599276304245</v>
+        <v>0.575992703437805</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G194" t="n">
-        <v>0.58107727766037</v>
+        <v>0.581077218055725</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G195" t="n">
-        <v>0.58107727766037</v>
+        <v>0.581077218055725</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>0.783500015735626</v>
       </c>
       <c r="G196" t="n">
-        <v>0.569092452526093</v>
+        <v>0.569092571735382</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>0.783500015735626</v>
       </c>
       <c r="G197" t="n">
-        <v>0.569092452526093</v>
+        <v>0.569092571735382</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G198" t="n">
-        <v>0.573813736438751</v>
+        <v>0.573813796043396</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>0.805000007152557</v>
       </c>
       <c r="G199" t="n">
-        <v>0.58470892906189</v>
+        <v>0.584708988666534</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>0.795499980449677</v>
       </c>
       <c r="G203" t="n">
-        <v>0.577808678150177</v>
+        <v>0.577808618545532</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>0.795499980449677</v>
       </c>
       <c r="G204" t="n">
-        <v>0.577808678150177</v>
+        <v>0.577808618545532</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>0.795499980449677</v>
       </c>
       <c r="G205" t="n">
-        <v>0.577808678150177</v>
+        <v>0.577808618545532</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G206" t="n">
-        <v>0.578171849250793</v>
+        <v>0.578171730041504</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G215" t="n">
-        <v>0.594151377677917</v>
+        <v>0.594151496887207</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>0.828999996185303</v>
       </c>
       <c r="G217" t="n">
-        <v>0.602141201496124</v>
+        <v>0.602141261100769</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>0.819500029087067</v>
       </c>
       <c r="G220" t="n">
-        <v>0.595240890979767</v>
+        <v>0.595240950584412</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>0.817499995231628</v>
       </c>
       <c r="G221" t="n">
-        <v>0.593788266181946</v>
+        <v>0.593788325786591</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>0.824999988079071</v>
       </c>
       <c r="G222" t="n">
-        <v>0.599235832691193</v>
+        <v>0.599235892295837</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>0.841000020503998</v>
       </c>
       <c r="G223" t="n">
-        <v>0.610857367515564</v>
+        <v>0.610857427120209</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G224" t="n">
-        <v>0.610131025314331</v>
+        <v>0.610131084918976</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>0.83050000667572</v>
       </c>
       <c r="G225" t="n">
-        <v>0.603230714797974</v>
+        <v>0.603230834007263</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>0.829500019550323</v>
       </c>
       <c r="G227" t="n">
-        <v>0.602504372596741</v>
+        <v>0.602504432201385</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>0.83050000667572</v>
       </c>
       <c r="G228" t="n">
-        <v>0.603230714797974</v>
+        <v>0.603230834007263</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G229" t="n">
-        <v>0.595604062080383</v>
+        <v>0.595604181289673</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G231" t="n">
-        <v>0.595604062080383</v>
+        <v>0.595604181289673</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G232" t="n">
-        <v>0.595604062080383</v>
+        <v>0.595604181289673</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>0.814999997615814</v>
       </c>
       <c r="G233" t="n">
-        <v>0.591972410678864</v>
+        <v>0.591972351074219</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>0.83050000667572</v>
       </c>
       <c r="G234" t="n">
-        <v>0.603230714797974</v>
+        <v>0.603230834007263</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G235" t="n">
-        <v>0.599962174892426</v>
+        <v>0.599962055683136</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G236" t="n">
-        <v>0.602867543697357</v>
+        <v>0.602867603302002</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G237" t="n">
-        <v>0.602867543697357</v>
+        <v>0.602867603302002</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G238" t="n">
-        <v>0.602867543697357</v>
+        <v>0.602867603302002</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G239" t="n">
-        <v>0.602867543697357</v>
+        <v>0.602867603302002</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G240" t="n">
-        <v>0.606499314308167</v>
+        <v>0.606499254703522</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G241" t="n">
-        <v>0.60867840051651</v>
+        <v>0.608678460121155</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G242" t="n">
-        <v>0.610131025314331</v>
+        <v>0.610131084918976</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G244" t="n">
-        <v>0.610131025314331</v>
+        <v>0.610131084918976</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G246" t="n">
-        <v>0.624658048152924</v>
+        <v>0.624657988548279</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G247" t="n">
-        <v>0.614489078521729</v>
+        <v>0.614489138126373</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G248" t="n">
-        <v>0.624658048152924</v>
+        <v>0.624657988548279</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>0.865499973297119</v>
       </c>
       <c r="G249" t="n">
-        <v>0.62865287065506</v>
+        <v>0.628652811050415</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>0.883000016212463</v>
       </c>
       <c r="G250" t="n">
-        <v>0.641363918781281</v>
+        <v>0.641363978385925</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>0.876500010490417</v>
       </c>
       <c r="G252" t="n">
-        <v>0.636642694473267</v>
+        <v>0.636642754077911</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G253" t="n">
-        <v>0.634826898574829</v>
+        <v>0.63482677936554</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>0.872500002384186</v>
       </c>
       <c r="G254" t="n">
-        <v>0.63373738527298</v>
+        <v>0.633737325668335</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>0.895500004291534</v>
       </c>
       <c r="G255" t="n">
-        <v>0.650443196296692</v>
+        <v>0.650443255901337</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>0.912500023841858</v>
       </c>
       <c r="G256" t="n">
-        <v>0.662791192531586</v>
+        <v>0.66279125213623</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G258" t="n">
-        <v>0.665333390235901</v>
+        <v>0.665333449840546</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G259" t="n">
-        <v>0.653711795806885</v>
+        <v>0.653711915016174</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>0.903500020503998</v>
       </c>
       <c r="G267" t="n">
-        <v>0.6562539935112</v>
+        <v>0.656254053115845</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>0.934499979019165</v>
       </c>
       <c r="G269" t="n">
-        <v>0.678770840167999</v>
+        <v>0.678770780563354</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>0.944999992847443</v>
       </c>
       <c r="G272" t="n">
-        <v>0.68639749288559</v>
+        <v>0.686397433280945</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>0.957499980926514</v>
       </c>
       <c r="G273" t="n">
-        <v>0.695476830005646</v>
+        <v>0.695476710796356</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>0.968999981880188</v>
       </c>
       <c r="G274" t="n">
-        <v>0.703829705715179</v>
+        <v>0.703829646110535</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G276" t="n">
-        <v>0.698745369911194</v>
+        <v>0.698745310306549</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>0.950500011444092</v>
       </c>
       <c r="G277" t="n">
-        <v>0.690392374992371</v>
+        <v>0.690392315387726</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>0.91949999332428</v>
       </c>
       <c r="G278" t="n">
-        <v>0.667875707149506</v>
+        <v>0.667875587940216</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G281" t="n">
-        <v>0.682765781879425</v>
+        <v>0.682765662670135</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G282" t="n">
-        <v>0.690029144287109</v>
+        <v>0.690029203891754</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>0.953000009059906</v>
       </c>
       <c r="G285" t="n">
-        <v>0.692208230495453</v>
+        <v>0.692208111286163</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G286" t="n">
-        <v>0.711819529533386</v>
+        <v>0.711819589138031</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G287" t="n">
-        <v>0.720535755157471</v>
+        <v>0.720535635948181</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>0.980499982833862</v>
       </c>
       <c r="G288" t="n">
-        <v>0.712182760238647</v>
+        <v>0.712182700634003</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>0.974500000476837</v>
       </c>
       <c r="G289" t="n">
-        <v>0.707824647426605</v>
+        <v>0.70782470703125</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G290" t="n">
-        <v>0.711819529533386</v>
+        <v>0.711819589138031</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>0.981500029563904</v>
       </c>
       <c r="G291" t="n">
-        <v>0.712908983230591</v>
+        <v>0.712909042835236</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G292" t="n">
-        <v>0.711819529533386</v>
+        <v>0.711819589138031</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>0.977500021457672</v>
       </c>
       <c r="G293" t="n">
-        <v>0.710003674030304</v>
+        <v>0.710003733634949</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>0.995500028133392</v>
       </c>
       <c r="G294" t="n">
-        <v>0.723077893257141</v>
+        <v>0.723078012466431</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G297" t="n">
-        <v>0.780822396278381</v>
+        <v>0.780822515487671</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>1.12100005149841</v>
       </c>
       <c r="G299" t="n">
-        <v>0.81423431634903</v>
+        <v>0.814234435558319</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G300" t="n">
-        <v>0.845467388629913</v>
+        <v>0.845467448234558</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G301" t="n">
-        <v>0.857088804244995</v>
+        <v>0.85708874464035</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>1.20299994945526</v>
       </c>
       <c r="G302" t="n">
-        <v>0.873794853687286</v>
+        <v>0.873794734477997</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G303" t="n">
-        <v>0.918828308582306</v>
+        <v>0.918828248977661</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G305" t="n">
-        <v>0.919554650783539</v>
+        <v>0.919554710388184</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G306" t="n">
-        <v>0.882510960102081</v>
+        <v>0.882511079311371</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>1.28900003433228</v>
       </c>
       <c r="G307" t="n">
-        <v>0.936260461807251</v>
+        <v>0.936260759830475</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G308" t="n">
-        <v>0.955145537853241</v>
+        <v>0.955145716667175</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G310" t="n">
-        <v>0.997999966144562</v>
+        <v>0.998000025749207</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G311" t="n">
-        <v>0.980567634105682</v>
+        <v>0.980567693710327</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>1.35399997234344</v>
       </c>
       <c r="G312" t="n">
-        <v>0.983473122119904</v>
+        <v>0.983473241329193</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G313" t="n">
-        <v>0.974756896495819</v>
+        <v>0.974757075309753</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>1.33200001716614</v>
       </c>
       <c r="G314" t="n">
-        <v>0.967493534088135</v>
+        <v>0.96749347448349</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>1.35599994659424</v>
       </c>
       <c r="G315" t="n">
-        <v>0.984925806522369</v>
+        <v>0.984925866127014</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G316" t="n">
-        <v>1.02778041362762</v>
+        <v>1.02778017520905</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G317" t="n">
-        <v>1.0626448392868</v>
+        <v>1.06264495849609</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G318" t="n">
-        <v>1.10985732078552</v>
+        <v>1.10985743999481</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G319" t="n">
-        <v>1.1476274728775</v>
+        <v>1.14762759208679</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G320" t="n">
-        <v>1.13310050964355</v>
+        <v>1.13310039043427</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G321" t="n">
-        <v>1.13310050964355</v>
+        <v>1.13310039043427</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G322" t="n">
-        <v>1.09315133094788</v>
+        <v>1.09315156936646</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G328" t="n">
-        <v>1.19120812416077</v>
+        <v>1.19120836257935</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G329" t="n">
-        <v>1.19120812416077</v>
+        <v>1.19120836257935</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G330" t="n">
-        <v>1.16941785812378</v>
+        <v>1.16941797733307</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G331" t="n">
-        <v>1.14036405086517</v>
+        <v>1.14036417007446</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G332" t="n">
-        <v>1.11494195461273</v>
+        <v>1.11494147777557</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>1.58599996566772</v>
       </c>
       <c r="G333" t="n">
-        <v>1.1519855260849</v>
+        <v>1.15198540687561</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>1.56900000572205</v>
       </c>
       <c r="G334" t="n">
-        <v>1.13963758945465</v>
+        <v>1.13963770866394</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G335" t="n">
-        <v>1.11494195461273</v>
+        <v>1.11494147777557</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G339" t="n">
-        <v>1.16215455532074</v>
+        <v>1.16215443611145</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>1.59300005435944</v>
       </c>
       <c r="G340" t="n">
-        <v>1.15707004070282</v>
+        <v>1.15706992149353</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G341" t="n">
-        <v>1.23478889465332</v>
+        <v>1.23478901386261</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G342" t="n">
-        <v>1.23478889465332</v>
+        <v>1.23478901386261</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G345" t="n">
-        <v>1.27837002277374</v>
+        <v>1.27836978435516</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G346" t="n">
-        <v>1.27837002277374</v>
+        <v>1.27836978435516</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G348" t="n">
-        <v>1.34809923171997</v>
+        <v>1.34809911251068</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G349" t="n">
-        <v>1.36480498313904</v>
+        <v>1.36480510234833</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G350" t="n">
-        <v>1.4018486738205</v>
+        <v>1.40184879302979</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G351" t="n">
-        <v>1.40548050403595</v>
+        <v>1.40548038482666</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G352" t="n">
-        <v>1.30451834201813</v>
+        <v>1.30451822280884</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G353" t="n">
-        <v>1.34374105930328</v>
+        <v>1.34374094009399</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>1.85300004482269</v>
       </c>
       <c r="G354" t="n">
-        <v>1.34592020511627</v>
+        <v>1.34592008590698</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>1.76900005340576</v>
       </c>
       <c r="G356" t="n">
-        <v>1.28490686416626</v>
+        <v>1.28490674495697</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>1.80299997329712</v>
       </c>
       <c r="G357" t="n">
-        <v>1.30960273742676</v>
+        <v>1.30960285663605</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G358" t="n">
-        <v>1.30742359161377</v>
+        <v>1.30742383003235</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>1.7389999628067</v>
       </c>
       <c r="G360" t="n">
-        <v>1.26311671733856</v>
+        <v>1.26311647891998</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G363" t="n">
-        <v>1.28563332557678</v>
+        <v>1.2856330871582</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G365" t="n">
-        <v>1.31839036941528</v>
+        <v>1.31839048862457</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G366" t="n">
-        <v>1.30357718467712</v>
+        <v>1.30357706546783</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>1.75</v>
       </c>
       <c r="G367" t="n">
-        <v>1.29617035388947</v>
+        <v>1.29617023468018</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G369" t="n">
-        <v>1.28135693073273</v>
+        <v>1.28135704994202</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G370" t="n">
-        <v>1.23691689968109</v>
+        <v>1.2369167804718</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G371" t="n">
-        <v>1.26654386520386</v>
+        <v>1.26654374599457</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G373" t="n">
-        <v>1.25173032283783</v>
+        <v>1.25173020362854</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>1.61300003528595</v>
       </c>
       <c r="G374" t="n">
-        <v>1.19469881057739</v>
+        <v>1.1946986913681</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>1.68900001049042</v>
       </c>
       <c r="G375" t="n">
-        <v>1.25098943710327</v>
+        <v>1.25098967552185</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>1.72899997234344</v>
       </c>
       <c r="G377" t="n">
-        <v>1.28061640262604</v>
+        <v>1.28061628341675</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G378" t="n">
-        <v>1.27246916294098</v>
+        <v>1.27246904373169</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G379" t="n">
-        <v>1.27395045757294</v>
+        <v>1.27395021915436</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G380" t="n">
-        <v>1.27469110488892</v>
+        <v>1.27469086647034</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G381" t="n">
-        <v>1.24876749515533</v>
+        <v>1.24876773357391</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>1.69200003147125</v>
       </c>
       <c r="G382" t="n">
-        <v>1.2532114982605</v>
+        <v>1.25321161746979</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G384" t="n">
-        <v>1.22210347652435</v>
+        <v>1.22210359573364</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G386" t="n">
-        <v>1.23395419120789</v>
+        <v>1.23395431041718</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G387" t="n">
-        <v>1.22951006889343</v>
+        <v>1.22951018810272</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>1.62899994850159</v>
       </c>
       <c r="G388" t="n">
-        <v>1.20654952526093</v>
+        <v>1.20654940605164</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>1.63900005817413</v>
       </c>
       <c r="G390" t="n">
-        <v>1.21395611763</v>
+        <v>1.21395623683929</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G391" t="n">
-        <v>1.21469664573669</v>
+        <v>1.21469688415527</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G392" t="n">
-        <v>1.21099352836609</v>
+        <v>1.21099364757538</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G393" t="n">
-        <v>1.19395792484283</v>
+        <v>1.19395804405212</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G394" t="n">
-        <v>1.2072901725769</v>
+        <v>1.20729029178619</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>1.63100004196167</v>
       </c>
       <c r="G395" t="n">
-        <v>1.20803070068359</v>
+        <v>1.20803081989288</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>1.61899995803833</v>
       </c>
       <c r="G396" t="n">
-        <v>1.19914269447327</v>
+        <v>1.19914281368256</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G397" t="n">
-        <v>1.2072901725769</v>
+        <v>1.20729029178619</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G398" t="n">
-        <v>1.2072901725769</v>
+        <v>1.20729029178619</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G399" t="n">
-        <v>1.19247674942017</v>
+        <v>1.19247686862946</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G400" t="n">
-        <v>1.19247674942017</v>
+        <v>1.19247686862946</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G401" t="n">
-        <v>1.19840228557587</v>
+        <v>1.19840204715729</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>1.60699999332428</v>
       </c>
       <c r="G402" t="n">
-        <v>1.19025480747223</v>
+        <v>1.19025468826294</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G406" t="n">
-        <v>1.2072901725769</v>
+        <v>1.20729029178619</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G411" t="n">
-        <v>1.18507027626038</v>
+        <v>1.1850700378418</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G413" t="n">
-        <v>1.18358862400055</v>
+        <v>1.18358886241913</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G415" t="n">
-        <v>1.16803479194641</v>
+        <v>1.16803467273712</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>1.54799997806549</v>
       </c>
       <c r="G417" t="n">
-        <v>1.14655518531799</v>
+        <v>1.14655542373657</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>1.54700005054474</v>
       </c>
       <c r="G418" t="n">
-        <v>1.14581453800201</v>
+        <v>1.14581477642059</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G419" t="n">
-        <v>1.12433516979218</v>
+        <v>1.12433540821075</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G420" t="n">
-        <v>1.12211334705353</v>
+        <v>1.12211322784424</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G421" t="n">
-        <v>1.12877929210663</v>
+        <v>1.12877941131592</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>1.5110000371933</v>
       </c>
       <c r="G422" t="n">
-        <v>1.11915051937103</v>
+        <v>1.11915063858032</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>1.51699995994568</v>
       </c>
       <c r="G423" t="n">
-        <v>1.1235945224762</v>
+        <v>1.12359440326691</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G424" t="n">
-        <v>1.17766344547272</v>
+        <v>1.17766356468201</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G425" t="n">
-        <v>1.14062976837158</v>
+        <v>1.14063000679016</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G426" t="n">
-        <v>1.1554434299469</v>
+        <v>1.15544331073761</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G429" t="n">
-        <v>1.17766344547272</v>
+        <v>1.17766356468201</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>1.73099994659424</v>
       </c>
       <c r="G431" t="n">
-        <v>1.282097697258</v>
+        <v>1.28209757804871</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G432" t="n">
-        <v>1.25173032283783</v>
+        <v>1.25173020362854</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G434" t="n">
-        <v>1.26654386520386</v>
+        <v>1.26654374599457</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G440" t="n">
-        <v>1.37468135356903</v>
+        <v>1.37468123435974</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G442" t="n">
-        <v>1.39245748519897</v>
+        <v>1.39245736598969</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G444" t="n">
-        <v>1.41986215114594</v>
+        <v>1.41986203193665</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G445" t="n">
-        <v>1.48059701919556</v>
+        <v>1.48059678077698</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>1.98800003528595</v>
       </c>
       <c r="G452" t="n">
-        <v>1.47244954109192</v>
+        <v>1.47244966030121</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G453" t="n">
-        <v>1.44430422782898</v>
+        <v>1.44430434703827</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G455" t="n">
-        <v>1.39245748519897</v>
+        <v>1.39245736598969</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G456" t="n">
-        <v>1.39690136909485</v>
+        <v>1.39690124988556</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>1.89900004863739</v>
       </c>
       <c r="G457" t="n">
-        <v>1.40653002262115</v>
+        <v>1.40653014183044</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>1.91600000858307</v>
       </c>
       <c r="G460" t="n">
-        <v>1.41912150382996</v>
+        <v>1.41912126541138</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G461" t="n">
-        <v>1.40060460567474</v>
+        <v>1.40060472488403</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G463" t="n">
-        <v>1.41319632530212</v>
+        <v>1.41319608688354</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G464" t="n">
-        <v>1.39986419677734</v>
+        <v>1.39986407756805</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G465" t="n">
-        <v>1.4213433265686</v>
+        <v>1.42134344577789</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G466" t="n">
-        <v>1.39986419677734</v>
+        <v>1.39986407756805</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G467" t="n">
-        <v>1.42208409309387</v>
+        <v>1.42208397388458</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G468" t="n">
-        <v>1.38505065441132</v>
+        <v>1.38505053520203</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G470" t="n">
-        <v>1.37171864509583</v>
+        <v>1.37171876430511</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G471" t="n">
-        <v>1.39245748519897</v>
+        <v>1.39245736598969</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>1.87300002574921</v>
       </c>
       <c r="G472" t="n">
-        <v>1.38727271556854</v>
+        <v>1.38727259635925</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G473" t="n">
-        <v>1.36579310894012</v>
+        <v>1.3657933473587</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>1.84700000286102</v>
       </c>
       <c r="G474" t="n">
-        <v>1.36801517009735</v>
+        <v>1.36801528930664</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G478" t="n">
-        <v>1.22210347652435</v>
+        <v>1.22210359573364</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G483" t="n">
-        <v>1.09618997573853</v>
+        <v>1.09618985652924</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>1.53299999237061</v>
       </c>
       <c r="G485" t="n">
-        <v>1.13544523715973</v>
+        <v>1.13544511795044</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>1.48300004005432</v>
       </c>
       <c r="G486" t="n">
-        <v>1.09841179847717</v>
+        <v>1.09841191768646</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G487" t="n">
-        <v>1.10507774353027</v>
+        <v>1.10507786273956</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G488" t="n">
-        <v>1.08878326416016</v>
+        <v>1.08878314495087</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>1.45899999141693</v>
       </c>
       <c r="G489" t="n">
-        <v>1.08063590526581</v>
+        <v>1.08063578605652</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>1.4190000295639</v>
       </c>
       <c r="G490" t="n">
-        <v>1.05100905895233</v>
+        <v>1.05100893974304</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G491" t="n">
-        <v>1.01767885684967</v>
+        <v>1.01767897605896</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G494" t="n">
-        <v>1.04952788352966</v>
+        <v>1.04952764511108</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G495" t="n">
-        <v>1.02212297916412</v>
+        <v>1.02212285995483</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G496" t="n">
-        <v>1.00138425827026</v>
+        <v>1.00138437747955</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G497" t="n">
-        <v>1.03693616390228</v>
+        <v>1.03693628311157</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>1.42900002002716</v>
       </c>
       <c r="G499" t="n">
-        <v>1.05841565132141</v>
+        <v>1.05841553211212</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G500" t="n">
-        <v>1.03693616390228</v>
+        <v>1.03693628311157</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>1.4190000295639</v>
       </c>
       <c r="G501" t="n">
-        <v>1.05100905895233</v>
+        <v>1.05100893974304</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G502" t="n">
-        <v>1.05915641784668</v>
+        <v>1.0591561794281</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G503" t="n">
-        <v>1.06285965442657</v>
+        <v>1.06285953521729</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>1.43799996376038</v>
       </c>
       <c r="G504" t="n">
-        <v>1.06508183479309</v>
+        <v>1.06508159637451</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G505" t="n">
-        <v>1.05026841163635</v>
+        <v>1.05026829242706</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>1.42400002479553</v>
       </c>
       <c r="G506" t="n">
-        <v>1.05471253395081</v>
+        <v>1.05471229553223</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G507" t="n">
-        <v>1.06360030174255</v>
+        <v>1.06360042095184</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G510" t="n">
-        <v>1.08878326416016</v>
+        <v>1.08878314495087</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G511" t="n">
-        <v>1.06285965442657</v>
+        <v>1.06285953521729</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G512" t="n">
-        <v>1.0776731967926</v>
+        <v>1.07767307758331</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G513" t="n">
-        <v>1.06360030174255</v>
+        <v>1.06360042095184</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G514" t="n">
-        <v>1.0813764333725</v>
+        <v>1.08137655258179</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G515" t="n">
-        <v>1.14062976837158</v>
+        <v>1.14063000679016</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G516" t="n">
-        <v>1.21469664573669</v>
+        <v>1.21469688415527</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G517" t="n">
-        <v>1.21173417568207</v>
+        <v>1.21173441410065</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G518" t="n">
-        <v>1.18358862400055</v>
+        <v>1.18358886241913</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G519" t="n">
-        <v>1.17914485931396</v>
+        <v>1.17914462089539</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G520" t="n">
-        <v>1.17173802852631</v>
+        <v>1.17173790931702</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G521" t="n">
-        <v>1.18507027626038</v>
+        <v>1.1850700378418</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G522" t="n">
-        <v>1.16581273078918</v>
+        <v>1.1658126115799</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G523" t="n">
-        <v>1.15692472457886</v>
+        <v>1.15692484378815</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G524" t="n">
-        <v>1.13914859294891</v>
+        <v>1.1391487121582</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G525" t="n">
-        <v>1.12877929210663</v>
+        <v>1.12877941131592</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G526" t="n">
-        <v>1.14359259605408</v>
+        <v>1.14359271526337</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>1.60399997234344</v>
       </c>
       <c r="G527" t="n">
-        <v>1.18803286552429</v>
+        <v>1.188032746315</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G528" t="n">
-        <v>1.18358862400055</v>
+        <v>1.18358886241913</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G529" t="n">
-        <v>1.16581273078918</v>
+        <v>1.1658126115799</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G531" t="n">
-        <v>1.18507027626038</v>
+        <v>1.1850700378418</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G532" t="n">
-        <v>1.13914859294891</v>
+        <v>1.1391487121582</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G533" t="n">
-        <v>1.12729799747467</v>
+        <v>1.12729787826538</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G534" t="n">
-        <v>1.1554434299469</v>
+        <v>1.15544331073761</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G536" t="n">
-        <v>1.0813764333725</v>
+        <v>1.08137655258179</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G538" t="n">
-        <v>1.08582055568695</v>
+        <v>1.08582043647766</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G539" t="n">
-        <v>1.06360030174255</v>
+        <v>1.06360042095184</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G540" t="n">
-        <v>1.01619744300842</v>
+        <v>1.016197681427</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G542" t="n">
-        <v>0.985089421272278</v>
+        <v>0.985089540481567</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G543" t="n">
-        <v>1.03545486927032</v>
+        <v>1.03545498847961</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G544" t="n">
-        <v>1.01767885684967</v>
+        <v>1.01767897605896</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G545" t="n">
-        <v>1.03397369384766</v>
+        <v>1.03397357463837</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G549" t="n">
-        <v>0.991014897823334</v>
+        <v>0.991014838218689</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G550" t="n">
-        <v>0.993977427482605</v>
+        <v>0.993977606296539</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>1.31599998474121</v>
       </c>
       <c r="G551" t="n">
-        <v>0.974720001220703</v>
+        <v>0.974720239639282</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>1.28400003910065</v>
       </c>
       <c r="G552" t="n">
-        <v>0.951018929481506</v>
+        <v>0.951018810272217</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>1.29799997806549</v>
       </c>
       <c r="G554" t="n">
-        <v>0.961388230323792</v>
+        <v>0.961387991905212</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G556" t="n">
-        <v>0.927317321300507</v>
+        <v>0.927317202091217</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G557" t="n">
-        <v>0.998421609401703</v>
+        <v>0.998421728610992</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G558" t="n">
-        <v>1.03101086616516</v>
+        <v>1.03101098537445</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G561" t="n">
-        <v>1.02212297916412</v>
+        <v>1.02212285995483</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G562" t="n">
-        <v>1.03545486927032</v>
+        <v>1.03545498847961</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>1.37800002098083</v>
       </c>
       <c r="G563" t="n">
-        <v>1.02064168453217</v>
+        <v>1.02064144611359</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G564" t="n">
-        <v>1.03397369384766</v>
+        <v>1.03397357463837</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G565" t="n">
-        <v>1.05026841163635</v>
+        <v>1.05026829242706</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G567" t="n">
-        <v>1.0813764333725</v>
+        <v>1.08137655258179</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G569" t="n">
-        <v>1.03989911079407</v>
+        <v>1.03989899158478</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>1.43799996376038</v>
       </c>
       <c r="G570" t="n">
-        <v>1.06508183479309</v>
+        <v>1.06508159637451</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G573" t="n">
-        <v>1.02952969074249</v>
+        <v>1.0295295715332</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G574" t="n">
-        <v>1.03101086616516</v>
+        <v>1.03101098537445</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G576" t="n">
-        <v>0.991014897823334</v>
+        <v>0.991014838218689</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G577" t="n">
-        <v>1.01767885684967</v>
+        <v>1.01767897605896</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G581" t="n">
-        <v>0.992496252059937</v>
+        <v>0.992496311664581</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G582" t="n">
-        <v>0.998421609401703</v>
+        <v>0.998421728610992</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>1.34599995613098</v>
       </c>
       <c r="G583" t="n">
-        <v>0.9969402551651</v>
+        <v>0.996940135955811</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G584" t="n">
-        <v>1.02952969074249</v>
+        <v>1.0295295715332</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>1.38399994373322</v>
       </c>
       <c r="G585" t="n">
-        <v>1.02508544921875</v>
+        <v>1.02508556842804</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G586" t="n">
-        <v>1.02952969074249</v>
+        <v>1.0295295715332</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G587" t="n">
-        <v>1.04730570316315</v>
+        <v>1.04730582237244</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G588" t="n">
-        <v>1.02952969074249</v>
+        <v>1.0295295715332</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>1.38399994373322</v>
       </c>
       <c r="G589" t="n">
-        <v>1.02508544921875</v>
+        <v>1.02508556842804</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G590" t="n">
-        <v>1.01767885684967</v>
+        <v>1.01767897605896</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G593" t="n">
-        <v>1.00138425827026</v>
+        <v>1.00138437747955</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G594" t="n">
-        <v>0.992496252059937</v>
+        <v>0.992496311664581</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G595" t="n">
-        <v>1.05026841163635</v>
+        <v>1.05026829242706</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G596" t="n">
-        <v>1.08582055568695</v>
+        <v>1.08582043647766</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G597" t="n">
-        <v>1.09322702884674</v>
+        <v>1.09322690963745</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G599" t="n">
-        <v>1.09618997573853</v>
+        <v>1.09618985652924</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G603" t="n">
-        <v>1.06360030174255</v>
+        <v>1.06360042095184</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G605" t="n">
-        <v>1.02212297916412</v>
+        <v>1.02212285995483</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G607" t="n">
-        <v>0.985089421272278</v>
+        <v>0.985089540481567</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>1.317999958992</v>
       </c>
       <c r="G608" t="n">
-        <v>0.976201474666595</v>
+        <v>0.976201236248016</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>1.2940000295639</v>
       </c>
       <c r="G609" t="n">
-        <v>0.958425521850586</v>
+        <v>0.958425462245941</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G610" t="n">
-        <v>0.959906697273254</v>
+        <v>0.959906756877899</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>1.30799996852875</v>
       </c>
       <c r="G611" t="n">
-        <v>0.968794763088226</v>
+        <v>0.968794703483582</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G614" t="n">
-        <v>0.940649509429932</v>
+        <v>0.940649390220642</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>1.25</v>
       </c>
       <c r="G618" t="n">
-        <v>0.951411545276642</v>
+        <v>0.951411604881287</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G620" t="n">
-        <v>0.943800330162048</v>
+        <v>0.943800270557404</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G621" t="n">
-        <v>0.943800330162048</v>
+        <v>0.943800270557404</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G622" t="n">
-        <v>0.916399598121643</v>
+        <v>0.916399657726288</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G623" t="n">
-        <v>0.939233541488647</v>
+        <v>0.939233481884003</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G624" t="n">
-        <v>0.942278027534485</v>
+        <v>0.94227808713913</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G625" t="n">
-        <v>0.922488570213318</v>
+        <v>0.922488629817963</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>1.31599998474121</v>
       </c>
       <c r="G627" t="n">
-        <v>1.00164604187012</v>
+        <v>1.00164616107941</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G628" t="n">
-        <v>1.07471454143524</v>
+        <v>1.07471442222595</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G630" t="n">
-        <v>1.04122471809387</v>
+        <v>1.04122483730316</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G631" t="n">
-        <v>1.00925731658936</v>
+        <v>1.00925743579865</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G632" t="n">
-        <v>0.997079193592072</v>
+        <v>0.997079312801361</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G633" t="n">
-        <v>0.959022998809814</v>
+        <v>0.95902293920517</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>1.21599996089935</v>
       </c>
       <c r="G635" t="n">
-        <v>0.925533056259155</v>
+        <v>0.9255331158638</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>1.21800005435944</v>
       </c>
       <c r="G637" t="n">
-        <v>0.927055418491364</v>
+        <v>0.927055537700653</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G638" t="n">
-        <v>0.910310566425323</v>
+        <v>0.910310626029968</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>1.21800005435944</v>
       </c>
       <c r="G639" t="n">
-        <v>0.927055418491364</v>
+        <v>0.927055537700653</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>1.21800005435944</v>
       </c>
       <c r="G641" t="n">
-        <v>0.927055418491364</v>
+        <v>0.927055537700653</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G643" t="n">
-        <v>0.910310566425323</v>
+        <v>0.910310626029968</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G646" t="n">
-        <v>0.908788204193115</v>
+        <v>0.908788323402405</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G647" t="n">
-        <v>0.910310566425323</v>
+        <v>0.910310626029968</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>1.21399998664856</v>
       </c>
       <c r="G649" t="n">
-        <v>0.924010813236237</v>
+        <v>0.924010932445526</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>1.21599996089935</v>
       </c>
       <c r="G650" t="n">
-        <v>0.925533056259155</v>
+        <v>0.9255331158638</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G651" t="n">
-        <v>0.922488570213318</v>
+        <v>0.922488629817963</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G652" t="n">
-        <v>0.920966506004333</v>
+        <v>0.920966446399689</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G653" t="n">
-        <v>0.908788204193115</v>
+        <v>0.908788323402405</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G654" t="n">
-        <v>0.901176989078522</v>
+        <v>0.901177048683167</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G656" t="n">
-        <v>0.893565773963928</v>
+        <v>0.893565714359283</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G657" t="n">
-        <v>0.89661031961441</v>
+        <v>0.896610200405121</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G658" t="n">
-        <v>0.904221534729004</v>
+        <v>0.904221594333649</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G660" t="n">
-        <v>0.91335517168045</v>
+        <v>0.913355052471161</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G661" t="n">
-        <v>0.893565773963928</v>
+        <v>0.893565714359283</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G662" t="n">
-        <v>0.890521287918091</v>
+        <v>0.890521109104156</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G663" t="n">
-        <v>0.893565773963928</v>
+        <v>0.893565714359283</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G664" t="n">
-        <v>0.904221534729004</v>
+        <v>0.904221594333649</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G665" t="n">
-        <v>0.905743896961212</v>
+        <v>0.905743837356567</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G666" t="n">
-        <v>0.966634035110474</v>
+        <v>0.966634273529053</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G667" t="n">
-        <v>0.983379065990448</v>
+        <v>0.983378946781158</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G668" t="n">
-        <v>0.968156397342682</v>
+        <v>0.968156278133392</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>1.24800002574921</v>
       </c>
       <c r="G669" t="n">
-        <v>0.949889361858368</v>
+        <v>0.949889242649078</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G670" t="n">
-        <v>0.939233541488647</v>
+        <v>0.939233481884003</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G671" t="n">
-        <v>0.916399598121643</v>
+        <v>0.916399657726288</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G672" t="n">
-        <v>0.922488570213318</v>
+        <v>0.922488629817963</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G673" t="n">
-        <v>0.963589668273926</v>
+        <v>0.963589549064636</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G674" t="n">
-        <v>0.957500696182251</v>
+        <v>0.957500576972961</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G675" t="n">
-        <v>0.959022998809814</v>
+        <v>0.95902293920517</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G676" t="n">
-        <v>0.952933788299561</v>
+        <v>0.952933728694916</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G677" t="n">
-        <v>0.966634035110474</v>
+        <v>0.966634273529053</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G678" t="n">
-        <v>0.957500696182251</v>
+        <v>0.957500576972961</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>1.25</v>
       </c>
       <c r="G679" t="n">
-        <v>0.951411545276642</v>
+        <v>0.951411604881287</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G680" t="n">
-        <v>0.939233541488647</v>
+        <v>0.939233481884003</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G681" t="n">
-        <v>0.928577542304993</v>
+        <v>0.928577661514282</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G682" t="n">
-        <v>0.928577542304993</v>
+        <v>0.928577661514282</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G683" t="n">
-        <v>0.943800330162048</v>
+        <v>0.943800270557404</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G684" t="n">
-        <v>0.955978274345398</v>
+        <v>0.955978333950043</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G685" t="n">
-        <v>0.959022998809814</v>
+        <v>0.95902293920517</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>1.28400003910065</v>
       </c>
       <c r="G686" t="n">
-        <v>0.977289974689484</v>
+        <v>0.977290093898773</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>1.32200002670288</v>
       </c>
       <c r="G688" t="n">
-        <v>1.00621294975281</v>
+        <v>1.00621283054352</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>1.32200002670288</v>
       </c>
       <c r="G689" t="n">
-        <v>1.00621294975281</v>
+        <v>1.00621283054352</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G690" t="n">
-        <v>0.997079193592072</v>
+        <v>0.997079312801361</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G694" t="n">
-        <v>1.06558096408844</v>
+        <v>1.06558108329773</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>1.40600001811981</v>
       </c>
       <c r="G695" t="n">
-        <v>1.07014775276184</v>
+        <v>1.07014763355255</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G696" t="n">
-        <v>1.06405878067017</v>
+        <v>1.06405854225159</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G697" t="n">
-        <v>1.0625364780426</v>
+        <v>1.06253635883331</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G698" t="n">
-        <v>1.07166981697083</v>
+        <v>1.07167017459869</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G699" t="n">
-        <v>1.0625364780426</v>
+        <v>1.06253635883331</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G700" t="n">
-        <v>1.03665816783905</v>
+        <v>1.03665804862976</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G701" t="n">
-        <v>1.01686859130859</v>
+        <v>1.01686871051788</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>1.31599998474121</v>
       </c>
       <c r="G702" t="n">
-        <v>1.00164604187012</v>
+        <v>1.00164616107941</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G703" t="n">
-        <v>1.00925731658936</v>
+        <v>1.00925743579865</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>1.31400001049042</v>
       </c>
       <c r="G704" t="n">
-        <v>1.00012362003326</v>
+        <v>1.00012385845184</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G705" t="n">
-        <v>0.99251264333725</v>
+        <v>0.992512464523315</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G706" t="n">
-        <v>0.978812158107758</v>
+        <v>0.978812396526337</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G707" t="n">
-        <v>0.954455971717834</v>
+        <v>0.954456031322479</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G708" t="n">
-        <v>0.957500696182251</v>
+        <v>0.957500576972961</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G711" t="n">
-        <v>0.942278027534485</v>
+        <v>0.94227808713913</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G712" t="n">
-        <v>0.962067484855652</v>
+        <v>0.962067425251007</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G713" t="n">
-        <v>0.986423432826996</v>
+        <v>0.986423492431641</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G714" t="n">
-        <v>0.945322573184967</v>
+        <v>0.945322453975677</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G716" t="n">
-        <v>0.905743896961212</v>
+        <v>0.905743837356567</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G717" t="n">
-        <v>0.916399598121643</v>
+        <v>0.916399657726288</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G718" t="n">
-        <v>0.910310566425323</v>
+        <v>0.910310626029968</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G719" t="n">
-        <v>0.895087957382202</v>
+        <v>0.895088016986847</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G720" t="n">
-        <v>0.916399598121643</v>
+        <v>0.916399657726288</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G721" t="n">
-        <v>0.892043471336365</v>
+        <v>0.892043590545654</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G722" t="n">
-        <v>0.91335517168045</v>
+        <v>0.913355052471161</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G724" t="n">
-        <v>0.931622207164764</v>
+        <v>0.931622266769409</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G725" t="n">
-        <v>0.959022998809814</v>
+        <v>0.95902293920517</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G726" t="n">
-        <v>0.968156397342682</v>
+        <v>0.968156278133392</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G729" t="n">
-        <v>1.03513586521149</v>
+        <v>1.0351357460022</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G733" t="n">
-        <v>1.03361356258392</v>
+        <v>1.03361344337463</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G734" t="n">
-        <v>1.08080363273621</v>
+        <v>1.08080351352692</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>1.37800002098083</v>
       </c>
       <c r="G735" t="n">
-        <v>1.04883599281311</v>
+        <v>1.0488361120224</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>1.30799996852875</v>
       </c>
       <c r="G736" t="n">
-        <v>0.995557010173798</v>
+        <v>0.995556890964508</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G737" t="n">
-        <v>0.959022998809814</v>
+        <v>0.95902293920517</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G738" t="n">
-        <v>0.922488570213318</v>
+        <v>0.922488629817963</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>1.27600002288818</v>
       </c>
       <c r="G739" t="n">
-        <v>0.971200883388519</v>
+        <v>0.971201002597809</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G740" t="n">
-        <v>0.966634035110474</v>
+        <v>0.966634273529053</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G741" t="n">
-        <v>0.969678580760956</v>
+        <v>0.96967875957489</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G742" t="n">
-        <v>1.00925731658936</v>
+        <v>1.00925743579865</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G743" t="n">
-        <v>1.02904677391052</v>
+        <v>1.02904689311981</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G744" t="n">
-        <v>1.02904677391052</v>
+        <v>1.02904689311981</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G747" t="n">
-        <v>1.01230192184448</v>
+        <v>1.01230204105377</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>1.30599999427795</v>
       </c>
       <c r="G748" t="n">
-        <v>0.994034826755524</v>
+        <v>0.994034886360168</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G749" t="n">
-        <v>0.969678580760956</v>
+        <v>0.96967875957489</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G750" t="n">
-        <v>0.954455971717834</v>
+        <v>0.954456031322479</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G751" t="n">
-        <v>0.955978274345398</v>
+        <v>0.955978333950043</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G752" t="n">
-        <v>0.959022998809814</v>
+        <v>0.95902293920517</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G753" t="n">
-        <v>0.934666931629181</v>
+        <v>0.934666752815247</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>1.25</v>
       </c>
       <c r="G754" t="n">
-        <v>0.951411545276642</v>
+        <v>0.951411604881287</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G755" t="n">
-        <v>0.948367178440094</v>
+        <v>0.948367059230804</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G756" t="n">
-        <v>0.948367178440094</v>
+        <v>0.948367059230804</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G757" t="n">
-        <v>0.965111911296844</v>
+        <v>0.965111792087555</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G758" t="n">
-        <v>0.955978274345398</v>
+        <v>0.955978333950043</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G759" t="n">
-        <v>0.966634035110474</v>
+        <v>0.966634273529053</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G760" t="n">
-        <v>0.969678580760956</v>
+        <v>0.96967875957489</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>1.27799999713898</v>
       </c>
       <c r="G761" t="n">
-        <v>0.972723305225372</v>
+        <v>0.972723126411438</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G762" t="n">
-        <v>0.962067484855652</v>
+        <v>0.962067425251007</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G763" t="n">
-        <v>0.952933788299561</v>
+        <v>0.952933728694916</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G764" t="n">
-        <v>0.966634035110474</v>
+        <v>0.966634273529053</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G765" t="n">
-        <v>0.997079193592072</v>
+        <v>0.997079312801361</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G766" t="n">
-        <v>0.99251264333725</v>
+        <v>0.992512464523315</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G767" t="n">
-        <v>1.01686859130859</v>
+        <v>1.01686871051788</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G768" t="n">
-        <v>1.01077938079834</v>
+        <v>1.01077961921692</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G769" t="n">
-        <v>1.03361356258392</v>
+        <v>1.03361344337463</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G771" t="n">
-        <v>1.04426920413971</v>
+        <v>1.044269323349</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G772" t="n">
-        <v>1.03665816783905</v>
+        <v>1.03665804862976</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>1.37800002098083</v>
       </c>
       <c r="G774" t="n">
-        <v>1.04883599281311</v>
+        <v>1.0488361120224</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G776" t="n">
-        <v>1.04426920413971</v>
+        <v>1.044269323349</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G782" t="n">
-        <v>1.03665816783905</v>
+        <v>1.03665804862976</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G783" t="n">
-        <v>1.03361356258392</v>
+        <v>1.03361344337463</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G785" t="n">
-        <v>0.997079193592072</v>
+        <v>0.997079312801361</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G786" t="n">
-        <v>0.978812158107758</v>
+        <v>0.978812396526337</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>1.27799999713898</v>
       </c>
       <c r="G787" t="n">
-        <v>0.972723305225372</v>
+        <v>0.972723126411438</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>1.28199994564056</v>
       </c>
       <c r="G788" t="n">
-        <v>0.97576767206192</v>
+        <v>0.975767612457275</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G789" t="n">
-        <v>0.99251264333725</v>
+        <v>0.992512464523315</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>1.28799998760223</v>
       </c>
       <c r="G790" t="n">
-        <v>0.980334460735321</v>
+        <v>0.980334401130676</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G791" t="n">
-        <v>0.963589668273926</v>
+        <v>0.963589549064636</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G792" t="n">
-        <v>0.974245369434357</v>
+        <v>0.974245429039001</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G793" t="n">
-        <v>0.983379065990448</v>
+        <v>0.983378946781158</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>1.31200003623962</v>
       </c>
       <c r="G794" t="n">
-        <v>0.998601615428925</v>
+        <v>0.998601675033569</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>1.30599999427795</v>
       </c>
       <c r="G795" t="n">
-        <v>0.994034826755524</v>
+        <v>0.994034886360168</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>1.30599999427795</v>
       </c>
       <c r="G796" t="n">
-        <v>0.994034826755524</v>
+        <v>0.994034886360168</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G799" t="n">
-        <v>0.981856644153595</v>
+        <v>0.98185670375824</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>1.31200003623962</v>
       </c>
       <c r="G802" t="n">
-        <v>0.998601615428925</v>
+        <v>0.998601675033569</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G803" t="n">
-        <v>1.01230192184448</v>
+        <v>1.01230204105377</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G804" t="n">
-        <v>1.01839089393616</v>
+        <v>1.01839101314545</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G805" t="n">
-        <v>0.997079193592072</v>
+        <v>0.997079312801361</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G807" t="n">
-        <v>1.01230192184448</v>
+        <v>1.01230204105377</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>1.33399999141693</v>
       </c>
       <c r="G808" t="n">
-        <v>1.01534628868103</v>
+        <v>1.01534640789032</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G809" t="n">
-        <v>1.00925731658936</v>
+        <v>1.00925743579865</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G810" t="n">
-        <v>0.99251264333725</v>
+        <v>0.992512464523315</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G811" t="n">
-        <v>0.986423432826996</v>
+        <v>0.986423492431641</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G813" t="n">
-        <v>0.997079193592072</v>
+        <v>0.997079312801361</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G814" t="n">
-        <v>0.99251264333725</v>
+        <v>0.992512464523315</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G815" t="n">
-        <v>1.01230192184448</v>
+        <v>1.01230204105377</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>1.30599999427795</v>
       </c>
       <c r="G816" t="n">
-        <v>0.994034826755524</v>
+        <v>0.994034886360168</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>1.30599999427795</v>
       </c>
       <c r="G817" t="n">
-        <v>0.994034826755524</v>
+        <v>0.994034886360168</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>1.31599998474121</v>
       </c>
       <c r="G819" t="n">
-        <v>1.00164604187012</v>
+        <v>1.00164616107941</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>1.33399999141693</v>
       </c>
       <c r="G820" t="n">
-        <v>1.01534628868103</v>
+        <v>1.01534640789032</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G826" t="n">
-        <v>0.986423432826996</v>
+        <v>0.986423492431641</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>1.30599999427795</v>
       </c>
       <c r="G827" t="n">
-        <v>0.994034826755524</v>
+        <v>0.994034886360168</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G828" t="n">
-        <v>0.99251264333725</v>
+        <v>0.992512464523315</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>1.31599998474121</v>
       </c>
       <c r="G829" t="n">
-        <v>1.00164604187012</v>
+        <v>1.00164616107941</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>1.37800002098083</v>
       </c>
       <c r="G836" t="n">
-        <v>1.04883599281311</v>
+        <v>1.0488361120224</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>1.40600001811981</v>
       </c>
       <c r="G837" t="n">
-        <v>1.07014775276184</v>
+        <v>1.07014763355255</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G838" t="n">
-        <v>1.08080363273621</v>
+        <v>1.08080351352692</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G839" t="n">
-        <v>1.05949187278748</v>
+        <v>1.05949199199677</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G840" t="n">
-        <v>1.05796957015991</v>
+        <v>1.0579696893692</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G841" t="n">
-        <v>1.07166981697083</v>
+        <v>1.07167017459869</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G842" t="n">
-        <v>1.05492520332336</v>
+        <v>1.05492508411407</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>1.37800002098083</v>
       </c>
       <c r="G843" t="n">
-        <v>1.04883599281311</v>
+        <v>1.0488361120224</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G845" t="n">
-        <v>1.05796957015991</v>
+        <v>1.0579696893692</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G846" t="n">
-        <v>1.03513586521149</v>
+        <v>1.0351357460022</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>1.35599994659424</v>
       </c>
       <c r="G847" t="n">
-        <v>1.03209125995636</v>
+        <v>1.03209114074707</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G848" t="n">
-        <v>1.04122471809387</v>
+        <v>1.04122483730316</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G849" t="n">
-        <v>1.04122471809387</v>
+        <v>1.04122483730316</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G850" t="n">
-        <v>1.00925731658936</v>
+        <v>1.00925743579865</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G852" t="n">
-        <v>0.974245369434357</v>
+        <v>0.974245429039001</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>1.28199994564056</v>
       </c>
       <c r="G853" t="n">
-        <v>0.97576767206192</v>
+        <v>0.975767612457275</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G854" t="n">
-        <v>0.983379065990448</v>
+        <v>0.983378946781158</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G855" t="n">
-        <v>0.983379065990448</v>
+        <v>0.983378946781158</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G856" t="n">
-        <v>0.91335517168045</v>
+        <v>0.913355052471161</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G857" t="n">
-        <v>0.908788204193115</v>
+        <v>0.908788323402405</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>1.10199999809265</v>
       </c>
       <c r="G859" t="n">
-        <v>0.838764429092407</v>
+        <v>0.838764369487762</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G861" t="n">
-        <v>0.860076069831848</v>
+        <v>0.860076010227203</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>1.13199996948242</v>
       </c>
       <c r="G862" t="n">
-        <v>0.861598312854767</v>
+        <v>0.861598253250122</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>1.14400005340576</v>
       </c>
       <c r="G864" t="n">
-        <v>0.870731830596924</v>
+        <v>0.870731949806213</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G865" t="n">
-        <v>0.864642798900604</v>
+        <v>0.864642918109894</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>1.12399995326996</v>
       </c>
       <c r="G866" t="n">
-        <v>0.855509221553802</v>
+        <v>0.855509161949158</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G869" t="n">
-        <v>0.825147271156311</v>
+        <v>0.825147211551666</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>1.04799997806549</v>
       </c>
       <c r="G870" t="n">
-        <v>0.831494510173798</v>
+        <v>0.831494569778442</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>1.06400001049042</v>
       </c>
       <c r="G871" t="n">
-        <v>0.84418922662735</v>
+        <v>0.84418910741806</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>1.09200000762939</v>
       </c>
       <c r="G872" t="n">
-        <v>0.866404592990875</v>
+        <v>0.866404712200165</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>1.07599997520447</v>
       </c>
       <c r="G873" t="n">
-        <v>0.853710055351257</v>
+        <v>0.853710174560547</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G875" t="n">
-        <v>0.841015517711639</v>
+        <v>0.841015458106995</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>0.99099999666214</v>
       </c>
       <c r="G880" t="n">
-        <v>0.786270201206207</v>
+        <v>0.786270141601562</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G881" t="n">
-        <v>0.779129445552826</v>
+        <v>0.779129505157471</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G882" t="n">
-        <v>0.788650393486023</v>
+        <v>0.788650453090668</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G884" t="n">
-        <v>0.804518699645996</v>
+        <v>0.804518640041351</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G885" t="n">
-        <v>0.796584486961365</v>
+        <v>0.79658442735672</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G887" t="n">
-        <v>0.77754271030426</v>
+        <v>0.777542650699615</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G888" t="n">
-        <v>0.779129445552826</v>
+        <v>0.779129505157471</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G890" t="n">
-        <v>0.783889889717102</v>
+        <v>0.783889949321747</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G892" t="n">
-        <v>0.801344990730286</v>
+        <v>0.80134505033493</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G897" t="n">
-        <v>0.771195411682129</v>
+        <v>0.771195352077484</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G898" t="n">
-        <v>0.764847993850708</v>
+        <v>0.764848053455353</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>0.967000007629395</v>
       </c>
       <c r="G899" t="n">
-        <v>0.767228305339813</v>
+        <v>0.767228245735168</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>0.971000015735626</v>
       </c>
       <c r="G900" t="n">
-        <v>0.770401895046234</v>
+        <v>0.770402014255524</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G904" t="n">
-        <v>0.761674463748932</v>
+        <v>0.761674404144287</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G906" t="n">
-        <v>0.763261198997498</v>
+        <v>0.763261258602142</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G912" t="n">
-        <v>0.77754271030426</v>
+        <v>0.777542650699615</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G913" t="n">
-        <v>0.761674463748932</v>
+        <v>0.761674404144287</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>0.944999992847443</v>
       </c>
       <c r="G914" t="n">
-        <v>0.749773263931274</v>
+        <v>0.749773323535919</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G915" t="n">
-        <v>0.737872123718262</v>
+        <v>0.737872064113617</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>0.883000016212463</v>
       </c>
       <c r="G917" t="n">
-        <v>0.700581848621368</v>
+        <v>0.700581789016724</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G918" t="n">
-        <v>0.664878308773041</v>
+        <v>0.664878249168396</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G919" t="n">
-        <v>0.669638752937317</v>
+        <v>0.669638693332672</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G921" t="n">
-        <v>0.656944155693054</v>
+        <v>0.656944215297699</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G922" t="n">
-        <v>0.650596916675568</v>
+        <v>0.650596857070923</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G923" t="n">
-        <v>0.644249618053436</v>
+        <v>0.644249558448792</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G924" t="n">
-        <v>0.647423148155212</v>
+        <v>0.647423267364502</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>0.814999997615814</v>
       </c>
       <c r="G925" t="n">
-        <v>0.646629810333252</v>
+        <v>0.646629869937897</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G926" t="n">
-        <v>0.656944155693054</v>
+        <v>0.656944215297699</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>0.861000001430511</v>
       </c>
       <c r="G928" t="n">
-        <v>0.68312680721283</v>
+        <v>0.683126747608185</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G929" t="n">
-        <v>0.679159700870514</v>
+        <v>0.679159760475159</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G930" t="n">
-        <v>0.672812402248383</v>
+        <v>0.672812461853027</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>0.853999972343445</v>
       </c>
       <c r="G931" t="n">
-        <v>0.677572846412659</v>
+        <v>0.677572786808014</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>0.830999970436096</v>
       </c>
       <c r="G932" t="n">
-        <v>0.659324407577515</v>
+        <v>0.65932434797287</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G933" t="n">
-        <v>0.656944155693054</v>
+        <v>0.656944215297699</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>0.827000021934509</v>
       </c>
       <c r="G934" t="n">
-        <v>0.656150877475739</v>
+        <v>0.656150817871094</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G935" t="n">
-        <v>0.666465163230896</v>
+        <v>0.666465103626251</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G936" t="n">
-        <v>0.66329151391983</v>
+        <v>0.663291454315186</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>0.830999970436096</v>
       </c>
       <c r="G937" t="n">
-        <v>0.659324407577515</v>
+        <v>0.65932434797287</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G941" t="n">
-        <v>0.726764380931854</v>
+        <v>0.726764321327209</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G943" t="n">
-        <v>0.748979806900024</v>
+        <v>0.748979866504669</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G944" t="n">
-        <v>0.737872123718262</v>
+        <v>0.737872064113617</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>0.926999986171722</v>
       </c>
       <c r="G945" t="n">
-        <v>0.735491812229156</v>
+        <v>0.735491931438446</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G946" t="n">
-        <v>0.726764380931854</v>
+        <v>0.726764321327209</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G950" t="n">
-        <v>0.702962040901184</v>
+        <v>0.702961981296539</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>0.879000008106232</v>
       </c>
       <c r="G954" t="n">
-        <v>0.697408080101013</v>
+        <v>0.697408139705658</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G956" t="n">
-        <v>0.666465163230896</v>
+        <v>0.666465103626251</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G957" t="n">
-        <v>0.66329151391983</v>
+        <v>0.663291454315186</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>0.848999977111816</v>
       </c>
       <c r="G958" t="n">
-        <v>0.673605859279633</v>
+        <v>0.673605799674988</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>0.837000012397766</v>
       </c>
       <c r="G959" t="n">
-        <v>0.664084911346436</v>
+        <v>0.664084851741791</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G960" t="n">
-        <v>0.666465163230896</v>
+        <v>0.666465103626251</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G964" t="n">
-        <v>0.675986111164093</v>
+        <v>0.675985991954803</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G966" t="n">
-        <v>0.671225607395172</v>
+        <v>0.671225666999817</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>0.848999977111816</v>
       </c>
       <c r="G967" t="n">
-        <v>0.673605859279633</v>
+        <v>0.673605799674988</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G968" t="n">
-        <v>0.672812402248383</v>
+        <v>0.672812461853027</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G970" t="n">
-        <v>0.672018945217133</v>
+        <v>0.672019004821777</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G974" t="n">
-        <v>0.669638752937317</v>
+        <v>0.669638693332672</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>0.842999994754791</v>
       </c>
       <c r="G975" t="n">
-        <v>0.668845355510712</v>
+        <v>0.668845415115356</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G976" t="n">
-        <v>0.672812402248383</v>
+        <v>0.672812461853027</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G978" t="n">
-        <v>0.726764380931854</v>
+        <v>0.726764321327209</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G979" t="n">
-        <v>0.741045773029327</v>
+        <v>0.741045713424683</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G982" t="n">
-        <v>0.720417022705078</v>
+        <v>0.720417082309723</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G983" t="n">
-        <v>0.745806276798248</v>
+        <v>0.745806217193604</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>0.953000009059906</v>
       </c>
       <c r="G985" t="n">
-        <v>0.756120562553406</v>
+        <v>0.756120502948761</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G987" t="n">
-        <v>0.688680529594421</v>
+        <v>0.688680589199066</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>0.861000001430511</v>
       </c>
       <c r="G988" t="n">
-        <v>0.68312680721283</v>
+        <v>0.683126747608185</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>0.851000010967255</v>
       </c>
       <c r="G990" t="n">
-        <v>0.675192594528198</v>
+        <v>0.675192654132843</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>0.848999977111816</v>
       </c>
       <c r="G991" t="n">
-        <v>0.673605859279633</v>
+        <v>0.673605799674988</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G994" t="n">
-        <v>0.690267384052277</v>
+        <v>0.690267443656921</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>0.90200001001358</v>
       </c>
       <c r="G996" t="n">
-        <v>0.715656638145447</v>
+        <v>0.715656578540802</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G998" t="n">
-        <v>0.733111619949341</v>
+        <v>0.733111679553986</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G999" t="n">
-        <v>0.733111619949341</v>
+        <v>0.733111679553986</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G1000" t="n">
-        <v>0.737872123718262</v>
+        <v>0.737872064113617</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>0.930999994277954</v>
       </c>
       <c r="G1001" t="n">
-        <v>0.738665461540222</v>
+        <v>0.738665521144867</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G1003" t="n">
-        <v>0.737872123718262</v>
+        <v>0.737872064113617</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G1005" t="n">
-        <v>0.73152482509613</v>
+        <v>0.731524884700775</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G1006" t="n">
-        <v>0.734698534011841</v>
+        <v>0.734698474407196</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G1007" t="n">
-        <v>0.739458918571472</v>
+        <v>0.739458858966827</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G1009" t="n">
-        <v>0.736285269260406</v>
+        <v>0.736285209655762</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G1010" t="n">
-        <v>0.737872123718262</v>
+        <v>0.737872064113617</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G1013" t="n">
-        <v>0.733905017375946</v>
+        <v>0.733904957771301</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G1014" t="n">
-        <v>0.73152482509613</v>
+        <v>0.731524884700775</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G1018" t="n">
-        <v>0.718036770820618</v>
+        <v>0.718036830425262</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G1019" t="n">
-        <v>0.733905017375946</v>
+        <v>0.733904957771301</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G1021" t="n">
-        <v>0.736285269260406</v>
+        <v>0.736285209655762</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G1022" t="n">
-        <v>0.737872123718262</v>
+        <v>0.737872064113617</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>0.921000003814697</v>
       </c>
       <c r="G1023" t="n">
-        <v>0.73073148727417</v>
+        <v>0.730731427669525</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G1024" t="n">
-        <v>0.733905017375946</v>
+        <v>0.733904957771301</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G1025" t="n">
-        <v>0.733111619949341</v>
+        <v>0.733111679553986</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>0.916999995708466</v>
       </c>
       <c r="G1029" t="n">
-        <v>0.727557837963104</v>
+        <v>0.727557778358459</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G1031" t="n">
-        <v>0.737872123718262</v>
+        <v>0.737872064113617</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G1032" t="n">
-        <v>0.73152482509613</v>
+        <v>0.731524884700775</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1033" t="n">
-        <v>0.710896193981171</v>
+        <v>0.710896134376526</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G1036" t="n">
-        <v>0.695027947425842</v>
+        <v>0.695027887821198</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1037" t="n">
-        <v>0.656944155693054</v>
+        <v>0.656944215297699</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1038" t="n">
-        <v>0.669638752937317</v>
+        <v>0.669638693332672</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G1039" t="n">
-        <v>0.685506999492645</v>
+        <v>0.68550705909729</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>0.883000016212463</v>
       </c>
       <c r="G1040" t="n">
-        <v>0.700581848621368</v>
+        <v>0.700581789016724</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G1042" t="n">
-        <v>0.695027947425842</v>
+        <v>0.695027887821198</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G1045" t="n">
-        <v>0.702962040901184</v>
+        <v>0.702961981296539</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>0.887000024318695</v>
       </c>
       <c r="G1047" t="n">
-        <v>0.703755438327789</v>
+        <v>0.703755497932434</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G1048" t="n">
-        <v>0.695027947425842</v>
+        <v>0.695027887821198</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>0.873000025749207</v>
       </c>
       <c r="G1049" t="n">
-        <v>0.692647635936737</v>
+        <v>0.692647695541382</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1050" t="n">
-        <v>0.675986111164093</v>
+        <v>0.675985991954803</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1052" t="n">
-        <v>0.666465163230896</v>
+        <v>0.666465103626251</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1057" t="n">
-        <v>0.626794576644897</v>
+        <v>0.626794695854187</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>0.823000013828278</v>
       </c>
       <c r="G1058" t="n">
-        <v>0.652977168560028</v>
+        <v>0.652977108955383</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1060" t="n">
-        <v>0.671225607395172</v>
+        <v>0.671225666999817</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>0.816999971866608</v>
       </c>
       <c r="G1062" t="n">
-        <v>0.648216724395752</v>
+        <v>0.648216605186462</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.563321709632874</v>
+        <v>0.563321650028229</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.533172070980072</v>
+        <v>0.533172130584717</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.49191477894783</v>
+        <v>0.491914749145508</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.507782995700836</v>
+        <v>0.507783055305481</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1068" t="n">
-        <v>0.490327835083008</v>
+        <v>0.490327805280685</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>0.633000016212463</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.50222909450531</v>
+        <v>0.502229154109955</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>0.620999991893768</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.492708206176758</v>
+        <v>0.492708146572113</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.507782995700836</v>
+        <v>0.507783055305481</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.523651242256165</v>
+        <v>0.52365118265152</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1074" t="n">
-        <v>0.550627171993256</v>
+        <v>0.550627112388611</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1075" t="n">
-        <v>0.556974351406097</v>
+        <v>0.556974411010742</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.571255803108215</v>
+        <v>0.57125586271286</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1078" t="n">
-        <v>0.537932515144348</v>
+        <v>0.537932574748993</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.537932515144348</v>
+        <v>0.537932574748993</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>0.616999983787537</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.489534467458725</v>
+        <v>0.489534497261047</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1083" t="n">
-        <v>0.496675193309784</v>
+        <v>0.496675163507462</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1084" t="n">
-        <v>0.483980655670166</v>
+        <v>0.483980596065521</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>0.601000010967255</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.476839959621429</v>
+        <v>0.476839900016785</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>0.598999977111816</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.475253045558929</v>
+        <v>0.475253134965897</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1087" t="n">
-        <v>0.49191477894783</v>
+        <v>0.491914749145508</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>0.601000010967255</v>
       </c>
       <c r="G1089" t="n">
-        <v>0.476839959621429</v>
+        <v>0.476839900016785</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>0.615000009536743</v>
       </c>
       <c r="G1090" t="n">
-        <v>0.487947762012482</v>
+        <v>0.487947672605515</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>0.601000010967255</v>
       </c>
       <c r="G1091" t="n">
-        <v>0.476839959621429</v>
+        <v>0.476839900016785</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1092" t="n">
-        <v>0.476046502590179</v>
+        <v>0.476046532392502</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>0.592999994754791</v>
       </c>
       <c r="G1093" t="n">
-        <v>0.470492631196976</v>
+        <v>0.470492601394653</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G1094" t="n">
-        <v>0.464145362377167</v>
+        <v>0.464145332574844</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G1095" t="n">
-        <v>0.471286058425903</v>
+        <v>0.471286028623581</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1096" t="n">
-        <v>0.476046502590179</v>
+        <v>0.476046532392502</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>0.605000019073486</v>
       </c>
       <c r="G1097" t="n">
-        <v>0.480013579130173</v>
+        <v>0.480013608932495</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1098" t="n">
-        <v>0.485567450523376</v>
+        <v>0.485567480325699</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1099" t="n">
-        <v>0.476046502590179</v>
+        <v>0.476046532392502</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1101" t="n">
-        <v>0.476046502590179</v>
+        <v>0.476046532392502</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G1102" t="n">
-        <v>0.471286058425903</v>
+        <v>0.471286028623581</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G1104" t="n">
-        <v>0.471286058425903</v>
+        <v>0.471286028623581</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1105" t="n">
-        <v>0.476046502590179</v>
+        <v>0.476046532392502</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1106" t="n">
-        <v>0.4808070063591</v>
+        <v>0.480806976556778</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1107" t="n">
-        <v>0.476046502590179</v>
+        <v>0.476046532392502</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G1109" t="n">
-        <v>0.450657337903976</v>
+        <v>0.450657397508621</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.447483718395233</v>
+        <v>0.447483748197556</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.455417811870575</v>
+        <v>0.455417841672897</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1117" t="n">
-        <v>0.476046502590179</v>
+        <v>0.476046532392502</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>0.609000027179718</v>
       </c>
       <c r="G1118" t="n">
-        <v>0.483187198638916</v>
+        <v>0.483187228441238</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1119" t="n">
-        <v>0.476046502590179</v>
+        <v>0.476046532392502</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1120" t="n">
-        <v>0.476046502590179</v>
+        <v>0.476046532392502</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1122" t="n">
-        <v>0.4792200922966</v>
+        <v>0.479220151901245</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1123" t="n">
-        <v>0.476046502590179</v>
+        <v>0.476046532392502</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1124" t="n">
-        <v>0.49191477894783</v>
+        <v>0.491914749145508</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1127" t="n">
-        <v>0.566495358943939</v>
+        <v>0.566495418548584</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>0.654999971389771</v>
       </c>
       <c r="G1128" t="n">
-        <v>0.519684135913849</v>
+        <v>0.519684076309204</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1129" t="n">
-        <v>0.558561265468597</v>
+        <v>0.558561325073242</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>0.75900000333786</v>
       </c>
       <c r="G1131" t="n">
-        <v>0.602198839187622</v>
+        <v>0.602198898792267</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1134" t="n">
-        <v>0.56966906785965</v>
+        <v>0.569669008255005</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1137" t="n">
-        <v>0.566495358943939</v>
+        <v>0.566495418548584</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1140" t="n">
-        <v>0.545866668224335</v>
+        <v>0.545866727828979</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1142" t="n">
-        <v>0.533172070980072</v>
+        <v>0.533172130584717</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1143" t="n">
-        <v>0.545866668224335</v>
+        <v>0.545866727828979</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G1147" t="n">
-        <v>0.572842597961426</v>
+        <v>0.572842657566071</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>0.726999998092651</v>
       </c>
       <c r="G1150" t="n">
-        <v>0.576809644699097</v>
+        <v>0.576809704303741</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1151" t="n">
-        <v>0.610926330089569</v>
+        <v>0.610926389694214</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1152" t="n">
-        <v>0.626794576644897</v>
+        <v>0.626794695854187</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1153" t="n">
-        <v>0.614099979400635</v>
+        <v>0.61410003900528</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>0.757000029087067</v>
       </c>
       <c r="G1154" t="n">
-        <v>0.600612103939056</v>
+        <v>0.600612044334412</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1156" t="n">
-        <v>0.609339535236359</v>
+        <v>0.609339475631714</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1158" t="n">
-        <v>0.626794576644897</v>
+        <v>0.626794695854187</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>0.785000026226044</v>
       </c>
       <c r="G1159" t="n">
-        <v>0.622827529907227</v>
+        <v>0.622827589511871</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>0.788999974727631</v>
       </c>
       <c r="G1160" t="n">
-        <v>0.626001179218292</v>
+        <v>0.626001119613647</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>0.802999973297119</v>
       </c>
       <c r="G1162" t="n">
-        <v>0.6371089220047</v>
+        <v>0.63710880279541</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.617273688316345</v>
+        <v>0.6172736287117</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.620447337627411</v>
+        <v>0.620447278022766</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1165" t="n">
-        <v>0.653770565986633</v>
+        <v>0.653770506381989</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.690267384052277</v>
+        <v>0.690267443656921</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1170" t="n">
-        <v>0.696614801883698</v>
+        <v>0.696614742279053</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>0.876999974250793</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.695821344852448</v>
+        <v>0.695821285247803</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>0.883000016212463</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.700581848621368</v>
+        <v>0.700581789016724</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.695027947425842</v>
+        <v>0.695027887821198</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>0.882000029087067</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.699788391590118</v>
+        <v>0.699788451194763</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>0.887000024318695</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.703755438327789</v>
+        <v>0.703755497932434</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.693441152572632</v>
+        <v>0.693441092967987</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.685506999492645</v>
+        <v>0.68550705909729</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G1180" t="n">
-        <v>0.672018945217133</v>
+        <v>0.672019004821777</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.674399197101593</v>
+        <v>0.674399316310883</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>0.842999994754791</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.668845355510712</v>
+        <v>0.668845415115356</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.650596916675568</v>
+        <v>0.650596857070923</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>0.824999988079071</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.654563903808594</v>
+        <v>0.654564023017883</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.666465163230896</v>
+        <v>0.666465103626251</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1186" t="n">
-        <v>0.666465163230896</v>
+        <v>0.666465103626251</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.660117864608765</v>
+        <v>0.660117924213409</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>0.806999981403351</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.64028263092041</v>
+        <v>0.640282571315765</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.642662763595581</v>
+        <v>0.642662823200226</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>0.824999988079071</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.654563903808594</v>
+        <v>0.654564023017883</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.655357420444489</v>
+        <v>0.655357360839844</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.664878308773041</v>
+        <v>0.664878249168396</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1193" t="n">
-        <v>0.666465163230896</v>
+        <v>0.666465103626251</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>0.842999994754791</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.668845355510712</v>
+        <v>0.668845415115356</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.669638752937317</v>
+        <v>0.669638693332672</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.664878308773041</v>
+        <v>0.664878249168396</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.680746555328369</v>
+        <v>0.680746495723724</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>0.848999977111816</v>
       </c>
       <c r="G1199" t="n">
-        <v>0.673605859279633</v>
+        <v>0.673605799674988</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.664878308773041</v>
+        <v>0.664878249168396</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>0.851000010967255</v>
       </c>
       <c r="G1203" t="n">
-        <v>0.675192594528198</v>
+        <v>0.675192654132843</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.666465163230896</v>
+        <v>0.666465103626251</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G1207" t="n">
-        <v>0.66170471906662</v>
+        <v>0.661704659461975</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.690267384052277</v>
+        <v>0.690267443656921</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>0.85699999332428</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.679953157901764</v>
+        <v>0.679953098297119</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.672018945217133</v>
+        <v>0.672019004821777</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>0.879000008106232</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.697408080101013</v>
+        <v>0.697408139705658</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>0.888999998569489</v>
       </c>
       <c r="G1214" t="n">
-        <v>0.705342233181</v>
+        <v>0.705342292785645</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G1215" t="n">
-        <v>0.736285269260406</v>
+        <v>0.736285209655762</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G1219" t="n">
-        <v>0.693441152572632</v>
+        <v>0.693441092967987</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1221" t="n">
-        <v>0.696614801883698</v>
+        <v>0.696614742279053</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.710896193981171</v>
+        <v>0.710896134376526</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.710896193981171</v>
+        <v>0.710896134376526</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>0.897000014781952</v>
       </c>
       <c r="G1224" t="n">
-        <v>0.711689591407776</v>
+        <v>0.711689472198486</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>0.890999972820282</v>
       </c>
       <c r="G1225" t="n">
-        <v>0.70692902803421</v>
+        <v>0.706929087638855</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>0.866999983787537</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.687887251377106</v>
+        <v>0.687887191772461</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>0.814999997615814</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.646629810333252</v>
+        <v>0.646629869937897</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>0.882000029087067</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.699788391590118</v>
+        <v>0.699788451194763</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>0.888999998569489</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.705342233181</v>
+        <v>0.705342292785645</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.75056666135788</v>
+        <v>0.750566601753235</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G1240" t="n">
-        <v>0.769608616828918</v>
+        <v>0.769608557224274</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G1243" t="n">
-        <v>0.769608616828918</v>
+        <v>0.769608557224274</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G1246" t="n">
-        <v>0.771195411682129</v>
+        <v>0.771195352077484</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G1247" t="n">
-        <v>0.77754271030426</v>
+        <v>0.777542650699615</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1250" t="n">
-        <v>0.761674463748932</v>
+        <v>0.761674404144287</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>0.949000000953674</v>
       </c>
       <c r="G1251" t="n">
-        <v>0.75294691324234</v>
+        <v>0.752946853637695</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>1.07799994945526</v>
       </c>
       <c r="G1257" t="n">
-        <v>0.855296909809113</v>
+        <v>0.855296850204468</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1258" t="n">
-        <v>0.864817798137665</v>
+        <v>0.864817917346954</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>1.09200000762939</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.866404592990875</v>
+        <v>0.866404712200165</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>1.12600004673004</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.893380641937256</v>
+        <v>0.893380701541901</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>1.1139999628067</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.883859753608704</v>
+        <v>0.883859574794769</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1262" t="n">
-        <v>0.864817798137665</v>
+        <v>0.864817917346954</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>1.10599994659424</v>
       </c>
       <c r="G1263" t="n">
-        <v>0.877512395381927</v>
+        <v>0.877512335777283</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>1.06400001049042</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.84418922662735</v>
+        <v>0.84418910741806</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>1.08800005912781</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.863231062889099</v>
+        <v>0.863231122493744</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>1.09599995613098</v>
       </c>
       <c r="G1267" t="n">
-        <v>0.869578301906586</v>
+        <v>0.869578242301941</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>1.08800005912781</v>
       </c>
       <c r="G1268" t="n">
-        <v>0.863231062889099</v>
+        <v>0.863231122493744</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.860057353973389</v>
+        <v>0.860057413578033</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1272" t="n">
-        <v>0.864817798137665</v>
+        <v>0.864817917346954</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1273" t="n">
-        <v>0.88862019777298</v>
+        <v>0.88862007856369</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G1274" t="n">
-        <v>0.923530280590057</v>
+        <v>0.923530399799347</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1275" t="n">
-        <v>0.936224818229675</v>
+        <v>0.936224758625031</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>1.15799999237061</v>
       </c>
       <c r="G1276" t="n">
-        <v>0.918769896030426</v>
+        <v>0.918769776821136</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G1278" t="n">
-        <v>0.923530280590057</v>
+        <v>0.923530399799347</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1279" t="n">
-        <v>0.912422478199005</v>
+        <v>0.91242253780365</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1281" t="n">
-        <v>0.912422478199005</v>
+        <v>0.91242253780365</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G1282" t="n">
-        <v>0.875925540924072</v>
+        <v>0.875925600528717</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>1.10599994659424</v>
       </c>
       <c r="G1284" t="n">
-        <v>0.877512395381927</v>
+        <v>0.877512335777283</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1285" t="n">
-        <v>0.896554291248322</v>
+        <v>0.896554231643677</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1286" t="n">
-        <v>0.896554291248322</v>
+        <v>0.896554231643677</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1287" t="n">
-        <v>0.896554291248322</v>
+        <v>0.896554231643677</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1288" t="n">
-        <v>0.896554291248322</v>
+        <v>0.896554231643677</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>1.15799999237061</v>
       </c>
       <c r="G1289" t="n">
-        <v>0.918769896030426</v>
+        <v>0.918769776821136</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1291" t="n">
-        <v>0.95685350894928</v>
+        <v>0.956853449344635</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.928290724754333</v>
+        <v>0.928290665149689</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1293" t="n">
-        <v>0.961614012718201</v>
+        <v>0.961613953113556</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>1.21800005435944</v>
       </c>
       <c r="G1294" t="n">
-        <v>0.966374397277832</v>
+        <v>0.966374456882477</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1295" t="n">
-        <v>0.967961311340332</v>
+        <v>0.967961192131042</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>1.21399998664856</v>
       </c>
       <c r="G1296" t="n">
-        <v>0.963200688362122</v>
+        <v>0.963200867176056</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1297" t="n">
-        <v>0.944158971309662</v>
+        <v>0.944158852100372</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1298" t="n">
-        <v>0.967961311340332</v>
+        <v>0.967961192131042</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1299" t="n">
-        <v>0.944158971309662</v>
+        <v>0.944158852100372</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1301" t="n">
-        <v>0.960027158260345</v>
+        <v>0.96002721786499</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G1302" t="n">
-        <v>0.942572116851807</v>
+        <v>0.942572057247162</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G1303" t="n">
-        <v>0.923530280590057</v>
+        <v>0.923530399799347</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1305" t="n">
-        <v>0.95685350894928</v>
+        <v>0.956853449344635</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G1307" t="n">
-        <v>0.950506091117859</v>
+        <v>0.950506269931793</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G1308" t="n">
-        <v>0.971134901046753</v>
+        <v>0.971134960651398</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>1.21399998664856</v>
       </c>
       <c r="G1309" t="n">
-        <v>0.963200688362122</v>
+        <v>0.963200867176056</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G1311" t="n">
-        <v>0.971134901046753</v>
+        <v>0.971134960651398</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>1.21800005435944</v>
       </c>
       <c r="G1312" t="n">
-        <v>0.966374397277832</v>
+        <v>0.966374456882477</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1313" t="n">
-        <v>0.95685350894928</v>
+        <v>0.956853449344635</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1314" t="n">
-        <v>0.944158971309662</v>
+        <v>0.944158852100372</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>1.23199999332428</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.977482259273529</v>
+        <v>0.977482199668884</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1317" t="n">
-        <v>0.98382955789566</v>
+        <v>0.983829498291016</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G1318" t="n">
-        <v>0.980655670166016</v>
+        <v>0.980655610561371</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>1.27799999713898</v>
       </c>
       <c r="G1322" t="n">
-        <v>1.01397919654846</v>
+        <v>1.01397907733917</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.02826046943665</v>
+        <v>1.02826058864594</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1325" t="n">
-        <v>1.02508699893951</v>
+        <v>1.02508687973022</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.05206274986267</v>
+        <v>1.05206286907196</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>1.33200001716614</v>
       </c>
       <c r="G1327" t="n">
-        <v>1.05682325363159</v>
+        <v>1.0568231344223</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G1328" t="n">
-        <v>1.07269132137299</v>
+        <v>1.07269144058228</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.07269132137299</v>
+        <v>1.07269144058228</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1331" t="n">
-        <v>1.06317055225372</v>
+        <v>1.06317067146301</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1332" t="n">
-        <v>1.0393682718277</v>
+        <v>1.03936815261841</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>1.317999958992</v>
       </c>
       <c r="G1333" t="n">
-        <v>1.04571557044983</v>
+        <v>1.04571545124054</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.05206274986267</v>
+        <v>1.05206286907196</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1335" t="n">
-        <v>1.0615838766098</v>
+        <v>1.06158375740051</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G1338" t="n">
-        <v>1.06951808929443</v>
+        <v>1.06951773166656</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.05206274986267</v>
+        <v>1.05206286907196</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.05206274986267</v>
+        <v>1.05206286907196</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.0393682718277</v>
+        <v>1.03936815261841</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.0615838766098</v>
+        <v>1.06158375740051</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1345" t="n">
-        <v>1.08697283267975</v>
+        <v>1.08697295188904</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.08697283267975</v>
+        <v>1.08697295188904</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G1348" t="n">
-        <v>1.06951808929443</v>
+        <v>1.06951773166656</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1350" t="n">
-        <v>1.09490704536438</v>
+        <v>1.09490692615509</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1351" t="n">
-        <v>1.09490704536438</v>
+        <v>1.09490692615509</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.10284101963043</v>
+        <v>1.10284113883972</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1355" t="n">
-        <v>1.10284101963043</v>
+        <v>1.10284113883972</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.10284101963043</v>
+        <v>1.10284113883972</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.11236190795898</v>
+        <v>1.11236202716827</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.08697283267975</v>
+        <v>1.08697295188904</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1361" t="n">
-        <v>1.1980504989624</v>
+        <v>1.19805037975311</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>1.56400001049042</v>
       </c>
       <c r="G1362" t="n">
-        <v>1.24089467525482</v>
+        <v>1.24089455604553</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1363" t="n">
-        <v>1.25358915328979</v>
+        <v>1.25358939170837</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G1365" t="n">
-        <v>1.2964334487915</v>
+        <v>1.29643321037292</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G1366" t="n">
-        <v>1.32975661754608</v>
+        <v>1.32975649833679</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.34403789043427</v>
+        <v>1.34403800964355</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1369" t="n">
-        <v>1.42496585845947</v>
+        <v>1.42496597766876</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.46146297454834</v>
+        <v>1.46146285533905</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G1372" t="n">
-        <v>1.45511567592621</v>
+        <v>1.45511555671692</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>1.92400002479553</v>
       </c>
       <c r="G1374" t="n">
-        <v>1.526522397995</v>
+        <v>1.52652251720428</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.51382791996002</v>
+        <v>1.51382803916931</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.53286993503571</v>
+        <v>1.53286981582642</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>1.92799997329712</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.56636965274811</v>
+        <v>1.5663697719574</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1380" t="n">
-        <v>1.54362165927887</v>
+        <v>1.54362177848816</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G1382" t="n">
-        <v>1.49650061130524</v>
+        <v>1.49650049209595</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.52249825000763</v>
+        <v>1.52249836921692</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.52249825000763</v>
+        <v>1.52249836921692</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1385" t="n">
-        <v>1.49487566947937</v>
+        <v>1.49487578868866</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.49650061130524</v>
+        <v>1.49650049209595</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>1.78799998760223</v>
       </c>
       <c r="G1387" t="n">
-        <v>1.45262920856476</v>
+        <v>1.45262932777405</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.4136323928833</v>
+        <v>1.41363251209259</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.4315060377121</v>
+        <v>1.43150591850281</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>1.74600005149841</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.41850697994232</v>
+        <v>1.41850709915161</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1392" t="n">
-        <v>1.40875804424286</v>
+        <v>1.40875780582428</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G1397" t="n">
-        <v>1.35188746452332</v>
+        <v>1.3518875837326</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1398" t="n">
-        <v>1.36976110935211</v>
+        <v>1.36976099014282</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G1401" t="n">
-        <v>1.39575886726379</v>
+        <v>1.39575910568237</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1402" t="n">
-        <v>1.33238923549652</v>
+        <v>1.33238911628723</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1404" t="n">
-        <v>1.37788546085358</v>
+        <v>1.37788558006287</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G1406" t="n">
-        <v>1.35351240634918</v>
+        <v>1.35351252555847</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1408" t="n">
-        <v>1.3405134677887</v>
+        <v>1.34051358699799</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G1409" t="n">
-        <v>1.25277090072632</v>
+        <v>1.25277078151703</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G1416" t="n">
-        <v>1.42013192176819</v>
+        <v>1.4201318025589</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>1.75</v>
       </c>
       <c r="G1418" t="n">
-        <v>1.42175674438477</v>
+        <v>1.42175662517548</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G1419" t="n">
-        <v>1.4315060377121</v>
+        <v>1.43150591850281</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G1420" t="n">
-        <v>1.4315060377121</v>
+        <v>1.43150591850281</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G1421" t="n">
-        <v>1.51437401771545</v>
+        <v>1.51437389850616</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1424" t="n">
-        <v>1.49487566947937</v>
+        <v>1.49487578868866</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.49000108242035</v>
+        <v>1.49000120162964</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1426" t="n">
-        <v>1.51924860477448</v>
+        <v>1.51924872398376</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G1427" t="n">
-        <v>1.49812543392181</v>
+        <v>1.49812531471252</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1429" t="n">
-        <v>1.44612991809845</v>
+        <v>1.44612967967987</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1430" t="n">
-        <v>1.48350155353546</v>
+        <v>1.48350167274475</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G1437" t="n">
-        <v>1.49000108242035</v>
+        <v>1.49000120162964</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.55824542045593</v>
+        <v>1.55824553966522</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>1.95200002193451</v>
       </c>
       <c r="G1443" t="n">
-        <v>1.58586823940277</v>
+        <v>1.58586812019348</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G1445" t="n">
-        <v>1.61186599731445</v>
+        <v>1.61186587810516</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G1447" t="n">
-        <v>1.61999046802521</v>
+        <v>1.61999022960663</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G1448" t="n">
-        <v>1.56474483013153</v>
+        <v>1.56474494934082</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>1.90199995040894</v>
       </c>
       <c r="G1449" t="n">
-        <v>1.54524660110474</v>
+        <v>1.54524636268616</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>1.83800005912781</v>
       </c>
       <c r="G1451" t="n">
-        <v>1.49325096607208</v>
+        <v>1.49325084686279</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>1.81400001049042</v>
       </c>
       <c r="G1452" t="n">
-        <v>1.47375249862671</v>
+        <v>1.47375237941742</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>1.82200002670288</v>
       </c>
       <c r="G1453" t="n">
-        <v>1.48025190830231</v>
+        <v>1.48025178909302</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G1454" t="n">
-        <v>1.4315060377121</v>
+        <v>1.43150591850281</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1455" t="n">
-        <v>1.45425391197205</v>
+        <v>1.45425415039062</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G1457" t="n">
-        <v>1.52087342739105</v>
+        <v>1.52087354660034</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G1458" t="n">
-        <v>1.48837625980377</v>
+        <v>1.48837637901306</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>1.74600005149841</v>
       </c>
       <c r="G1461" t="n">
-        <v>1.41850697994232</v>
+        <v>1.41850709915161</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G1463" t="n">
-        <v>1.44775450229645</v>
+        <v>1.44775462150574</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1466" t="n">
-        <v>1.42988109588623</v>
+        <v>1.42988121509552</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1467" t="n">
-        <v>1.42988109588623</v>
+        <v>1.42988121509552</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>1.77600002288818</v>
       </c>
       <c r="G1469" t="n">
-        <v>1.44288003444672</v>
+        <v>1.44287991523743</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1470" t="n">
-        <v>1.47862720489502</v>
+        <v>1.47862708568573</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G1471" t="n">
-        <v>1.51437401771545</v>
+        <v>1.51437389850616</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1473" t="n">
-        <v>1.58424341678619</v>
+        <v>1.5842432975769</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>1.96599996089935</v>
       </c>
       <c r="G1474" t="n">
-        <v>1.59724223613739</v>
+        <v>1.5972421169281</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1475" t="n">
-        <v>1.59236752986908</v>
+        <v>1.59236764907837</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1476" t="n">
-        <v>1.59236752986908</v>
+        <v>1.59236764907837</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1477" t="n">
-        <v>1.59236752986908</v>
+        <v>1.59236764907837</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1478" t="n">
-        <v>1.58424341678619</v>
+        <v>1.5842432975769</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G1479" t="n">
-        <v>1.62323999404907</v>
+        <v>1.62324011325836</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1480" t="n">
-        <v>1.70610797405243</v>
+        <v>1.70610809326172</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G1482" t="n">
-        <v>1.68579745292664</v>
+        <v>1.68579733371735</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1483" t="n">
-        <v>1.63298916816711</v>
+        <v>1.6329892873764</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1484" t="n">
-        <v>1.70610797405243</v>
+        <v>1.70610809326172</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1485" t="n">
-        <v>1.64111351966858</v>
+        <v>1.64111363887787</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1486" t="n">
-        <v>1.66548633575439</v>
+        <v>1.66548645496368</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1487" t="n">
-        <v>1.64111351966858</v>
+        <v>1.64111363887787</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1488" t="n">
-        <v>1.72235667705536</v>
+        <v>1.72235679626465</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1489" t="n">
-        <v>1.71423244476318</v>
+        <v>1.71423232555389</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G1490" t="n">
-        <v>1.67767298221588</v>
+        <v>1.67767310142517</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G1491" t="n">
-        <v>1.67767298221588</v>
+        <v>1.67767310142517</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1492" t="n">
-        <v>1.70610797405243</v>
+        <v>1.70610809326172</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1493" t="n">
-        <v>1.76297831535339</v>
+        <v>1.76297843456268</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1494" t="n">
-        <v>1.68985950946808</v>
+        <v>1.68985939025879</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G1495" t="n">
-        <v>1.67767298221588</v>
+        <v>1.67767310142517</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1496" t="n">
-        <v>1.63298916816711</v>
+        <v>1.6329892873764</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G1498" t="n">
-        <v>1.59561729431152</v>
+        <v>1.59561741352081</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>1.98199999332428</v>
       </c>
       <c r="G1499" t="n">
-        <v>1.61024117469788</v>
+        <v>1.61024105548859</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G1500" t="n">
-        <v>1.56474483013153</v>
+        <v>1.56474494934082</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G1501" t="n">
-        <v>1.64517569541931</v>
+        <v>1.6451758146286</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1502" t="n">
-        <v>1.81984877586365</v>
+        <v>1.81984865665436</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1506" t="n">
-        <v>1.78735148906708</v>
+        <v>1.78735136985779</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G1507" t="n">
-        <v>1.74266755580902</v>
+        <v>1.74266767501831</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1508" t="n">
-        <v>1.74672985076904</v>
+        <v>1.74672996997833</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1509" t="n">
-        <v>1.73048114776611</v>
+        <v>1.7304812669754</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1511" t="n">
-        <v>1.77922713756561</v>
+        <v>1.77922701835632</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1513" t="n">
-        <v>1.77110278606415</v>
+        <v>1.77110290527344</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1514" t="n">
-        <v>1.7548543214798</v>
+        <v>1.75485420227051</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G1515" t="n">
-        <v>1.69392168521881</v>
+        <v>1.6939218044281</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1516" t="n">
-        <v>1.68985950946808</v>
+        <v>1.68985939025879</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G1517" t="n">
-        <v>1.69392168521881</v>
+        <v>1.6939218044281</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G1519" t="n">
-        <v>1.66142439842224</v>
+        <v>1.66142427921295</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1522" t="n">
-        <v>1.70610797405243</v>
+        <v>1.70610809326172</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>2.125</v>
       </c>
       <c r="G1527" t="n">
-        <v>1.72641909122467</v>
+        <v>1.72641885280609</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1528" t="n">
-        <v>1.72235667705536</v>
+        <v>1.72235679626465</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G1530" t="n">
-        <v>1.67767298221588</v>
+        <v>1.67767310142517</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1531" t="n">
-        <v>1.669548869133</v>
+        <v>1.66954874992371</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G1532" t="n">
-        <v>1.61999046802521</v>
+        <v>1.61999022960663</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1534" t="n">
-        <v>1.64111351966858</v>
+        <v>1.64111363887787</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1537" t="n">
-        <v>1.63298916816711</v>
+        <v>1.6329892873764</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G1539" t="n">
-        <v>1.5907427072525</v>
+        <v>1.59074258804321</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1542" t="n">
-        <v>1.48350155353546</v>
+        <v>1.48350167274475</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1543" t="n">
-        <v>1.50300014019012</v>
+        <v>1.50300002098083</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1544" t="n">
-        <v>1.51924860477448</v>
+        <v>1.51924872398376</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1548" t="n">
-        <v>1.54362165927887</v>
+        <v>1.54362177848816</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G1550" t="n">
-        <v>1.52249825000763</v>
+        <v>1.52249836921692</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G1552" t="n">
-        <v>1.44937944412231</v>
+        <v>1.4493795633316</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G1554" t="n">
-        <v>1.49812543392181</v>
+        <v>1.49812531471252</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G1556" t="n">
-        <v>1.44775450229645</v>
+        <v>1.44775462150574</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>1.72800004482269</v>
       </c>
       <c r="G1557" t="n">
-        <v>1.40388333797455</v>
+        <v>1.40388321876526</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>1.77400004863739</v>
       </c>
       <c r="G1558" t="n">
-        <v>1.44125533103943</v>
+        <v>1.44125521183014</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>1.68799996376038</v>
       </c>
       <c r="G1561" t="n">
-        <v>1.37138605117798</v>
+        <v>1.37138593196869</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G1562" t="n">
-        <v>1.35188746452332</v>
+        <v>1.3518875837326</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1563" t="n">
-        <v>1.35676217079163</v>
+        <v>1.35676205158234</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1564" t="n">
-        <v>1.3405134677887</v>
+        <v>1.34051358699799</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G1566" t="n">
-        <v>1.31126594543457</v>
+        <v>1.31126582622528</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.35351240634918</v>
+        <v>1.35351252555847</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>1.56400001049042</v>
       </c>
       <c r="G1570" t="n">
-        <v>1.27064454555511</v>
+        <v>1.27064442634583</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>1.5</v>
       </c>
       <c r="G1571" t="n">
-        <v>1.21864879131317</v>
+        <v>1.21864867210388</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G1572" t="n">
-        <v>1.21539902687073</v>
+        <v>1.21539890766144</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>1.5460000038147</v>
       </c>
       <c r="G1578" t="n">
-        <v>1.25602066516876</v>
+        <v>1.25602042675018</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1580" t="n">
-        <v>1.25114583969116</v>
+        <v>1.25114595890045</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>1.49399995803833</v>
       </c>
       <c r="G1582" t="n">
-        <v>1.21377396583557</v>
+        <v>1.21377408504486</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1584" t="n">
-        <v>1.14715456962585</v>
+        <v>1.14715468883514</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G1585" t="n">
-        <v>1.15202927589417</v>
+        <v>1.15202915668488</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1586" t="n">
-        <v>1.14552974700928</v>
+        <v>1.14552962779999</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1590" t="n">
-        <v>1.14390480518341</v>
+        <v>1.1439049243927</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1594" t="n">
-        <v>1.13740539550781</v>
+        <v>1.1374055147171</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>1.3639999628067</v>
       </c>
       <c r="G1595" t="n">
-        <v>1.10815787315369</v>
+        <v>1.1081577539444</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>1.46200001239777</v>
       </c>
       <c r="G1600" t="n">
-        <v>1.18777632713318</v>
+        <v>1.1877760887146</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G1601" t="n">
-        <v>1.20727443695068</v>
+        <v>1.20727455615997</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G1603" t="n">
-        <v>1.23977196216583</v>
+        <v>1.23977184295654</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G1604" t="n">
-        <v>1.22027361392975</v>
+        <v>1.22027349472046</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>1.432000041008</v>
       </c>
       <c r="G1605" t="n">
-        <v>1.16340339183807</v>
+        <v>1.16340327262878</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>1.432000041008</v>
       </c>
       <c r="G1607" t="n">
-        <v>1.16340339183807</v>
+        <v>1.16340327262878</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1608" t="n">
-        <v>1.16177845001221</v>
+        <v>1.16177833080292</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1609" t="n">
-        <v>1.16177845001221</v>
+        <v>1.16177833080292</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1610" t="n">
-        <v>1.16177845001221</v>
+        <v>1.16177833080292</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1611" t="n">
-        <v>1.16177845001221</v>
+        <v>1.16177833080292</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1616" t="n">
-        <v>1.09190917015076</v>
+        <v>1.09190928936005</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G1619" t="n">
-        <v>1.15527892112732</v>
+        <v>1.15527904033661</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1620" t="n">
-        <v>1.14715456962585</v>
+        <v>1.14715468883514</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>1.45799994468689</v>
       </c>
       <c r="G1627" t="n">
-        <v>1.18452632427216</v>
+        <v>1.18452644348145</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1628" t="n">
-        <v>1.2348974943161</v>
+        <v>1.23489725589752</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G1629" t="n">
-        <v>1.2365220785141</v>
+        <v>1.23652219772339</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G1630" t="n">
-        <v>1.27876853942871</v>
+        <v>1.278768658638</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>1.58599996566772</v>
       </c>
       <c r="G1631" t="n">
-        <v>1.28851771354675</v>
+        <v>1.28851795196533</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -71690,6 +71690,32 @@
         <v>0.773000001907349</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>77684</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>0.791000008583069</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>0.767000019550323</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>0.782000005245209</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>0.769999980926514</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>0.769999980926514</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/EM.MI.xlsx
+++ b/data/EM.MI.xlsx
@@ -427,7 +427,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G2" t="n">
-        <v>0.533523797988892</v>
+        <v>0.533523857593536</v>
       </c>
       <c r="H2" t="n">
         <v>21564</v>
@@ -456,7 +456,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G3" t="n">
-        <v>0.518079817295074</v>
+        <v>0.518079698085785</v>
       </c>
       <c r="H3" t="n">
         <v>297863</v>
@@ -485,7 +485,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G4" t="n">
-        <v>0.512463748455048</v>
+        <v>0.512463808059692</v>
       </c>
       <c r="H4" t="n">
         <v>53424</v>
@@ -514,7 +514,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G5" t="n">
-        <v>0.502635657787323</v>
+        <v>0.502635538578033</v>
       </c>
       <c r="H5" t="n">
         <v>211924</v>
@@ -630,7 +630,7 @@
         <v>0.728999972343445</v>
       </c>
       <c r="G9" t="n">
-        <v>0.511761724948883</v>
+        <v>0.511761665344238</v>
       </c>
       <c r="H9" t="n">
         <v>54763</v>
@@ -688,7 +688,7 @@
         <v>0.685000002384186</v>
       </c>
       <c r="G11" t="n">
-        <v>0.480873465538025</v>
+        <v>0.480873554944992</v>
       </c>
       <c r="H11" t="n">
         <v>49648</v>
@@ -746,7 +746,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G13" t="n">
-        <v>0.477363526821136</v>
+        <v>0.477363497018814</v>
       </c>
       <c r="H13" t="n">
         <v>58446</v>
@@ -775,7 +775,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G14" t="n">
-        <v>0.445071280002594</v>
+        <v>0.445071250200272</v>
       </c>
       <c r="H14" t="n">
         <v>72051</v>
@@ -804,7 +804,7 @@
         <v>0.639500021934509</v>
       </c>
       <c r="G15" t="n">
-        <v>0.448932260274887</v>
+        <v>0.448932319879532</v>
       </c>
       <c r="H15" t="n">
         <v>84253</v>
@@ -833,7 +833,7 @@
         <v>0.647000014781952</v>
       </c>
       <c r="G16" t="n">
-        <v>0.454197287559509</v>
+        <v>0.454197317361832</v>
       </c>
       <c r="H16" t="n">
         <v>101933</v>
@@ -891,7 +891,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G18" t="n">
-        <v>0.463323414325714</v>
+        <v>0.463323384523392</v>
       </c>
       <c r="H18" t="n">
         <v>1809</v>
@@ -920,7 +920,7 @@
         <v>0.659500002861023</v>
       </c>
       <c r="G19" t="n">
-        <v>0.462972342967987</v>
+        <v>0.462972372770309</v>
       </c>
       <c r="H19" t="n">
         <v>10258</v>
@@ -949,7 +949,7 @@
         <v>0.670499980449677</v>
       </c>
       <c r="G20" t="n">
-        <v>0.470694482326508</v>
+        <v>0.470694422721863</v>
       </c>
       <c r="H20" t="n">
         <v>45179</v>
@@ -978,7 +978,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G21" t="n">
-        <v>0.485787481069565</v>
+        <v>0.485787510871887</v>
       </c>
       <c r="H21" t="n">
         <v>10500</v>
@@ -1007,7 +1007,7 @@
         <v>0.689000010490417</v>
       </c>
       <c r="G22" t="n">
-        <v>0.483681559562683</v>
+        <v>0.483681529760361</v>
       </c>
       <c r="H22" t="n">
         <v>9549</v>
@@ -1036,7 +1036,7 @@
         <v>0.693000018596649</v>
       </c>
       <c r="G23" t="n">
-        <v>0.486489534378052</v>
+        <v>0.486489593982697</v>
       </c>
       <c r="H23" t="n">
         <v>17350</v>
@@ -1065,7 +1065,7 @@
         <v>0.672999978065491</v>
       </c>
       <c r="G24" t="n">
-        <v>0.472449421882629</v>
+        <v>0.472449451684952</v>
       </c>
       <c r="H24" t="n">
         <v>29126</v>
@@ -1094,7 +1094,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G25" t="n">
-        <v>0.463323414325714</v>
+        <v>0.463323384523392</v>
       </c>
       <c r="H25" t="n">
         <v>26547</v>
@@ -1181,7 +1181,7 @@
         <v>0.604499995708466</v>
       </c>
       <c r="G28" t="n">
-        <v>0.42436209321022</v>
+        <v>0.424362063407898</v>
       </c>
       <c r="H28" t="n">
         <v>102808</v>
@@ -1210,7 +1210,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G29" t="n">
-        <v>0.473151534795761</v>
+        <v>0.473151504993439</v>
       </c>
       <c r="H29" t="n">
         <v>87928</v>
@@ -1239,7 +1239,7 @@
         <v>0.634999990463257</v>
       </c>
       <c r="G30" t="n">
-        <v>0.445773243904114</v>
+        <v>0.445773273706436</v>
       </c>
       <c r="H30" t="n">
         <v>29464</v>
@@ -1268,7 +1268,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G31" t="n">
-        <v>0.449283212423325</v>
+        <v>0.449283331632614</v>
       </c>
       <c r="H31" t="n">
         <v>16357</v>
@@ -1355,7 +1355,7 @@
         <v>0.710500001907349</v>
       </c>
       <c r="G34" t="n">
-        <v>0.498774617910385</v>
+        <v>0.498774737119675</v>
       </c>
       <c r="H34" t="n">
         <v>87293</v>
@@ -1384,7 +1384,7 @@
         <v>0.703499972820282</v>
       </c>
       <c r="G35" t="n">
-        <v>0.4938605427742</v>
+        <v>0.493860572576523</v>
       </c>
       <c r="H35" t="n">
         <v>118831</v>
@@ -1413,7 +1413,7 @@
         <v>0.699500024318695</v>
       </c>
       <c r="G36" t="n">
-        <v>0.491052567958832</v>
+        <v>0.491052657365799</v>
       </c>
       <c r="H36" t="n">
         <v>60100</v>
@@ -1442,7 +1442,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G37" t="n">
-        <v>0.495615541934967</v>
+        <v>0.495615631341934</v>
       </c>
       <c r="H37" t="n">
         <v>102262</v>
@@ -1471,7 +1471,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G38" t="n">
-        <v>0.491403549909592</v>
+        <v>0.491403609514236</v>
       </c>
       <c r="H38" t="n">
         <v>30498</v>
@@ -1500,7 +1500,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G39" t="n">
-        <v>0.491403549909592</v>
+        <v>0.491403609514236</v>
       </c>
       <c r="H39" t="n">
         <v>24688</v>
@@ -1529,7 +1529,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G40" t="n">
-        <v>0.522291779518127</v>
+        <v>0.522291839122772</v>
       </c>
       <c r="H40" t="n">
         <v>106876</v>
@@ -1558,7 +1558,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G41" t="n">
-        <v>0.505443692207336</v>
+        <v>0.505443751811981</v>
       </c>
       <c r="H41" t="n">
         <v>78128</v>
@@ -1587,7 +1587,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G42" t="n">
-        <v>0.499827653169632</v>
+        <v>0.499827712774277</v>
       </c>
       <c r="H42" t="n">
         <v>34876</v>
@@ -1616,7 +1616,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G43" t="n">
-        <v>0.519483804702759</v>
+        <v>0.519483864307404</v>
       </c>
       <c r="H43" t="n">
         <v>136156</v>
@@ -1645,7 +1645,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G44" t="n">
-        <v>0.519483804702759</v>
+        <v>0.519483864307404</v>
       </c>
       <c r="H44" t="n">
         <v>106691</v>
@@ -1732,7 +1732,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G47" t="n">
-        <v>0.561604022979736</v>
+        <v>0.561603963375092</v>
       </c>
       <c r="H47" t="n">
         <v>340974</v>
@@ -1761,7 +1761,7 @@
         <v>0.800999999046326</v>
       </c>
       <c r="G48" t="n">
-        <v>0.562306046485901</v>
+        <v>0.56230616569519</v>
       </c>
       <c r="H48" t="n">
         <v>735180</v>
@@ -1790,7 +1790,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G49" t="n">
-        <v>0.570028245449066</v>
+        <v>0.570028066635132</v>
       </c>
       <c r="H49" t="n">
         <v>616056</v>
@@ -1848,7 +1848,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G51" t="n">
-        <v>0.565816164016724</v>
+        <v>0.565816104412079</v>
       </c>
       <c r="H51" t="n">
         <v>22399</v>
@@ -1877,7 +1877,7 @@
         <v>0.772499978542328</v>
       </c>
       <c r="G52" t="n">
-        <v>0.542298913002014</v>
+        <v>0.542299032211304</v>
       </c>
       <c r="H52" t="n">
         <v>56713</v>
@@ -1906,7 +1906,7 @@
         <v>0.773000001907349</v>
       </c>
       <c r="G53" t="n">
-        <v>0.542649984359741</v>
+        <v>0.542649865150452</v>
       </c>
       <c r="H53" t="n">
         <v>22422</v>
@@ -1935,7 +1935,7 @@
         <v>0.777499973773956</v>
       </c>
       <c r="G54" t="n">
-        <v>0.545808970928192</v>
+        <v>0.545808911323547</v>
       </c>
       <c r="H54" t="n">
         <v>52736</v>
@@ -1964,7 +1964,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G55" t="n">
-        <v>0.53633189201355</v>
+        <v>0.536331832408905</v>
       </c>
       <c r="H55" t="n">
         <v>82495</v>
@@ -1993,7 +1993,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>0.533523797988892</v>
+        <v>0.533523857593536</v>
       </c>
       <c r="H56" t="n">
         <v>24555</v>
@@ -2051,7 +2051,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G58" t="n">
-        <v>0.561604022979736</v>
+        <v>0.561603963375092</v>
       </c>
       <c r="H58" t="n">
         <v>120900</v>
@@ -2080,7 +2080,7 @@
         <v>0.766499996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>0.538086950778961</v>
+        <v>0.538086891174316</v>
       </c>
       <c r="H59" t="n">
         <v>234658</v>
@@ -2109,7 +2109,7 @@
         <v>0.766499996185303</v>
       </c>
       <c r="G60" t="n">
-        <v>0.538086950778961</v>
+        <v>0.538086891174316</v>
       </c>
       <c r="H60" t="n">
         <v>11199</v>
@@ -2138,7 +2138,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G61" t="n">
-        <v>0.560200035572052</v>
+        <v>0.560200095176697</v>
       </c>
       <c r="H61" t="n">
         <v>23522</v>
@@ -2167,7 +2167,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G62" t="n">
-        <v>0.554583966732025</v>
+        <v>0.55458402633667</v>
       </c>
       <c r="H62" t="n">
         <v>181563</v>
@@ -2196,7 +2196,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G63" t="n">
-        <v>0.547563970088959</v>
+        <v>0.547564029693604</v>
       </c>
       <c r="H63" t="n">
         <v>80597</v>
@@ -2225,7 +2225,7 @@
         <v>0.760999977588654</v>
       </c>
       <c r="G64" t="n">
-        <v>0.534225821495056</v>
+        <v>0.534225881099701</v>
       </c>
       <c r="H64" t="n">
         <v>41514</v>
@@ -2254,7 +2254,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G65" t="n">
-        <v>0.533523797988892</v>
+        <v>0.533523857593536</v>
       </c>
       <c r="H65" t="n">
         <v>3018</v>
@@ -2283,7 +2283,7 @@
         <v>0.753000020980835</v>
       </c>
       <c r="G66" t="n">
-        <v>0.528609752655029</v>
+        <v>0.528609871864319</v>
       </c>
       <c r="H66" t="n">
         <v>2955</v>
@@ -2312,7 +2312,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G67" t="n">
-        <v>0.523695766925812</v>
+        <v>0.523695826530457</v>
       </c>
       <c r="H67" t="n">
         <v>123826</v>
@@ -2341,7 +2341,7 @@
         <v>0.75</v>
       </c>
       <c r="G68" t="n">
-        <v>0.52650386095047</v>
+        <v>0.526503801345825</v>
       </c>
       <c r="H68" t="n">
         <v>12420</v>
@@ -2370,7 +2370,7 @@
         <v>0.765500009059906</v>
       </c>
       <c r="G69" t="n">
-        <v>0.537384867668152</v>
+        <v>0.537384986877441</v>
       </c>
       <c r="H69" t="n">
         <v>2479</v>
@@ -2399,7 +2399,7 @@
         <v>0.774500012397766</v>
       </c>
       <c r="G70" t="n">
-        <v>0.543703019618988</v>
+        <v>0.543702960014343</v>
       </c>
       <c r="H70" t="n">
         <v>31799</v>
@@ -2428,7 +2428,7 @@
         <v>0.787000000476837</v>
       </c>
       <c r="G71" t="n">
-        <v>0.552478015422821</v>
+        <v>0.552478075027466</v>
       </c>
       <c r="H71" t="n">
         <v>15646</v>
@@ -2457,7 +2457,7 @@
         <v>0.795000016689301</v>
       </c>
       <c r="G72" t="n">
-        <v>0.558094143867493</v>
+        <v>0.558094084262848</v>
       </c>
       <c r="H72" t="n">
         <v>28709</v>
@@ -2515,7 +2515,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G74" t="n">
-        <v>0.554583966732025</v>
+        <v>0.55458402633667</v>
       </c>
       <c r="H74" t="n">
         <v>412</v>
@@ -2544,7 +2544,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G75" t="n">
-        <v>0.554583966732025</v>
+        <v>0.55458402633667</v>
       </c>
       <c r="H75" t="n">
         <v>15004</v>
@@ -2573,7 +2573,7 @@
         <v>0.795000016689301</v>
       </c>
       <c r="G76" t="n">
-        <v>0.558094143867493</v>
+        <v>0.558094084262848</v>
       </c>
       <c r="H76" t="n">
         <v>30618</v>
@@ -2602,7 +2602,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G77" t="n">
-        <v>0.572836220264435</v>
+        <v>0.57283616065979</v>
       </c>
       <c r="H77" t="n">
         <v>98169</v>
@@ -2660,7 +2660,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G79" t="n">
-        <v>0.571432173252106</v>
+        <v>0.57143223285675</v>
       </c>
       <c r="H79" t="n">
         <v>20303</v>
@@ -2689,7 +2689,7 @@
         <v>0.817499995231628</v>
       </c>
       <c r="G80" t="n">
-        <v>0.573889195919037</v>
+        <v>0.573889136314392</v>
       </c>
       <c r="H80" t="n">
         <v>328</v>
@@ -2718,7 +2718,7 @@
         <v>0.790499985218048</v>
       </c>
       <c r="G81" t="n">
-        <v>0.554935038089752</v>
+        <v>0.554935097694397</v>
       </c>
       <c r="H81" t="n">
         <v>15994</v>
@@ -2747,7 +2747,7 @@
         <v>0.790499985218048</v>
       </c>
       <c r="G82" t="n">
-        <v>0.554935038089752</v>
+        <v>0.554935097694397</v>
       </c>
       <c r="H82" t="n">
         <v>2005</v>
@@ -2805,7 +2805,7 @@
         <v>0.766499996185303</v>
       </c>
       <c r="G84" t="n">
-        <v>0.538086950778961</v>
+        <v>0.538086891174316</v>
       </c>
       <c r="H84" t="n">
         <v>47211</v>
@@ -2834,7 +2834,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G85" t="n">
-        <v>0.540543913841248</v>
+        <v>0.540543973445892</v>
       </c>
       <c r="H85" t="n">
         <v>2700</v>
@@ -2863,7 +2863,7 @@
         <v>0.761500000953674</v>
       </c>
       <c r="G86" t="n">
-        <v>0.534576892852783</v>
+        <v>0.534576833248138</v>
       </c>
       <c r="H86" t="n">
         <v>1950</v>
@@ -2892,7 +2892,7 @@
         <v>0.750999987125397</v>
       </c>
       <c r="G87" t="n">
-        <v>0.527205884456635</v>
+        <v>0.52720582485199</v>
       </c>
       <c r="H87" t="n">
         <v>8005</v>
@@ -2921,7 +2921,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G88" t="n">
-        <v>0.537735939025879</v>
+        <v>0.537735879421234</v>
       </c>
       <c r="H88" t="n">
         <v>11711</v>
@@ -2950,7 +2950,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G89" t="n">
-        <v>0.540543913841248</v>
+        <v>0.540543973445892</v>
       </c>
       <c r="H89" t="n">
         <v>7930</v>
@@ -3008,7 +3008,7 @@
         <v>0.751500010490417</v>
       </c>
       <c r="G91" t="n">
-        <v>0.527556836605072</v>
+        <v>0.527556777000427</v>
       </c>
       <c r="H91" t="n">
         <v>17680</v>
@@ -3037,7 +3037,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G92" t="n">
-        <v>0.519483804702759</v>
+        <v>0.519483864307404</v>
       </c>
       <c r="H92" t="n">
         <v>38027</v>
@@ -3066,7 +3066,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G93" t="n">
-        <v>0.516675770282745</v>
+        <v>0.51667582988739</v>
       </c>
       <c r="H93" t="n">
         <v>20016</v>
@@ -3124,7 +3124,7 @@
         <v>0.756500005722046</v>
       </c>
       <c r="G95" t="n">
-        <v>0.53106689453125</v>
+        <v>0.53106701374054</v>
       </c>
       <c r="H95" t="n">
         <v>11236</v>
@@ -3153,7 +3153,7 @@
         <v>0.745000004768372</v>
       </c>
       <c r="G96" t="n">
-        <v>0.522993803024292</v>
+        <v>0.522993862628937</v>
       </c>
       <c r="H96" t="n">
         <v>30278</v>
@@ -3182,7 +3182,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G97" t="n">
-        <v>0.519483804702759</v>
+        <v>0.519483864307404</v>
       </c>
       <c r="H97" t="n">
         <v>16218</v>
@@ -3211,7 +3211,7 @@
         <v>0.72350001335144</v>
       </c>
       <c r="G98" t="n">
-        <v>0.507900774478912</v>
+        <v>0.507900714874268</v>
       </c>
       <c r="H98" t="n">
         <v>19870</v>
@@ -3240,7 +3240,7 @@
         <v>0.710500001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>0.498774617910385</v>
+        <v>0.498774737119675</v>
       </c>
       <c r="H99" t="n">
         <v>44948</v>
@@ -3269,7 +3269,7 @@
         <v>0.715499997138977</v>
       </c>
       <c r="G100" t="n">
-        <v>0.502284705638885</v>
+        <v>0.502284646034241</v>
       </c>
       <c r="H100" t="n">
         <v>50051</v>
@@ -3356,7 +3356,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G103" t="n">
-        <v>0.512463748455048</v>
+        <v>0.512463808059692</v>
       </c>
       <c r="H103" t="n">
         <v>27329</v>
@@ -3385,7 +3385,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G104" t="n">
-        <v>0.512463748455048</v>
+        <v>0.512463808059692</v>
       </c>
       <c r="H104" t="n">
         <v>18929</v>
@@ -3414,7 +3414,7 @@
         <v>0.732500016689301</v>
       </c>
       <c r="G105" t="n">
-        <v>0.514218747615814</v>
+        <v>0.514218807220459</v>
       </c>
       <c r="H105" t="n">
         <v>53015</v>
@@ -3443,7 +3443,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G106" t="n">
-        <v>0.512463748455048</v>
+        <v>0.512463808059692</v>
       </c>
       <c r="H106" t="n">
         <v>117779</v>
@@ -3472,7 +3472,7 @@
         <v>0.736500024795532</v>
       </c>
       <c r="G107" t="n">
-        <v>0.517026841640472</v>
+        <v>0.517026782035828</v>
       </c>
       <c r="H107" t="n">
         <v>61073</v>
@@ -3501,7 +3501,7 @@
         <v>0.746500015258789</v>
       </c>
       <c r="G108" t="n">
-        <v>0.524046778678894</v>
+        <v>0.524046897888184</v>
       </c>
       <c r="H108" t="n">
         <v>22780</v>
@@ -3530,7 +3530,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G109" t="n">
-        <v>0.523695766925812</v>
+        <v>0.523695826530457</v>
       </c>
       <c r="H109" t="n">
         <v>115068</v>
@@ -3588,7 +3588,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G111" t="n">
-        <v>0.520064055919647</v>
+        <v>0.520064115524292</v>
       </c>
       <c r="H111" t="n">
         <v>30142</v>
@@ -3617,7 +3617,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G112" t="n">
-        <v>0.524422109127045</v>
+        <v>0.524422168731689</v>
       </c>
       <c r="H112" t="n">
         <v>23958</v>
@@ -3646,7 +3646,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G113" t="n">
-        <v>0.524422109127045</v>
+        <v>0.524422168731689</v>
       </c>
       <c r="H113" t="n">
         <v>38320</v>
@@ -3704,7 +3704,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G115" t="n">
-        <v>0.511347889900208</v>
+        <v>0.511347949504852</v>
       </c>
       <c r="H115" t="n">
         <v>22805</v>
@@ -3733,7 +3733,7 @@
         <v>0.700500011444092</v>
       </c>
       <c r="G116" t="n">
-        <v>0.508805751800537</v>
+        <v>0.508805811405182</v>
       </c>
       <c r="H116" t="n">
         <v>11977</v>
@@ -3791,7 +3791,7 @@
         <v>0.700500011444092</v>
       </c>
       <c r="G118" t="n">
-        <v>0.508805751800537</v>
+        <v>0.508805811405182</v>
       </c>
       <c r="H118" t="n">
         <v>1690</v>
@@ -3878,7 +3878,7 @@
         <v>0.700500011444092</v>
       </c>
       <c r="G121" t="n">
-        <v>0.508805751800537</v>
+        <v>0.508805811405182</v>
       </c>
       <c r="H121" t="n">
         <v>8518</v>
@@ -3907,7 +3907,7 @@
         <v>0.716499984264374</v>
       </c>
       <c r="G122" t="n">
-        <v>0.520427286624908</v>
+        <v>0.520427227020264</v>
       </c>
       <c r="H122" t="n">
         <v>28793</v>
@@ -3936,7 +3936,7 @@
         <v>0.720499992370605</v>
       </c>
       <c r="G123" t="n">
-        <v>0.523332715034485</v>
+        <v>0.52333265542984</v>
       </c>
       <c r="H123" t="n">
         <v>24872</v>
@@ -3965,7 +3965,7 @@
         <v>0.683000028133392</v>
       </c>
       <c r="G124" t="n">
-        <v>0.496094703674316</v>
+        <v>0.496094673871994</v>
       </c>
       <c r="H124" t="n">
         <v>28005</v>
@@ -4023,7 +4023,7 @@
         <v>0.70550000667572</v>
       </c>
       <c r="G126" t="n">
-        <v>0.512437343597412</v>
+        <v>0.512437522411346</v>
       </c>
       <c r="H126" t="n">
         <v>2005</v>
@@ -4052,7 +4052,7 @@
         <v>0.717000007629395</v>
       </c>
       <c r="G127" t="n">
-        <v>0.520790457725525</v>
+        <v>0.52079039812088</v>
       </c>
       <c r="H127" t="n">
         <v>505</v>
@@ -4081,7 +4081,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G128" t="n">
-        <v>0.509895205497742</v>
+        <v>0.509895265102386</v>
       </c>
       <c r="H128" t="n">
         <v>771</v>
@@ -4110,7 +4110,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G129" t="n">
-        <v>0.51715874671936</v>
+        <v>0.517158627510071</v>
       </c>
       <c r="H129" t="n">
         <v>2150</v>
@@ -4139,7 +4139,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G130" t="n">
-        <v>0.504810750484467</v>
+        <v>0.504810810089111</v>
       </c>
       <c r="H130" t="n">
         <v>32655</v>
@@ -4168,7 +4168,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G131" t="n">
-        <v>0.496821016073227</v>
+        <v>0.496820956468582</v>
       </c>
       <c r="H131" t="n">
         <v>25170</v>
@@ -4197,7 +4197,7 @@
         <v>0.669000029563904</v>
       </c>
       <c r="G132" t="n">
-        <v>0.485925793647766</v>
+        <v>0.485925823450089</v>
       </c>
       <c r="H132" t="n">
         <v>24314</v>
@@ -4226,7 +4226,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G133" t="n">
-        <v>0.476483345031738</v>
+        <v>0.476483315229416</v>
       </c>
       <c r="H133" t="n">
         <v>40262</v>
@@ -4255,7 +4255,7 @@
         <v>0.661499977111816</v>
       </c>
       <c r="G134" t="n">
-        <v>0.480478227138519</v>
+        <v>0.480478197336197</v>
       </c>
       <c r="H134" t="n">
         <v>50445</v>
@@ -4284,7 +4284,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G135" t="n">
-        <v>0.486652135848999</v>
+        <v>0.486652106046677</v>
       </c>
       <c r="H135" t="n">
         <v>14719</v>
@@ -4313,7 +4313,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G136" t="n">
-        <v>0.486652135848999</v>
+        <v>0.486652106046677</v>
       </c>
       <c r="H136" t="n">
         <v>65267</v>
@@ -4342,7 +4342,7 @@
         <v>0.662999987602234</v>
       </c>
       <c r="G137" t="n">
-        <v>0.481567740440369</v>
+        <v>0.481567770242691</v>
       </c>
       <c r="H137" t="n">
         <v>20578</v>
@@ -4371,7 +4371,7 @@
         <v>0.662999987602234</v>
       </c>
       <c r="G138" t="n">
-        <v>0.481567740440369</v>
+        <v>0.481567770242691</v>
       </c>
       <c r="H138" t="n">
         <v>28795</v>
@@ -4400,7 +4400,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G139" t="n">
-        <v>0.492462903261185</v>
+        <v>0.492462992668152</v>
       </c>
       <c r="H139" t="n">
         <v>22196</v>
@@ -4429,7 +4429,7 @@
         <v>0.684499979019165</v>
       </c>
       <c r="G140" t="n">
-        <v>0.497184157371521</v>
+        <v>0.497184187173843</v>
       </c>
       <c r="H140" t="n">
         <v>9736</v>
@@ -4458,7 +4458,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G141" t="n">
-        <v>0.486652135848999</v>
+        <v>0.486652106046677</v>
       </c>
       <c r="H141" t="n">
         <v>128976</v>
@@ -4487,7 +4487,7 @@
         <v>0.697499990463257</v>
       </c>
       <c r="G142" t="n">
-        <v>0.506626665592194</v>
+        <v>0.506626725196838</v>
       </c>
       <c r="H142" t="n">
         <v>30306</v>
@@ -4545,7 +4545,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G144" t="n">
-        <v>0.493915677070618</v>
+        <v>0.493915617465973</v>
       </c>
       <c r="H144" t="n">
         <v>55889</v>
@@ -4632,7 +4632,7 @@
         <v>0.669000029563904</v>
       </c>
       <c r="G147" t="n">
-        <v>0.485925793647766</v>
+        <v>0.485925823450089</v>
       </c>
       <c r="H147" t="n">
         <v>336135</v>
@@ -4690,7 +4690,7 @@
         <v>0.665499985218048</v>
       </c>
       <c r="G149" t="n">
-        <v>0.483383595943451</v>
+        <v>0.483383566141129</v>
       </c>
       <c r="H149" t="n">
         <v>13095</v>
@@ -4719,7 +4719,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G150" t="n">
-        <v>0.486652135848999</v>
+        <v>0.486652106046677</v>
       </c>
       <c r="H150" t="n">
         <v>37042</v>
@@ -4777,7 +4777,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G152" t="n">
-        <v>0.489557594060898</v>
+        <v>0.489557504653931</v>
       </c>
       <c r="H152" t="n">
         <v>17357</v>
@@ -4806,7 +4806,7 @@
         <v>0.66100001335144</v>
       </c>
       <c r="G153" t="n">
-        <v>0.480115085840225</v>
+        <v>0.480114996433258</v>
       </c>
       <c r="H153" t="n">
         <v>6011</v>
@@ -4835,7 +4835,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G154" t="n">
-        <v>0.486652135848999</v>
+        <v>0.486652106046677</v>
       </c>
       <c r="H154" t="n">
         <v>75689</v>
@@ -4864,7 +4864,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G155" t="n">
-        <v>0.488104850053787</v>
+        <v>0.488104820251465</v>
       </c>
       <c r="H155" t="n">
         <v>147764</v>
@@ -4893,7 +4893,7 @@
         <v>0.677500009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>0.492099702358246</v>
+        <v>0.492099672555923</v>
       </c>
       <c r="H156" t="n">
         <v>23358</v>
@@ -4922,7 +4922,7 @@
         <v>0.677500009536743</v>
       </c>
       <c r="G157" t="n">
-        <v>0.492099702358246</v>
+        <v>0.492099672555923</v>
       </c>
       <c r="H157" t="n">
         <v>30395</v>
@@ -4951,7 +4951,7 @@
         <v>0.685000002384186</v>
       </c>
       <c r="G158" t="n">
-        <v>0.497547298669815</v>
+        <v>0.497547268867493</v>
       </c>
       <c r="H158" t="n">
         <v>35927</v>
@@ -4980,7 +4980,7 @@
         <v>0.694500029087067</v>
       </c>
       <c r="G159" t="n">
-        <v>0.504447638988495</v>
+        <v>0.50444769859314</v>
       </c>
       <c r="H159" t="n">
         <v>29162</v>
@@ -5125,7 +5125,7 @@
         <v>0.734499990940094</v>
       </c>
       <c r="G164" t="n">
-        <v>0.533501505851746</v>
+        <v>0.533501446247101</v>
       </c>
       <c r="H164" t="n">
         <v>32862</v>
@@ -5154,7 +5154,7 @@
         <v>0.739499986171722</v>
       </c>
       <c r="G165" t="n">
-        <v>0.53713321685791</v>
+        <v>0.537133157253265</v>
       </c>
       <c r="H165" t="n">
         <v>15939</v>
@@ -5212,7 +5212,7 @@
         <v>0.746500015258789</v>
       </c>
       <c r="G167" t="n">
-        <v>0.542217612266541</v>
+        <v>0.54221773147583</v>
       </c>
       <c r="H167" t="n">
         <v>667</v>
@@ -5241,7 +5241,7 @@
         <v>0.746500015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>0.542217612266541</v>
+        <v>0.54221773147583</v>
       </c>
       <c r="H168" t="n">
         <v>6263</v>
@@ -5270,7 +5270,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G169" t="n">
-        <v>0.536770045757294</v>
+        <v>0.536769986152649</v>
       </c>
       <c r="H169" t="n">
         <v>10185</v>
@@ -5299,7 +5299,7 @@
         <v>0.739499986171722</v>
       </c>
       <c r="G170" t="n">
-        <v>0.53713321685791</v>
+        <v>0.537133157253265</v>
       </c>
       <c r="H170" t="n">
         <v>22241</v>
@@ -5328,7 +5328,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G171" t="n">
-        <v>0.547665238380432</v>
+        <v>0.547665297985077</v>
       </c>
       <c r="H171" t="n">
         <v>45038</v>
@@ -5357,7 +5357,7 @@
         <v>0.771499991416931</v>
       </c>
       <c r="G172" t="n">
-        <v>0.560376346111298</v>
+        <v>0.560376286506653</v>
       </c>
       <c r="H172" t="n">
         <v>80724</v>
@@ -5386,7 +5386,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G173" t="n">
-        <v>0.566550195217133</v>
+        <v>0.566550254821777</v>
       </c>
       <c r="H173" t="n">
         <v>210064</v>
@@ -5473,7 +5473,7 @@
         <v>0.778999984264374</v>
       </c>
       <c r="G176" t="n">
-        <v>0.565823972225189</v>
+        <v>0.565823793411255</v>
       </c>
       <c r="H176" t="n">
         <v>48823</v>
@@ -5502,7 +5502,7 @@
         <v>0.773000001907349</v>
       </c>
       <c r="G177" t="n">
-        <v>0.561465859413147</v>
+        <v>0.561465799808502</v>
       </c>
       <c r="H177" t="n">
         <v>81390</v>
@@ -5531,7 +5531,7 @@
         <v>0.773000001907349</v>
       </c>
       <c r="G178" t="n">
-        <v>0.561465859413147</v>
+        <v>0.561465799808502</v>
       </c>
       <c r="H178" t="n">
         <v>16900</v>
@@ -5618,7 +5618,7 @@
         <v>0.763000011444092</v>
       </c>
       <c r="G181" t="n">
-        <v>0.554202377796173</v>
+        <v>0.554202437400818</v>
       </c>
       <c r="H181" t="n">
         <v>99213</v>
@@ -5647,7 +5647,7 @@
         <v>0.757499992847443</v>
       </c>
       <c r="G182" t="n">
-        <v>0.550207436084747</v>
+        <v>0.550207495689392</v>
       </c>
       <c r="H182" t="n">
         <v>14948</v>
@@ -5676,7 +5676,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G183" t="n">
-        <v>0.549117922782898</v>
+        <v>0.549117982387543</v>
       </c>
       <c r="H183" t="n">
         <v>20477</v>
@@ -5705,7 +5705,7 @@
         <v>0.774500012397766</v>
       </c>
       <c r="G184" t="n">
-        <v>0.562555372714996</v>
+        <v>0.562555313110352</v>
       </c>
       <c r="H184" t="n">
         <v>80691</v>
@@ -5734,7 +5734,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G185" t="n">
-        <v>0.565097630023956</v>
+        <v>0.565097510814667</v>
       </c>
       <c r="H185" t="n">
         <v>183268</v>
@@ -5763,7 +5763,7 @@
         <v>0.796999990940094</v>
       </c>
       <c r="G186" t="n">
-        <v>0.578898191452026</v>
+        <v>0.578898131847382</v>
       </c>
       <c r="H186" t="n">
         <v>199584</v>
@@ -5850,7 +5850,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G189" t="n">
-        <v>0.573813617229462</v>
+        <v>0.573813736438751</v>
       </c>
       <c r="H189" t="n">
         <v>7512</v>
@@ -5879,7 +5879,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G190" t="n">
-        <v>0.566550195217133</v>
+        <v>0.566550254821777</v>
       </c>
       <c r="H190" t="n">
         <v>21830</v>
@@ -5966,7 +5966,7 @@
         <v>0.795000016689301</v>
       </c>
       <c r="G193" t="n">
-        <v>0.577445507049561</v>
+        <v>0.577445447444916</v>
       </c>
       <c r="H193" t="n">
         <v>22834</v>
@@ -6053,7 +6053,7 @@
         <v>0.783500015735626</v>
       </c>
       <c r="G196" t="n">
-        <v>0.569092512130737</v>
+        <v>0.569092571735382</v>
       </c>
       <c r="H196" t="n">
         <v>52687</v>
@@ -6082,7 +6082,7 @@
         <v>0.783500015735626</v>
       </c>
       <c r="G197" t="n">
-        <v>0.569092512130737</v>
+        <v>0.569092571735382</v>
       </c>
       <c r="H197" t="n">
         <v>6871</v>
@@ -6111,7 +6111,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G198" t="n">
-        <v>0.573813617229462</v>
+        <v>0.573813736438751</v>
       </c>
       <c r="H198" t="n">
         <v>18994</v>
@@ -6198,7 +6198,7 @@
         <v>0.807500004768372</v>
       </c>
       <c r="G201" t="n">
-        <v>0.586524724960327</v>
+        <v>0.586524784564972</v>
       </c>
       <c r="H201" t="n">
         <v>14017</v>
@@ -6343,7 +6343,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G206" t="n">
-        <v>0.578171849250793</v>
+        <v>0.578171730041504</v>
       </c>
       <c r="H206" t="n">
         <v>16345</v>
@@ -6372,7 +6372,7 @@
         <v>0.801500022411346</v>
       </c>
       <c r="G207" t="n">
-        <v>0.582166731357574</v>
+        <v>0.582166612148285</v>
       </c>
       <c r="H207" t="n">
         <v>33880</v>
@@ -6401,7 +6401,7 @@
         <v>0.807500004768372</v>
       </c>
       <c r="G208" t="n">
-        <v>0.586524724960327</v>
+        <v>0.586524784564972</v>
       </c>
       <c r="H208" t="n">
         <v>9737</v>
@@ -6459,7 +6459,7 @@
         <v>0.802999973297119</v>
       </c>
       <c r="G210" t="n">
-        <v>0.583256244659424</v>
+        <v>0.583256185054779</v>
       </c>
       <c r="H210" t="n">
         <v>42656</v>
@@ -6604,7 +6604,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G215" t="n">
-        <v>0.594151377677917</v>
+        <v>0.594151437282562</v>
       </c>
       <c r="H215" t="n">
         <v>14485</v>
@@ -6662,7 +6662,7 @@
         <v>0.828999996185303</v>
       </c>
       <c r="G217" t="n">
-        <v>0.602141261100769</v>
+        <v>0.602141201496124</v>
       </c>
       <c r="H217" t="n">
         <v>50642</v>
@@ -6749,7 +6749,7 @@
         <v>0.819500029087067</v>
       </c>
       <c r="G220" t="n">
-        <v>0.595240950584412</v>
+        <v>0.595241010189056</v>
       </c>
       <c r="H220" t="n">
         <v>11381</v>
@@ -6836,7 +6836,7 @@
         <v>0.841000020503998</v>
       </c>
       <c r="G223" t="n">
-        <v>0.610857427120209</v>
+        <v>0.610857367515564</v>
       </c>
       <c r="H223" t="n">
         <v>258664</v>
@@ -6894,7 +6894,7 @@
         <v>0.83050000667572</v>
       </c>
       <c r="G225" t="n">
-        <v>0.603230714797974</v>
+        <v>0.603230774402618</v>
       </c>
       <c r="H225" t="n">
         <v>23318</v>
@@ -6923,7 +6923,7 @@
         <v>0.833500027656555</v>
       </c>
       <c r="G226" t="n">
-        <v>0.605409860610962</v>
+        <v>0.605409801006317</v>
       </c>
       <c r="H226" t="n">
         <v>105062</v>
@@ -6952,7 +6952,7 @@
         <v>0.829500019550323</v>
       </c>
       <c r="G227" t="n">
-        <v>0.602504432201385</v>
+        <v>0.60250449180603</v>
       </c>
       <c r="H227" t="n">
         <v>81013</v>
@@ -6981,7 +6981,7 @@
         <v>0.83050000667572</v>
       </c>
       <c r="G228" t="n">
-        <v>0.603230714797974</v>
+        <v>0.603230774402618</v>
       </c>
       <c r="H228" t="n">
         <v>88957</v>
@@ -7010,7 +7010,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G229" t="n">
-        <v>0.595604062080383</v>
+        <v>0.595604121685028</v>
       </c>
       <c r="H229" t="n">
         <v>22295</v>
@@ -7039,7 +7039,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G230" t="n">
-        <v>0.601414859294891</v>
+        <v>0.601414978504181</v>
       </c>
       <c r="H230" t="n">
         <v>46478</v>
@@ -7068,7 +7068,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G231" t="n">
-        <v>0.595604062080383</v>
+        <v>0.595604121685028</v>
       </c>
       <c r="H231" t="n">
         <v>65452</v>
@@ -7097,7 +7097,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G232" t="n">
-        <v>0.595604062080383</v>
+        <v>0.595604121685028</v>
       </c>
       <c r="H232" t="n">
         <v>22499</v>
@@ -7126,7 +7126,7 @@
         <v>0.814999997615814</v>
       </c>
       <c r="G233" t="n">
-        <v>0.591972351074219</v>
+        <v>0.591972410678864</v>
       </c>
       <c r="H233" t="n">
         <v>13767</v>
@@ -7155,7 +7155,7 @@
         <v>0.83050000667572</v>
       </c>
       <c r="G234" t="n">
-        <v>0.603230714797974</v>
+        <v>0.603230774402618</v>
       </c>
       <c r="H234" t="n">
         <v>86829</v>
@@ -7184,7 +7184,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G235" t="n">
-        <v>0.59996223449707</v>
+        <v>0.599962174892426</v>
       </c>
       <c r="H235" t="n">
         <v>13634</v>
@@ -7329,7 +7329,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G240" t="n">
-        <v>0.606499314308167</v>
+        <v>0.606499254703522</v>
       </c>
       <c r="H240" t="n">
         <v>14505</v>
@@ -7358,7 +7358,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G241" t="n">
-        <v>0.608678340911865</v>
+        <v>0.60867840051651</v>
       </c>
       <c r="H241" t="n">
         <v>3694</v>
@@ -7474,7 +7474,7 @@
         <v>0.835500001907349</v>
       </c>
       <c r="G245" t="n">
-        <v>0.606862485408783</v>
+        <v>0.606862545013428</v>
       </c>
       <c r="H245" t="n">
         <v>63041</v>
@@ -7532,7 +7532,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G247" t="n">
-        <v>0.614489138126373</v>
+        <v>0.614489078521729</v>
       </c>
       <c r="H247" t="n">
         <v>23241</v>
@@ -7619,7 +7619,7 @@
         <v>0.883000016212463</v>
       </c>
       <c r="G250" t="n">
-        <v>0.64136403799057</v>
+        <v>0.641363918781281</v>
       </c>
       <c r="H250" t="n">
         <v>169896</v>
@@ -7648,7 +7648,7 @@
         <v>0.875500023365021</v>
       </c>
       <c r="G251" t="n">
-        <v>0.635916292667389</v>
+        <v>0.635916352272034</v>
       </c>
       <c r="H251" t="n">
         <v>83995</v>
@@ -7677,7 +7677,7 @@
         <v>0.876500010490417</v>
       </c>
       <c r="G252" t="n">
-        <v>0.636642634868622</v>
+        <v>0.636642694473267</v>
       </c>
       <c r="H252" t="n">
         <v>41511</v>
@@ -7793,7 +7793,7 @@
         <v>0.912500023841858</v>
       </c>
       <c r="G256" t="n">
-        <v>0.662791073322296</v>
+        <v>0.66279125213623</v>
       </c>
       <c r="H256" t="n">
         <v>225093</v>
@@ -7822,7 +7822,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G257" t="n">
-        <v>0.660975337028503</v>
+        <v>0.660975396633148</v>
       </c>
       <c r="H257" t="n">
         <v>39613</v>
@@ -7851,7 +7851,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G258" t="n">
-        <v>0.665333390235901</v>
+        <v>0.665333449840546</v>
       </c>
       <c r="H258" t="n">
         <v>83638</v>
@@ -7909,7 +7909,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G260" t="n">
-        <v>0.657343506813049</v>
+        <v>0.657343566417694</v>
       </c>
       <c r="H260" t="n">
         <v>18991</v>
@@ -7938,7 +7938,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G261" t="n">
-        <v>0.657343506813049</v>
+        <v>0.657343566417694</v>
       </c>
       <c r="H261" t="n">
         <v>26783</v>
@@ -7967,7 +7967,7 @@
         <v>0.913999974727631</v>
       </c>
       <c r="G262" t="n">
-        <v>0.66388064622879</v>
+        <v>0.663880586624146</v>
       </c>
       <c r="H262" t="n">
         <v>4024</v>
@@ -7996,7 +7996,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G263" t="n">
-        <v>0.660975337028503</v>
+        <v>0.660975396633148</v>
       </c>
       <c r="H263" t="n">
         <v>76160</v>
@@ -8025,7 +8025,7 @@
         <v>0.919000029563904</v>
       </c>
       <c r="G264" t="n">
-        <v>0.6675124168396</v>
+        <v>0.667512357234955</v>
       </c>
       <c r="H264" t="n">
         <v>22615</v>
@@ -8054,7 +8054,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G265" t="n">
-        <v>0.660975337028503</v>
+        <v>0.660975396633148</v>
       </c>
       <c r="H265" t="n">
         <v>58678</v>
@@ -8083,7 +8083,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G266" t="n">
-        <v>0.658070027828217</v>
+        <v>0.658069968223572</v>
       </c>
       <c r="H266" t="n">
         <v>55598</v>
@@ -8141,7 +8141,7 @@
         <v>0.908500015735626</v>
       </c>
       <c r="G268" t="n">
-        <v>0.659885704517365</v>
+        <v>0.659885823726654</v>
       </c>
       <c r="H268" t="n">
         <v>29310</v>
@@ -8170,7 +8170,7 @@
         <v>0.934499979019165</v>
       </c>
       <c r="G269" t="n">
-        <v>0.678770840167999</v>
+        <v>0.678770780563354</v>
       </c>
       <c r="H269" t="n">
         <v>149226</v>
@@ -8199,7 +8199,7 @@
         <v>0.942499995231628</v>
       </c>
       <c r="G270" t="n">
-        <v>0.684581577777863</v>
+        <v>0.684581518173218</v>
       </c>
       <c r="H270" t="n">
         <v>67403</v>
@@ -8228,7 +8228,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G271" t="n">
-        <v>0.681313037872314</v>
+        <v>0.681313097476959</v>
       </c>
       <c r="H271" t="n">
         <v>27701</v>
@@ -8286,7 +8286,7 @@
         <v>0.957499980926514</v>
       </c>
       <c r="G273" t="n">
-        <v>0.695476830005646</v>
+        <v>0.695476770401001</v>
       </c>
       <c r="H273" t="n">
         <v>115910</v>
@@ -8460,7 +8460,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G279" t="n">
-        <v>0.668238759040833</v>
+        <v>0.668238818645477</v>
       </c>
       <c r="H279" t="n">
         <v>53266</v>
@@ -8489,7 +8489,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G280" t="n">
-        <v>0.681313037872314</v>
+        <v>0.681313097476959</v>
       </c>
       <c r="H280" t="n">
         <v>84975</v>
@@ -8663,7 +8663,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G286" t="n">
-        <v>0.711819529533386</v>
+        <v>0.711819589138031</v>
       </c>
       <c r="H286" t="n">
         <v>200382</v>
@@ -8692,7 +8692,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G287" t="n">
-        <v>0.720535755157471</v>
+        <v>0.720535695552826</v>
       </c>
       <c r="H287" t="n">
         <v>528262</v>
@@ -8750,7 +8750,7 @@
         <v>0.974500000476837</v>
       </c>
       <c r="G289" t="n">
-        <v>0.70782470703125</v>
+        <v>0.707824647426605</v>
       </c>
       <c r="H289" t="n">
         <v>116802</v>
@@ -8779,7 +8779,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G290" t="n">
-        <v>0.711819529533386</v>
+        <v>0.711819589138031</v>
       </c>
       <c r="H290" t="n">
         <v>84570</v>
@@ -8837,7 +8837,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G292" t="n">
-        <v>0.711819529533386</v>
+        <v>0.711819589138031</v>
       </c>
       <c r="H292" t="n">
         <v>79819</v>
@@ -8866,7 +8866,7 @@
         <v>0.977500021457672</v>
       </c>
       <c r="G293" t="n">
-        <v>0.710003614425659</v>
+        <v>0.710003733634949</v>
       </c>
       <c r="H293" t="n">
         <v>79975</v>
@@ -8924,7 +8924,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G295" t="n">
-        <v>0.740873336791992</v>
+        <v>0.740873515605927</v>
       </c>
       <c r="H295" t="n">
         <v>414230</v>
@@ -8953,7 +8953,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G296" t="n">
-        <v>0.766295552253723</v>
+        <v>0.766295492649078</v>
       </c>
       <c r="H296" t="n">
         <v>568829</v>
@@ -8982,7 +8982,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G297" t="n">
-        <v>0.780822455883026</v>
+        <v>0.780822515487671</v>
       </c>
       <c r="H297" t="n">
         <v>380865</v>
@@ -9011,7 +9011,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G298" t="n">
-        <v>0.777190864086151</v>
+        <v>0.777190685272217</v>
       </c>
       <c r="H298" t="n">
         <v>249671</v>
@@ -9098,7 +9098,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G301" t="n">
-        <v>0.85708874464035</v>
+        <v>0.85708886384964</v>
       </c>
       <c r="H301" t="n">
         <v>192095</v>
@@ -9127,7 +9127,7 @@
         <v>1.20299994945526</v>
       </c>
       <c r="G302" t="n">
-        <v>0.873794853687286</v>
+        <v>0.873794794082642</v>
       </c>
       <c r="H302" t="n">
         <v>463138</v>
@@ -9243,7 +9243,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G306" t="n">
-        <v>0.882510900497437</v>
+        <v>0.882511079311371</v>
       </c>
       <c r="H306" t="n">
         <v>1618702</v>
@@ -9272,7 +9272,7 @@
         <v>1.28900003433228</v>
       </c>
       <c r="G307" t="n">
-        <v>0.936260581016541</v>
+        <v>0.936260759830475</v>
       </c>
       <c r="H307" t="n">
         <v>991754</v>
@@ -9359,7 +9359,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G310" t="n">
-        <v>0.997999966144562</v>
+        <v>0.998000144958496</v>
       </c>
       <c r="H310" t="n">
         <v>1067470</v>
@@ -9388,7 +9388,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G311" t="n">
-        <v>0.980567753314972</v>
+        <v>0.980567991733551</v>
       </c>
       <c r="H311" t="n">
         <v>653693</v>
@@ -9417,7 +9417,7 @@
         <v>1.35399997234344</v>
       </c>
       <c r="G312" t="n">
-        <v>0.983473062515259</v>
+        <v>0.983473122119904</v>
       </c>
       <c r="H312" t="n">
         <v>591511</v>
@@ -9446,7 +9446,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G313" t="n">
-        <v>0.974757134914398</v>
+        <v>0.974756896495819</v>
       </c>
       <c r="H313" t="n">
         <v>300846</v>
@@ -9475,7 +9475,7 @@
         <v>1.33200001716614</v>
       </c>
       <c r="G314" t="n">
-        <v>0.967493534088135</v>
+        <v>0.967493653297424</v>
       </c>
       <c r="H314" t="n">
         <v>736020</v>
@@ -9504,7 +9504,7 @@
         <v>1.35599994659424</v>
       </c>
       <c r="G315" t="n">
-        <v>0.984925806522369</v>
+        <v>0.984925985336304</v>
       </c>
       <c r="H315" t="n">
         <v>757620</v>
@@ -9562,7 +9562,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G317" t="n">
-        <v>1.06264495849609</v>
+        <v>1.06264507770538</v>
       </c>
       <c r="H317" t="n">
         <v>803280</v>
@@ -9591,7 +9591,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G318" t="n">
-        <v>1.10985732078552</v>
+        <v>1.10985743999481</v>
       </c>
       <c r="H318" t="n">
         <v>1345874</v>
@@ -9620,7 +9620,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G319" t="n">
-        <v>1.14762723445892</v>
+        <v>1.1476274728775</v>
       </c>
       <c r="H319" t="n">
         <v>936775</v>
@@ -9649,7 +9649,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G320" t="n">
-        <v>1.13310039043427</v>
+        <v>1.13310050964355</v>
       </c>
       <c r="H320" t="n">
         <v>632979</v>
@@ -9678,7 +9678,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G321" t="n">
-        <v>1.13310039043427</v>
+        <v>1.13310050964355</v>
       </c>
       <c r="H321" t="n">
         <v>987524</v>
@@ -9707,7 +9707,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G322" t="n">
-        <v>1.09315133094788</v>
+        <v>1.09315145015717</v>
       </c>
       <c r="H322" t="n">
         <v>613305</v>
@@ -9736,7 +9736,7 @@
         <v>1.5</v>
       </c>
       <c r="G323" t="n">
-        <v>1.089519739151</v>
+        <v>1.08951985836029</v>
       </c>
       <c r="H323" t="n">
         <v>739978</v>
@@ -9823,7 +9823,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G326" t="n">
-        <v>1.12583708763123</v>
+        <v>1.12583720684052</v>
       </c>
       <c r="H326" t="n">
         <v>394176</v>
@@ -9852,7 +9852,7 @@
         <v>1.54900002479553</v>
       </c>
       <c r="G327" t="n">
-        <v>1.12511074542999</v>
+        <v>1.1251106262207</v>
       </c>
       <c r="H327" t="n">
         <v>512927</v>
@@ -9881,7 +9881,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G328" t="n">
-        <v>1.19120812416077</v>
+        <v>1.19120824337006</v>
       </c>
       <c r="H328" t="n">
         <v>967480</v>
@@ -9910,7 +9910,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G329" t="n">
-        <v>1.19120812416077</v>
+        <v>1.19120824337006</v>
       </c>
       <c r="H329" t="n">
         <v>519840</v>
@@ -9968,7 +9968,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G331" t="n">
-        <v>1.14036405086517</v>
+        <v>1.14036393165588</v>
       </c>
       <c r="H331" t="n">
         <v>379908</v>
@@ -10113,7 +10113,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G336" t="n">
-        <v>1.15852248668671</v>
+        <v>1.15852272510529</v>
       </c>
       <c r="H336" t="n">
         <v>302729</v>
@@ -10316,7 +10316,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G343" t="n">
-        <v>1.2565792798996</v>
+        <v>1.25657951831818</v>
       </c>
       <c r="H343" t="n">
         <v>345767</v>
@@ -10461,7 +10461,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G348" t="n">
-        <v>1.34809911251068</v>
+        <v>1.3480988740921</v>
       </c>
       <c r="H348" t="n">
         <v>919141</v>
@@ -10490,7 +10490,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G349" t="n">
-        <v>1.36480510234833</v>
+        <v>1.36480498313904</v>
       </c>
       <c r="H349" t="n">
         <v>470458</v>
@@ -10577,7 +10577,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G352" t="n">
-        <v>1.30451822280884</v>
+        <v>1.30451834201813</v>
       </c>
       <c r="H352" t="n">
         <v>611218</v>
@@ -10664,7 +10664,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G355" t="n">
-        <v>1.34301471710205</v>
+        <v>1.34301459789276</v>
       </c>
       <c r="H355" t="n">
         <v>221232</v>
@@ -10693,7 +10693,7 @@
         <v>1.76900005340576</v>
       </c>
       <c r="G356" t="n">
-        <v>1.28490698337555</v>
+        <v>1.28490686416626</v>
       </c>
       <c r="H356" t="n">
         <v>2156239</v>
@@ -10722,7 +10722,7 @@
         <v>1.80299997329712</v>
       </c>
       <c r="G357" t="n">
-        <v>1.30960273742676</v>
+        <v>1.30960261821747</v>
       </c>
       <c r="H357" t="n">
         <v>1580811</v>
@@ -10780,7 +10780,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G359" t="n">
-        <v>1.3146870136261</v>
+        <v>1.31468713283539</v>
       </c>
       <c r="H359" t="n">
         <v>1080815</v>
@@ -10838,7 +10838,7 @@
         <v>1.73699998855591</v>
       </c>
       <c r="G361" t="n">
-        <v>1.26166391372681</v>
+        <v>1.26166367530823</v>
       </c>
       <c r="H361" t="n">
         <v>441570</v>
@@ -10896,7 +10896,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G363" t="n">
-        <v>1.28563320636749</v>
+        <v>1.28563332557678</v>
       </c>
       <c r="H363" t="n">
         <v>221410</v>
@@ -10925,7 +10925,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G364" t="n">
-        <v>1.3146870136261</v>
+        <v>1.31468713283539</v>
       </c>
       <c r="H364" t="n">
         <v>295469</v>
@@ -10954,7 +10954,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G365" t="n">
-        <v>1.31839048862457</v>
+        <v>1.31839025020599</v>
       </c>
       <c r="H365" t="n">
         <v>285600</v>
@@ -10983,7 +10983,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G366" t="n">
-        <v>1.30357694625854</v>
+        <v>1.30357706546783</v>
       </c>
       <c r="H366" t="n">
         <v>182524</v>
@@ -11012,7 +11012,7 @@
         <v>1.75</v>
       </c>
       <c r="G367" t="n">
-        <v>1.29617023468018</v>
+        <v>1.29617047309875</v>
       </c>
       <c r="H367" t="n">
         <v>180229</v>
@@ -11070,7 +11070,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G369" t="n">
-        <v>1.28135681152344</v>
+        <v>1.28135704994202</v>
       </c>
       <c r="H369" t="n">
         <v>355257</v>
@@ -11099,7 +11099,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G370" t="n">
-        <v>1.2369167804718</v>
+        <v>1.23691666126251</v>
       </c>
       <c r="H370" t="n">
         <v>358904</v>
@@ -11128,7 +11128,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G371" t="n">
-        <v>1.26654374599457</v>
+        <v>1.26654362678528</v>
       </c>
       <c r="H371" t="n">
         <v>222201</v>
@@ -11157,7 +11157,7 @@
         <v>1.69700002670288</v>
       </c>
       <c r="G372" t="n">
-        <v>1.25691485404968</v>
+        <v>1.25691497325897</v>
       </c>
       <c r="H372" t="n">
         <v>157969</v>
@@ -11186,7 +11186,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G373" t="n">
-        <v>1.25173032283783</v>
+        <v>1.25173044204712</v>
       </c>
       <c r="H373" t="n">
         <v>198211</v>
@@ -11244,7 +11244,7 @@
         <v>1.68900001049042</v>
       </c>
       <c r="G375" t="n">
-        <v>1.25098967552185</v>
+        <v>1.25098955631256</v>
       </c>
       <c r="H375" t="n">
         <v>735219</v>
@@ -11273,7 +11273,7 @@
         <v>1.67700004577637</v>
       </c>
       <c r="G376" t="n">
-        <v>1.24210155010223</v>
+        <v>1.24210143089294</v>
       </c>
       <c r="H376" t="n">
         <v>829594</v>
@@ -11331,7 +11331,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G378" t="n">
-        <v>1.27246904373169</v>
+        <v>1.27246880531311</v>
       </c>
       <c r="H378" t="n">
         <v>180531</v>
@@ -11360,7 +11360,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G379" t="n">
-        <v>1.27395033836365</v>
+        <v>1.27395045757294</v>
       </c>
       <c r="H379" t="n">
         <v>140530</v>
@@ -11418,7 +11418,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G381" t="n">
-        <v>1.24876749515533</v>
+        <v>1.24876737594604</v>
       </c>
       <c r="H381" t="n">
         <v>125611</v>
@@ -11476,7 +11476,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G383" t="n">
-        <v>1.22654747962952</v>
+        <v>1.22654759883881</v>
       </c>
       <c r="H383" t="n">
         <v>127086</v>
@@ -11563,7 +11563,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G386" t="n">
-        <v>1.23395431041718</v>
+        <v>1.23395419120789</v>
       </c>
       <c r="H386" t="n">
         <v>148586</v>
@@ -11592,7 +11592,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G387" t="n">
-        <v>1.22951030731201</v>
+        <v>1.22951018810272</v>
       </c>
       <c r="H387" t="n">
         <v>63386</v>
@@ -11650,7 +11650,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G389" t="n">
-        <v>1.19988334178925</v>
+        <v>1.19988346099854</v>
       </c>
       <c r="H389" t="n">
         <v>125686</v>
@@ -11679,7 +11679,7 @@
         <v>1.63900005817413</v>
       </c>
       <c r="G390" t="n">
-        <v>1.21395623683929</v>
+        <v>1.21395611763</v>
       </c>
       <c r="H390" t="n">
         <v>102718</v>
@@ -11708,7 +11708,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G391" t="n">
-        <v>1.21469664573669</v>
+        <v>1.21469688415527</v>
       </c>
       <c r="H391" t="n">
         <v>66489</v>
@@ -11737,7 +11737,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G392" t="n">
-        <v>1.21099352836609</v>
+        <v>1.2109934091568</v>
       </c>
       <c r="H392" t="n">
         <v>116054</v>
@@ -11766,7 +11766,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G393" t="n">
-        <v>1.19395804405212</v>
+        <v>1.19395816326141</v>
       </c>
       <c r="H393" t="n">
         <v>171215</v>
@@ -11824,7 +11824,7 @@
         <v>1.63100004196167</v>
       </c>
       <c r="G395" t="n">
-        <v>1.20803070068359</v>
+        <v>1.20803093910217</v>
       </c>
       <c r="H395" t="n">
         <v>66708</v>
@@ -11853,7 +11853,7 @@
         <v>1.61899995803833</v>
       </c>
       <c r="G396" t="n">
-        <v>1.19914281368256</v>
+        <v>1.19914269447327</v>
       </c>
       <c r="H396" t="n">
         <v>75072</v>
@@ -11998,7 +11998,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G401" t="n">
-        <v>1.19840216636658</v>
+        <v>1.19840204715729</v>
       </c>
       <c r="H401" t="n">
         <v>56997</v>
@@ -12027,7 +12027,7 @@
         <v>1.60699999332428</v>
       </c>
       <c r="G402" t="n">
-        <v>1.19025480747223</v>
+        <v>1.19025468826294</v>
       </c>
       <c r="H402" t="n">
         <v>76761</v>
@@ -12056,7 +12056,7 @@
         <v>1.61699998378754</v>
       </c>
       <c r="G403" t="n">
-        <v>1.19766139984131</v>
+        <v>1.19766163825989</v>
       </c>
       <c r="H403" t="n">
         <v>126871</v>
@@ -12114,7 +12114,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G405" t="n">
-        <v>1.17025649547577</v>
+        <v>1.17025673389435</v>
       </c>
       <c r="H405" t="n">
         <v>151908</v>
@@ -12172,7 +12172,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G407" t="n">
-        <v>1.19988334178925</v>
+        <v>1.19988346099854</v>
       </c>
       <c r="H407" t="n">
         <v>242007</v>
@@ -12201,7 +12201,7 @@
         <v>1.63199996948242</v>
       </c>
       <c r="G408" t="n">
-        <v>1.20877146720886</v>
+        <v>1.20877134799957</v>
       </c>
       <c r="H408" t="n">
         <v>61617</v>
@@ -12259,7 +12259,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G410" t="n">
-        <v>1.19988334178925</v>
+        <v>1.19988346099854</v>
       </c>
       <c r="H410" t="n">
         <v>51777</v>
@@ -12317,7 +12317,7 @@
         <v>1.61600005626678</v>
       </c>
       <c r="G412" t="n">
-        <v>1.19692087173462</v>
+        <v>1.19692075252533</v>
       </c>
       <c r="H412" t="n">
         <v>242274</v>
@@ -12462,7 +12462,7 @@
         <v>1.54799997806549</v>
       </c>
       <c r="G417" t="n">
-        <v>1.14655530452728</v>
+        <v>1.14655542373657</v>
       </c>
       <c r="H417" t="n">
         <v>87938</v>
@@ -12491,7 +12491,7 @@
         <v>1.54700005054474</v>
       </c>
       <c r="G418" t="n">
-        <v>1.1458146572113</v>
+        <v>1.14581477642059</v>
       </c>
       <c r="H418" t="n">
         <v>88744</v>
@@ -12520,7 +12520,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G419" t="n">
-        <v>1.12433528900146</v>
+        <v>1.12433516979218</v>
       </c>
       <c r="H419" t="n">
         <v>134923</v>
@@ -12549,7 +12549,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G420" t="n">
-        <v>1.12211310863495</v>
+        <v>1.12211334705353</v>
       </c>
       <c r="H420" t="n">
         <v>89838</v>
@@ -12607,7 +12607,7 @@
         <v>1.5110000371933</v>
       </c>
       <c r="G422" t="n">
-        <v>1.11915051937103</v>
+        <v>1.11915063858032</v>
       </c>
       <c r="H422" t="n">
         <v>88478</v>
@@ -12636,7 +12636,7 @@
         <v>1.51699995994568</v>
       </c>
       <c r="G423" t="n">
-        <v>1.1235945224762</v>
+        <v>1.12359464168549</v>
       </c>
       <c r="H423" t="n">
         <v>39959</v>
@@ -12723,7 +12723,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G426" t="n">
-        <v>1.15544331073761</v>
+        <v>1.15544319152832</v>
       </c>
       <c r="H426" t="n">
         <v>163474</v>
@@ -12752,7 +12752,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G427" t="n">
-        <v>1.14803659915924</v>
+        <v>1.14803671836853</v>
       </c>
       <c r="H427" t="n">
         <v>125203</v>
@@ -12781,7 +12781,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G428" t="n">
-        <v>1.11840987205505</v>
+        <v>1.11840975284576</v>
       </c>
       <c r="H428" t="n">
         <v>267021</v>
@@ -12839,7 +12839,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G430" t="n">
-        <v>1.25469291210175</v>
+        <v>1.25469303131104</v>
       </c>
       <c r="H430" t="n">
         <v>830558</v>
@@ -12897,7 +12897,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G432" t="n">
-        <v>1.25173032283783</v>
+        <v>1.25173044204712</v>
       </c>
       <c r="H432" t="n">
         <v>328481</v>
@@ -12955,7 +12955,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G434" t="n">
-        <v>1.26654374599457</v>
+        <v>1.26654362678528</v>
       </c>
       <c r="H434" t="n">
         <v>177999</v>
@@ -13013,7 +13013,7 @@
         <v>1.77400004863739</v>
       </c>
       <c r="G436" t="n">
-        <v>1.3139466047287</v>
+        <v>1.31394636631012</v>
       </c>
       <c r="H436" t="n">
         <v>504769</v>
@@ -13071,7 +13071,7 @@
         <v>1.75800001621246</v>
       </c>
       <c r="G438" t="n">
-        <v>1.30209577083588</v>
+        <v>1.30209589004517</v>
       </c>
       <c r="H438" t="n">
         <v>345662</v>
@@ -13100,7 +13100,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G439" t="n">
-        <v>1.35172045230865</v>
+        <v>1.35172057151794</v>
       </c>
       <c r="H439" t="n">
         <v>473821</v>
@@ -13129,7 +13129,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G440" t="n">
-        <v>1.37468123435974</v>
+        <v>1.37468111515045</v>
       </c>
       <c r="H440" t="n">
         <v>592749</v>
@@ -13187,7 +13187,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G442" t="n">
-        <v>1.3924572467804</v>
+        <v>1.39245736598969</v>
       </c>
       <c r="H442" t="n">
         <v>306642</v>
@@ -13245,7 +13245,7 @@
         <v>1.91700005531311</v>
       </c>
       <c r="G444" t="n">
-        <v>1.41986215114594</v>
+        <v>1.41986203193665</v>
       </c>
       <c r="H444" t="n">
         <v>631289</v>
@@ -13274,7 +13274,7 @@
         <v>1.99899995326996</v>
       </c>
       <c r="G445" t="n">
-        <v>1.48059701919556</v>
+        <v>1.48059689998627</v>
       </c>
       <c r="H445" t="n">
         <v>926424</v>
@@ -13303,7 +13303,7 @@
         <v>2</v>
       </c>
       <c r="G446" t="n">
-        <v>1.48133766651154</v>
+        <v>1.48133754730225</v>
       </c>
       <c r="H446" t="n">
         <v>748564</v>
@@ -13390,7 +13390,7 @@
         <v>2.0220000743866</v>
       </c>
       <c r="G449" t="n">
-        <v>1.49763238430023</v>
+        <v>1.49763226509094</v>
       </c>
       <c r="H449" t="n">
         <v>357142</v>
@@ -13419,7 +13419,7 @@
         <v>2</v>
       </c>
       <c r="G450" t="n">
-        <v>1.48133766651154</v>
+        <v>1.48133754730225</v>
       </c>
       <c r="H450" t="n">
         <v>216633</v>
@@ -13448,7 +13448,7 @@
         <v>2</v>
       </c>
       <c r="G451" t="n">
-        <v>1.48133766651154</v>
+        <v>1.48133754730225</v>
       </c>
       <c r="H451" t="n">
         <v>350466</v>
@@ -13477,7 +13477,7 @@
         <v>1.98800003528595</v>
       </c>
       <c r="G452" t="n">
-        <v>1.47244954109192</v>
+        <v>1.47244966030121</v>
       </c>
       <c r="H452" t="n">
         <v>148471</v>
@@ -13506,7 +13506,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G453" t="n">
-        <v>1.44430422782898</v>
+        <v>1.44430410861969</v>
       </c>
       <c r="H453" t="n">
         <v>206879</v>
@@ -13535,7 +13535,7 @@
         <v>1.90400004386902</v>
       </c>
       <c r="G454" t="n">
-        <v>1.41023349761963</v>
+        <v>1.41023325920105</v>
       </c>
       <c r="H454" t="n">
         <v>454896</v>
@@ -13564,7 +13564,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G455" t="n">
-        <v>1.3924572467804</v>
+        <v>1.39245736598969</v>
       </c>
       <c r="H455" t="n">
         <v>217444</v>
@@ -13593,7 +13593,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G456" t="n">
-        <v>1.39690148830414</v>
+        <v>1.39690136909485</v>
       </c>
       <c r="H456" t="n">
         <v>147872</v>
@@ -13622,7 +13622,7 @@
         <v>1.89900004863739</v>
       </c>
       <c r="G457" t="n">
-        <v>1.40653014183044</v>
+        <v>1.40653026103973</v>
       </c>
       <c r="H457" t="n">
         <v>107319</v>
@@ -13651,7 +13651,7 @@
         <v>1.88300001621246</v>
       </c>
       <c r="G458" t="n">
-        <v>1.3946795463562</v>
+        <v>1.39467942714691</v>
       </c>
       <c r="H458" t="n">
         <v>145865</v>
@@ -13680,7 +13680,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G459" t="n">
-        <v>1.4339348077774</v>
+        <v>1.43393468856812</v>
       </c>
       <c r="H459" t="n">
         <v>253296</v>
@@ -13709,7 +13709,7 @@
         <v>1.91600000858307</v>
       </c>
       <c r="G460" t="n">
-        <v>1.41912150382996</v>
+        <v>1.41912138462067</v>
       </c>
       <c r="H460" t="n">
         <v>190838</v>
@@ -13738,7 +13738,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G461" t="n">
-        <v>1.40060460567474</v>
+        <v>1.40060472488403</v>
       </c>
       <c r="H461" t="n">
         <v>168607</v>
@@ -13796,7 +13796,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G463" t="n">
-        <v>1.41319608688354</v>
+        <v>1.41319620609283</v>
       </c>
       <c r="H463" t="n">
         <v>474841</v>
@@ -13825,7 +13825,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G464" t="n">
-        <v>1.39986407756805</v>
+        <v>1.39986395835876</v>
       </c>
       <c r="H464" t="n">
         <v>165446</v>
@@ -13883,7 +13883,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G466" t="n">
-        <v>1.39986407756805</v>
+        <v>1.39986395835876</v>
       </c>
       <c r="H466" t="n">
         <v>159279</v>
@@ -13912,7 +13912,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G467" t="n">
-        <v>1.42208397388458</v>
+        <v>1.42208409309387</v>
       </c>
       <c r="H467" t="n">
         <v>80534</v>
@@ -13941,7 +13941,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G468" t="n">
-        <v>1.38505053520203</v>
+        <v>1.38505065441132</v>
       </c>
       <c r="H468" t="n">
         <v>279706</v>
@@ -13999,7 +13999,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G470" t="n">
-        <v>1.37171840667725</v>
+        <v>1.37171864509583</v>
       </c>
       <c r="H470" t="n">
         <v>72557</v>
@@ -14028,7 +14028,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G471" t="n">
-        <v>1.3924572467804</v>
+        <v>1.39245736598969</v>
       </c>
       <c r="H471" t="n">
         <v>68488</v>
@@ -14057,7 +14057,7 @@
         <v>1.87300002574921</v>
       </c>
       <c r="G472" t="n">
-        <v>1.38727247714996</v>
+        <v>1.38727259635925</v>
       </c>
       <c r="H472" t="n">
         <v>77585</v>
@@ -14086,7 +14086,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G473" t="n">
-        <v>1.36579322814941</v>
+        <v>1.3657933473587</v>
       </c>
       <c r="H473" t="n">
         <v>49621</v>
@@ -14115,7 +14115,7 @@
         <v>1.84700000286102</v>
       </c>
       <c r="G474" t="n">
-        <v>1.36801517009735</v>
+        <v>1.36801540851593</v>
       </c>
       <c r="H474" t="n">
         <v>127644</v>
@@ -14144,7 +14144,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G475" t="n">
-        <v>1.35172045230865</v>
+        <v>1.35172057151794</v>
       </c>
       <c r="H475" t="n">
         <v>190264</v>
@@ -14173,7 +14173,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G476" t="n">
-        <v>1.31987190246582</v>
+        <v>1.31987166404724</v>
       </c>
       <c r="H476" t="n">
         <v>255331</v>
@@ -14289,7 +14289,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G480" t="n">
-        <v>1.11840987205505</v>
+        <v>1.11840975284576</v>
       </c>
       <c r="H480" t="n">
         <v>286838</v>
@@ -14434,7 +14434,7 @@
         <v>1.53299999237061</v>
       </c>
       <c r="G485" t="n">
-        <v>1.13544523715973</v>
+        <v>1.13544511795044</v>
       </c>
       <c r="H485" t="n">
         <v>157705</v>
@@ -14463,7 +14463,7 @@
         <v>1.48300004005432</v>
       </c>
       <c r="G486" t="n">
-        <v>1.09841191768646</v>
+        <v>1.09841179847717</v>
       </c>
       <c r="H486" t="n">
         <v>345908</v>
@@ -14492,7 +14492,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G487" t="n">
-        <v>1.10507774353027</v>
+        <v>1.10507786273956</v>
       </c>
       <c r="H487" t="n">
         <v>78110</v>
@@ -14579,7 +14579,7 @@
         <v>1.4190000295639</v>
       </c>
       <c r="G490" t="n">
-        <v>1.05100905895233</v>
+        <v>1.05100882053375</v>
       </c>
       <c r="H490" t="n">
         <v>208632</v>
@@ -14608,7 +14608,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G491" t="n">
-        <v>1.01767885684967</v>
+        <v>1.01767897605896</v>
       </c>
       <c r="H491" t="n">
         <v>429766</v>
@@ -14637,7 +14637,7 @@
         <v>1.43400001525879</v>
       </c>
       <c r="G492" t="n">
-        <v>1.06211912631989</v>
+        <v>1.0621190071106</v>
       </c>
       <c r="H492" t="n">
         <v>350676</v>
@@ -14753,7 +14753,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G496" t="n">
-        <v>1.00138425827026</v>
+        <v>1.00138413906097</v>
       </c>
       <c r="H496" t="n">
         <v>237509</v>
@@ -14782,7 +14782,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G497" t="n">
-        <v>1.03693616390228</v>
+        <v>1.03693628311157</v>
       </c>
       <c r="H497" t="n">
         <v>193642</v>
@@ -14811,7 +14811,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G498" t="n">
-        <v>1.01323485374451</v>
+        <v>1.0132349729538</v>
       </c>
       <c r="H498" t="n">
         <v>542627</v>
@@ -14840,7 +14840,7 @@
         <v>1.42900002002716</v>
       </c>
       <c r="G499" t="n">
-        <v>1.0584157705307</v>
+        <v>1.05841565132141</v>
       </c>
       <c r="H499" t="n">
         <v>494787</v>
@@ -14869,7 +14869,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G500" t="n">
-        <v>1.03693616390228</v>
+        <v>1.03693628311157</v>
       </c>
       <c r="H500" t="n">
         <v>326303</v>
@@ -14898,7 +14898,7 @@
         <v>1.4190000295639</v>
       </c>
       <c r="G501" t="n">
-        <v>1.05100905895233</v>
+        <v>1.05100882053375</v>
       </c>
       <c r="H501" t="n">
         <v>228697</v>
@@ -14927,7 +14927,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G502" t="n">
-        <v>1.05915629863739</v>
+        <v>1.05915641784668</v>
       </c>
       <c r="H502" t="n">
         <v>152475</v>
@@ -15043,7 +15043,7 @@
         <v>1.42400002479553</v>
       </c>
       <c r="G506" t="n">
-        <v>1.05471241474152</v>
+        <v>1.05471229553223</v>
       </c>
       <c r="H506" t="n">
         <v>145102</v>
@@ -15072,7 +15072,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G507" t="n">
-        <v>1.06360042095184</v>
+        <v>1.06360054016113</v>
       </c>
       <c r="H507" t="n">
         <v>260274</v>
@@ -15130,7 +15130,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G509" t="n">
-        <v>1.09026443958282</v>
+        <v>1.09026455879211</v>
       </c>
       <c r="H509" t="n">
         <v>259873</v>
@@ -15217,7 +15217,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G512" t="n">
-        <v>1.07767307758331</v>
+        <v>1.0776731967926</v>
       </c>
       <c r="H512" t="n">
         <v>103857</v>
@@ -15246,7 +15246,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G513" t="n">
-        <v>1.06360042095184</v>
+        <v>1.06360054016113</v>
       </c>
       <c r="H513" t="n">
         <v>89671</v>
@@ -15275,7 +15275,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G514" t="n">
-        <v>1.08137631416321</v>
+        <v>1.0813764333725</v>
       </c>
       <c r="H514" t="n">
         <v>321644</v>
@@ -15333,7 +15333,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G516" t="n">
-        <v>1.21469664573669</v>
+        <v>1.21469688415527</v>
       </c>
       <c r="H516" t="n">
         <v>1111957</v>
@@ -15420,7 +15420,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G519" t="n">
-        <v>1.17914485931396</v>
+        <v>1.17914462089539</v>
       </c>
       <c r="H519" t="n">
         <v>319407</v>
@@ -15449,7 +15449,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G520" t="n">
-        <v>1.17173802852631</v>
+        <v>1.1717381477356</v>
       </c>
       <c r="H520" t="n">
         <v>379135</v>
@@ -15507,7 +15507,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G522" t="n">
-        <v>1.16581273078918</v>
+        <v>1.1658126115799</v>
       </c>
       <c r="H522" t="n">
         <v>189565</v>
@@ -15623,7 +15623,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G526" t="n">
-        <v>1.14359283447266</v>
+        <v>1.14359271526337</v>
       </c>
       <c r="H526" t="n">
         <v>289761</v>
@@ -15652,7 +15652,7 @@
         <v>1.60399997234344</v>
       </c>
       <c r="G527" t="n">
-        <v>1.18803286552429</v>
+        <v>1.188032746315</v>
       </c>
       <c r="H527" t="n">
         <v>499779</v>
@@ -15710,7 +15710,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G529" t="n">
-        <v>1.16581273078918</v>
+        <v>1.1658126115799</v>
       </c>
       <c r="H529" t="n">
         <v>161258</v>
@@ -15855,7 +15855,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G534" t="n">
-        <v>1.15544331073761</v>
+        <v>1.15544319152832</v>
       </c>
       <c r="H534" t="n">
         <v>377481</v>
@@ -15884,7 +15884,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G535" t="n">
-        <v>1.11840987205505</v>
+        <v>1.11840975284576</v>
       </c>
       <c r="H535" t="n">
         <v>307287</v>
@@ -15913,7 +15913,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G536" t="n">
-        <v>1.08137631416321</v>
+        <v>1.0813764333725</v>
       </c>
       <c r="H536" t="n">
         <v>466085</v>
@@ -15971,7 +15971,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G538" t="n">
-        <v>1.08582055568695</v>
+        <v>1.08582031726837</v>
       </c>
       <c r="H538" t="n">
         <v>247826</v>
@@ -16000,7 +16000,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G539" t="n">
-        <v>1.06360042095184</v>
+        <v>1.06360054016113</v>
       </c>
       <c r="H539" t="n">
         <v>240255</v>
@@ -16087,7 +16087,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G542" t="n">
-        <v>0.985089540481567</v>
+        <v>0.985089480876923</v>
       </c>
       <c r="H542" t="n">
         <v>253269</v>
@@ -16116,7 +16116,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G543" t="n">
-        <v>1.03545498847961</v>
+        <v>1.0354551076889</v>
       </c>
       <c r="H543" t="n">
         <v>243714</v>
@@ -16145,7 +16145,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G544" t="n">
-        <v>1.01767885684967</v>
+        <v>1.01767897605896</v>
       </c>
       <c r="H544" t="n">
         <v>279153</v>
@@ -16261,7 +16261,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G548" t="n">
-        <v>0.995458841323853</v>
+        <v>0.995458900928497</v>
       </c>
       <c r="H548" t="n">
         <v>91495</v>
@@ -16290,7 +16290,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G549" t="n">
-        <v>0.991014897823334</v>
+        <v>0.991014778614044</v>
       </c>
       <c r="H549" t="n">
         <v>153168</v>
@@ -16319,7 +16319,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G550" t="n">
-        <v>0.993977665901184</v>
+        <v>0.993977606296539</v>
       </c>
       <c r="H550" t="n">
         <v>88534</v>
@@ -16348,7 +16348,7 @@
         <v>1.31599998474121</v>
       </c>
       <c r="G551" t="n">
-        <v>0.974720120429993</v>
+        <v>0.974720239639282</v>
       </c>
       <c r="H551" t="n">
         <v>122190</v>
@@ -16377,7 +16377,7 @@
         <v>1.28400003910065</v>
       </c>
       <c r="G552" t="n">
-        <v>0.951018750667572</v>
+        <v>0.951018810272217</v>
       </c>
       <c r="H552" t="n">
         <v>161965</v>
@@ -16406,7 +16406,7 @@
         <v>1.28799998760223</v>
       </c>
       <c r="G553" t="n">
-        <v>0.953981459140778</v>
+        <v>0.953981399536133</v>
       </c>
       <c r="H553" t="n">
         <v>256788</v>
@@ -16464,7 +16464,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G555" t="n">
-        <v>0.918429255485535</v>
+        <v>0.918429315090179</v>
       </c>
       <c r="H555" t="n">
         <v>331395</v>
@@ -16493,7 +16493,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G556" t="n">
-        <v>0.927317380905151</v>
+        <v>0.927317321300507</v>
       </c>
       <c r="H556" t="n">
         <v>109070</v>
@@ -16522,7 +16522,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G557" t="n">
-        <v>0.998421609401703</v>
+        <v>0.998421549797058</v>
       </c>
       <c r="H557" t="n">
         <v>394951</v>
@@ -16551,7 +16551,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G558" t="n">
-        <v>1.03101098537445</v>
+        <v>1.03101086616516</v>
       </c>
       <c r="H558" t="n">
         <v>460975</v>
@@ -16580,7 +16580,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G559" t="n">
-        <v>0.995458841323853</v>
+        <v>0.995458900928497</v>
       </c>
       <c r="H559" t="n">
         <v>368448</v>
@@ -16667,7 +16667,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G562" t="n">
-        <v>1.03545498847961</v>
+        <v>1.0354551076889</v>
       </c>
       <c r="H562" t="n">
         <v>214612</v>
@@ -16783,7 +16783,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G566" t="n">
-        <v>1.07841396331787</v>
+        <v>1.07841372489929</v>
       </c>
       <c r="H566" t="n">
         <v>356526</v>
@@ -16812,7 +16812,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G567" t="n">
-        <v>1.08137631416321</v>
+        <v>1.0813764333725</v>
       </c>
       <c r="H567" t="n">
         <v>314530</v>
@@ -16841,7 +16841,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G568" t="n">
-        <v>1.05323100090027</v>
+        <v>1.05323112010956</v>
       </c>
       <c r="H568" t="n">
         <v>199266</v>
@@ -16870,7 +16870,7 @@
         <v>1.40400004386902</v>
       </c>
       <c r="G569" t="n">
-        <v>1.03989887237549</v>
+        <v>1.03989899158478</v>
       </c>
       <c r="H569" t="n">
         <v>275024</v>
@@ -16957,7 +16957,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G572" t="n">
-        <v>1.05323100090027</v>
+        <v>1.05323112010956</v>
       </c>
       <c r="H572" t="n">
         <v>50990</v>
@@ -16986,7 +16986,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G573" t="n">
-        <v>1.0295295715332</v>
+        <v>1.02952969074249</v>
       </c>
       <c r="H573" t="n">
         <v>243674</v>
@@ -17015,7 +17015,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G574" t="n">
-        <v>1.03101098537445</v>
+        <v>1.03101086616516</v>
       </c>
       <c r="H574" t="n">
         <v>55307</v>
@@ -17044,7 +17044,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G575" t="n">
-        <v>1.00730967521667</v>
+        <v>1.00730955600739</v>
       </c>
       <c r="H575" t="n">
         <v>384329</v>
@@ -17073,7 +17073,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G576" t="n">
-        <v>0.991014897823334</v>
+        <v>0.991014778614044</v>
       </c>
       <c r="H576" t="n">
         <v>90878</v>
@@ -17102,7 +17102,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G577" t="n">
-        <v>1.01767885684967</v>
+        <v>1.01767897605896</v>
       </c>
       <c r="H577" t="n">
         <v>94201</v>
@@ -17160,7 +17160,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G579" t="n">
-        <v>0.999902904033661</v>
+        <v>0.999902963638306</v>
       </c>
       <c r="H579" t="n">
         <v>57479</v>
@@ -17189,7 +17189,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G580" t="n">
-        <v>1.01323485374451</v>
+        <v>1.0132349729538</v>
       </c>
       <c r="H580" t="n">
         <v>103511</v>
@@ -17218,7 +17218,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G581" t="n">
-        <v>0.992496132850647</v>
+        <v>0.992496192455292</v>
       </c>
       <c r="H581" t="n">
         <v>67595</v>
@@ -17247,7 +17247,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G582" t="n">
-        <v>0.998421609401703</v>
+        <v>0.998421549797058</v>
       </c>
       <c r="H582" t="n">
         <v>189058</v>
@@ -17276,7 +17276,7 @@
         <v>1.34599995613098</v>
       </c>
       <c r="G583" t="n">
-        <v>0.996940135955811</v>
+        <v>0.996940195560455</v>
       </c>
       <c r="H583" t="n">
         <v>62609</v>
@@ -17305,7 +17305,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G584" t="n">
-        <v>1.0295295715332</v>
+        <v>1.02952969074249</v>
       </c>
       <c r="H584" t="n">
         <v>150463</v>
@@ -17334,7 +17334,7 @@
         <v>1.38399994373322</v>
       </c>
       <c r="G585" t="n">
-        <v>1.02508533000946</v>
+        <v>1.02508568763733</v>
       </c>
       <c r="H585" t="n">
         <v>172760</v>
@@ -17363,7 +17363,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G586" t="n">
-        <v>1.0295295715332</v>
+        <v>1.02952969074249</v>
       </c>
       <c r="H586" t="n">
         <v>142117</v>
@@ -17392,7 +17392,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G587" t="n">
-        <v>1.04730546474457</v>
+        <v>1.04730570316315</v>
       </c>
       <c r="H587" t="n">
         <v>202091</v>
@@ -17421,7 +17421,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G588" t="n">
-        <v>1.0295295715332</v>
+        <v>1.02952969074249</v>
       </c>
       <c r="H588" t="n">
         <v>201402</v>
@@ -17450,7 +17450,7 @@
         <v>1.38399994373322</v>
       </c>
       <c r="G589" t="n">
-        <v>1.02508533000946</v>
+        <v>1.02508568763733</v>
       </c>
       <c r="H589" t="n">
         <v>88040</v>
@@ -17479,7 +17479,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G590" t="n">
-        <v>1.01767885684967</v>
+        <v>1.01767897605896</v>
       </c>
       <c r="H590" t="n">
         <v>64032</v>
@@ -17508,7 +17508,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G591" t="n">
-        <v>1.01323485374451</v>
+        <v>1.0132349729538</v>
       </c>
       <c r="H591" t="n">
         <v>52459</v>
@@ -17566,7 +17566,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G593" t="n">
-        <v>1.00138425827026</v>
+        <v>1.00138413906097</v>
       </c>
       <c r="H593" t="n">
         <v>94119</v>
@@ -17595,7 +17595,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G594" t="n">
-        <v>0.992496132850647</v>
+        <v>0.992496192455292</v>
       </c>
       <c r="H594" t="n">
         <v>111965</v>
@@ -17653,7 +17653,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G596" t="n">
-        <v>1.08582055568695</v>
+        <v>1.08582031726837</v>
       </c>
       <c r="H596" t="n">
         <v>702023</v>
@@ -17711,7 +17711,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G598" t="n">
-        <v>1.13174188137054</v>
+        <v>1.13174176216125</v>
       </c>
       <c r="H598" t="n">
         <v>625352</v>
@@ -17769,7 +17769,7 @@
         <v>1.49399995803833</v>
       </c>
       <c r="G600" t="n">
-        <v>1.10655927658081</v>
+        <v>1.10655915737152</v>
       </c>
       <c r="H600" t="n">
         <v>271776</v>
@@ -17798,7 +17798,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G601" t="n">
-        <v>1.07841396331787</v>
+        <v>1.07841372489929</v>
       </c>
       <c r="H601" t="n">
         <v>237313</v>
@@ -17827,7 +17827,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G602" t="n">
-        <v>1.08730185031891</v>
+        <v>1.0873019695282</v>
       </c>
       <c r="H602" t="n">
         <v>74707</v>
@@ -17856,7 +17856,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G603" t="n">
-        <v>1.06360042095184</v>
+        <v>1.06360054016113</v>
       </c>
       <c r="H603" t="n">
         <v>145863</v>
@@ -17943,7 +17943,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G606" t="n">
-        <v>0.999902904033661</v>
+        <v>0.999902963638306</v>
       </c>
       <c r="H606" t="n">
         <v>183501</v>
@@ -17972,7 +17972,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G607" t="n">
-        <v>0.985089540481567</v>
+        <v>0.985089480876923</v>
       </c>
       <c r="H607" t="n">
         <v>194897</v>
@@ -18001,7 +18001,7 @@
         <v>1.317999958992</v>
       </c>
       <c r="G608" t="n">
-        <v>0.976201474666595</v>
+        <v>0.97620153427124</v>
       </c>
       <c r="H608" t="n">
         <v>235633</v>
@@ -18030,7 +18030,7 @@
         <v>1.2940000295639</v>
       </c>
       <c r="G609" t="n">
-        <v>0.958425343036652</v>
+        <v>0.958425402641296</v>
       </c>
       <c r="H609" t="n">
         <v>244117</v>
@@ -18088,7 +18088,7 @@
         <v>1.30799996852875</v>
       </c>
       <c r="G611" t="n">
-        <v>0.968794643878937</v>
+        <v>0.968794822692871</v>
       </c>
       <c r="H611" t="n">
         <v>224659</v>
@@ -18117,7 +18117,7 @@
         <v>1.30200004577637</v>
       </c>
       <c r="G612" t="n">
-        <v>0.964350700378418</v>
+        <v>0.964350819587708</v>
       </c>
       <c r="H612" t="n">
         <v>143499</v>
@@ -18233,7 +18233,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G616" t="n">
-        <v>0.915466547012329</v>
+        <v>0.915466606616974</v>
       </c>
       <c r="H616" t="n">
         <v>208101</v>
@@ -18262,7 +18262,7 @@
         <v>1.30200004577637</v>
       </c>
       <c r="G617" t="n">
-        <v>0.964350700378418</v>
+        <v>0.964350819587708</v>
       </c>
       <c r="H617" t="n">
         <v>306651</v>
@@ -18320,7 +18320,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G619" t="n">
-        <v>0.946844577789307</v>
+        <v>0.946844816207886</v>
       </c>
       <c r="H619" t="n">
         <v>114902</v>
@@ -18407,7 +18407,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G622" t="n">
-        <v>0.916399538516998</v>
+        <v>0.916399657726288</v>
       </c>
       <c r="H622" t="n">
         <v>213604</v>
@@ -18436,7 +18436,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G623" t="n">
-        <v>0.939233422279358</v>
+        <v>0.939233541488647</v>
       </c>
       <c r="H623" t="n">
         <v>100877</v>
@@ -18465,7 +18465,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G624" t="n">
-        <v>0.94227808713913</v>
+        <v>0.94227796792984</v>
       </c>
       <c r="H624" t="n">
         <v>28130</v>
@@ -18523,7 +18523,7 @@
         <v>1.30200004577637</v>
       </c>
       <c r="G626" t="n">
-        <v>0.990990340709686</v>
+        <v>0.990990400314331</v>
       </c>
       <c r="H626" t="n">
         <v>670447</v>
@@ -18581,7 +18581,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G628" t="n">
-        <v>1.07471454143524</v>
+        <v>1.07471442222595</v>
       </c>
       <c r="H628" t="n">
         <v>714660</v>
@@ -18697,7 +18697,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G632" t="n">
-        <v>0.997079193592072</v>
+        <v>0.997079253196716</v>
       </c>
       <c r="H632" t="n">
         <v>323021</v>
@@ -18755,7 +18755,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G634" t="n">
-        <v>0.933144330978394</v>
+        <v>0.933144390583038</v>
       </c>
       <c r="H634" t="n">
         <v>242929</v>
@@ -18813,7 +18813,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G636" t="n">
-        <v>0.919444024562836</v>
+        <v>0.919444143772125</v>
       </c>
       <c r="H636" t="n">
         <v>222960</v>
@@ -18842,7 +18842,7 @@
         <v>1.21800005435944</v>
       </c>
       <c r="G637" t="n">
-        <v>0.927055478096008</v>
+        <v>0.927055537700653</v>
       </c>
       <c r="H637" t="n">
         <v>125708</v>
@@ -18871,7 +18871,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G638" t="n">
-        <v>0.910310626029968</v>
+        <v>0.910310506820679</v>
       </c>
       <c r="H638" t="n">
         <v>223478</v>
@@ -18900,7 +18900,7 @@
         <v>1.21800005435944</v>
       </c>
       <c r="G639" t="n">
-        <v>0.927055478096008</v>
+        <v>0.927055537700653</v>
       </c>
       <c r="H639" t="n">
         <v>131985</v>
@@ -18958,7 +18958,7 @@
         <v>1.21800005435944</v>
       </c>
       <c r="G641" t="n">
-        <v>0.927055478096008</v>
+        <v>0.927055537700653</v>
       </c>
       <c r="H641" t="n">
         <v>86979</v>
@@ -19016,7 +19016,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G643" t="n">
-        <v>0.910310626029968</v>
+        <v>0.910310506820679</v>
       </c>
       <c r="H643" t="n">
         <v>129224</v>
@@ -19045,7 +19045,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G644" t="n">
-        <v>0.89813244342804</v>
+        <v>0.898132562637329</v>
       </c>
       <c r="H644" t="n">
         <v>301410</v>
@@ -19074,7 +19074,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G645" t="n">
-        <v>0.89813244342804</v>
+        <v>0.898132562637329</v>
       </c>
       <c r="H645" t="n">
         <v>214574</v>
@@ -19103,7 +19103,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G646" t="n">
-        <v>0.90878838300705</v>
+        <v>0.908788204193115</v>
       </c>
       <c r="H646" t="n">
         <v>100571</v>
@@ -19132,7 +19132,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G647" t="n">
-        <v>0.910310626029968</v>
+        <v>0.910310506820679</v>
       </c>
       <c r="H647" t="n">
         <v>184949</v>
@@ -19161,7 +19161,7 @@
         <v>1.22200000286102</v>
       </c>
       <c r="G648" t="n">
-        <v>0.930099964141846</v>
+        <v>0.93010002374649</v>
       </c>
       <c r="H648" t="n">
         <v>173812</v>
@@ -19190,7 +19190,7 @@
         <v>1.21399998664856</v>
       </c>
       <c r="G649" t="n">
-        <v>0.924010872840881</v>
+        <v>0.924010932445526</v>
       </c>
       <c r="H649" t="n">
         <v>222863</v>
@@ -19277,7 +19277,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G652" t="n">
-        <v>0.920966327190399</v>
+        <v>0.920966386795044</v>
       </c>
       <c r="H652" t="n">
         <v>93462</v>
@@ -19306,7 +19306,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G653" t="n">
-        <v>0.90878838300705</v>
+        <v>0.908788204193115</v>
       </c>
       <c r="H653" t="n">
         <v>295295</v>
@@ -19335,7 +19335,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G654" t="n">
-        <v>0.901176989078522</v>
+        <v>0.901177048683167</v>
       </c>
       <c r="H654" t="n">
         <v>162630</v>
@@ -19422,7 +19422,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G657" t="n">
-        <v>0.89661031961441</v>
+        <v>0.896610140800476</v>
       </c>
       <c r="H657" t="n">
         <v>127352</v>
@@ -19451,7 +19451,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G658" t="n">
-        <v>0.904221594333649</v>
+        <v>0.904221415519714</v>
       </c>
       <c r="H658" t="n">
         <v>246355</v>
@@ -19480,7 +19480,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G659" t="n">
-        <v>0.919444024562836</v>
+        <v>0.919444143772125</v>
       </c>
       <c r="H659" t="n">
         <v>136583</v>
@@ -19625,7 +19625,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G664" t="n">
-        <v>0.904221594333649</v>
+        <v>0.904221415519714</v>
       </c>
       <c r="H664" t="n">
         <v>100757</v>
@@ -19654,7 +19654,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G665" t="n">
-        <v>0.905743777751923</v>
+        <v>0.905743956565857</v>
       </c>
       <c r="H665" t="n">
         <v>203730</v>
@@ -19683,7 +19683,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G666" t="n">
-        <v>0.966634035110474</v>
+        <v>0.966634213924408</v>
       </c>
       <c r="H666" t="n">
         <v>2042203</v>
@@ -19712,7 +19712,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G667" t="n">
-        <v>0.983379065990448</v>
+        <v>0.983379125595093</v>
       </c>
       <c r="H667" t="n">
         <v>956672</v>
@@ -19741,7 +19741,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G668" t="n">
-        <v>0.968156337738037</v>
+        <v>0.968156456947327</v>
       </c>
       <c r="H668" t="n">
         <v>315683</v>
@@ -19770,7 +19770,7 @@
         <v>1.24800002574921</v>
       </c>
       <c r="G669" t="n">
-        <v>0.949889361858368</v>
+        <v>0.949889183044434</v>
       </c>
       <c r="H669" t="n">
         <v>249154</v>
@@ -19799,7 +19799,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G670" t="n">
-        <v>0.939233422279358</v>
+        <v>0.939233541488647</v>
       </c>
       <c r="H670" t="n">
         <v>218460</v>
@@ -19828,7 +19828,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G671" t="n">
-        <v>0.916399538516998</v>
+        <v>0.916399657726288</v>
       </c>
       <c r="H671" t="n">
         <v>186165</v>
@@ -19915,7 +19915,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G674" t="n">
-        <v>0.957500696182251</v>
+        <v>0.957500576972961</v>
       </c>
       <c r="H674" t="n">
         <v>132620</v>
@@ -19973,7 +19973,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G676" t="n">
-        <v>0.952933788299561</v>
+        <v>0.952933669090271</v>
       </c>
       <c r="H676" t="n">
         <v>87659</v>
@@ -20002,7 +20002,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G677" t="n">
-        <v>0.966634035110474</v>
+        <v>0.966634213924408</v>
       </c>
       <c r="H677" t="n">
         <v>142892</v>
@@ -20031,7 +20031,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G678" t="n">
-        <v>0.957500696182251</v>
+        <v>0.957500576972961</v>
       </c>
       <c r="H678" t="n">
         <v>252858</v>
@@ -20089,7 +20089,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G680" t="n">
-        <v>0.939233422279358</v>
+        <v>0.939233541488647</v>
       </c>
       <c r="H680" t="n">
         <v>81183</v>
@@ -20118,7 +20118,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G681" t="n">
-        <v>0.928577661514282</v>
+        <v>0.928577721118927</v>
       </c>
       <c r="H681" t="n">
         <v>261082</v>
@@ -20147,7 +20147,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G682" t="n">
-        <v>0.928577661514282</v>
+        <v>0.928577721118927</v>
       </c>
       <c r="H682" t="n">
         <v>178101</v>
@@ -20263,7 +20263,7 @@
         <v>1.28400003910065</v>
       </c>
       <c r="G686" t="n">
-        <v>0.977289855480194</v>
+        <v>0.977289974689484</v>
       </c>
       <c r="H686" t="n">
         <v>148253</v>
@@ -20292,7 +20292,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G687" t="n">
-        <v>1.00469052791595</v>
+        <v>1.00469064712524</v>
       </c>
       <c r="H687" t="n">
         <v>573421</v>
@@ -20379,7 +20379,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G690" t="n">
-        <v>0.997079193592072</v>
+        <v>0.997079253196716</v>
       </c>
       <c r="H690" t="n">
         <v>103065</v>
@@ -20408,7 +20408,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G691" t="n">
-        <v>1.02752447128296</v>
+        <v>1.02752459049225</v>
       </c>
       <c r="H691" t="n">
         <v>344766</v>
@@ -20437,7 +20437,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G692" t="n">
-        <v>1.02295768260956</v>
+        <v>1.02295780181885</v>
       </c>
       <c r="H692" t="n">
         <v>474201</v>
@@ -20524,7 +20524,7 @@
         <v>1.40600001811981</v>
       </c>
       <c r="G695" t="n">
-        <v>1.07014775276184</v>
+        <v>1.07014763355255</v>
       </c>
       <c r="H695" t="n">
         <v>295235</v>
@@ -20553,7 +20553,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G696" t="n">
-        <v>1.06405878067017</v>
+        <v>1.06405889987946</v>
       </c>
       <c r="H696" t="n">
         <v>213634</v>
@@ -20582,7 +20582,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G697" t="n">
-        <v>1.06253635883331</v>
+        <v>1.0625364780426</v>
       </c>
       <c r="H697" t="n">
         <v>199103</v>
@@ -20640,7 +20640,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G699" t="n">
-        <v>1.06253635883331</v>
+        <v>1.0625364780426</v>
       </c>
       <c r="H699" t="n">
         <v>88064</v>
@@ -20698,7 +20698,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G701" t="n">
-        <v>1.01686859130859</v>
+        <v>1.01686871051788</v>
       </c>
       <c r="H701" t="n">
         <v>390229</v>
@@ -20785,7 +20785,7 @@
         <v>1.31400001049042</v>
       </c>
       <c r="G704" t="n">
-        <v>1.00012373924255</v>
+        <v>1.00012385845184</v>
       </c>
       <c r="H704" t="n">
         <v>49596</v>
@@ -20814,7 +20814,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G705" t="n">
-        <v>0.99251252412796</v>
+        <v>0.99251264333725</v>
       </c>
       <c r="H705" t="n">
         <v>190928</v>
@@ -20843,7 +20843,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G706" t="n">
-        <v>0.978812158107758</v>
+        <v>0.978812336921692</v>
       </c>
       <c r="H706" t="n">
         <v>197598</v>
@@ -20872,7 +20872,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G707" t="n">
-        <v>0.954455971717834</v>
+        <v>0.954456090927124</v>
       </c>
       <c r="H707" t="n">
         <v>199663</v>
@@ -20901,7 +20901,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G708" t="n">
-        <v>0.957500696182251</v>
+        <v>0.957500576972961</v>
       </c>
       <c r="H708" t="n">
         <v>187830</v>
@@ -20930,7 +20930,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G709" t="n">
-        <v>0.946844577789307</v>
+        <v>0.946844816207886</v>
       </c>
       <c r="H709" t="n">
         <v>87432</v>
@@ -20959,7 +20959,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G710" t="n">
-        <v>0.933144330978394</v>
+        <v>0.933144390583038</v>
       </c>
       <c r="H710" t="n">
         <v>206624</v>
@@ -20988,7 +20988,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G711" t="n">
-        <v>0.94227808713913</v>
+        <v>0.94227796792984</v>
       </c>
       <c r="H711" t="n">
         <v>196843</v>
@@ -21017,7 +21017,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G712" t="n">
-        <v>0.962067365646362</v>
+        <v>0.962067306041718</v>
       </c>
       <c r="H712" t="n">
         <v>138417</v>
@@ -21046,7 +21046,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G713" t="n">
-        <v>0.986423552036285</v>
+        <v>0.986423492431641</v>
       </c>
       <c r="H713" t="n">
         <v>79917</v>
@@ -21075,7 +21075,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G714" t="n">
-        <v>0.945322513580322</v>
+        <v>0.945322453975677</v>
       </c>
       <c r="H714" t="n">
         <v>114687</v>
@@ -21104,7 +21104,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G715" t="n">
-        <v>0.933144330978394</v>
+        <v>0.933144390583038</v>
       </c>
       <c r="H715" t="n">
         <v>201288</v>
@@ -21133,7 +21133,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G716" t="n">
-        <v>0.905743777751923</v>
+        <v>0.905743956565857</v>
       </c>
       <c r="H716" t="n">
         <v>348854</v>
@@ -21162,7 +21162,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G717" t="n">
-        <v>0.916399538516998</v>
+        <v>0.916399657726288</v>
       </c>
       <c r="H717" t="n">
         <v>217570</v>
@@ -21191,7 +21191,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G718" t="n">
-        <v>0.910310626029968</v>
+        <v>0.910310506820679</v>
       </c>
       <c r="H718" t="n">
         <v>119081</v>
@@ -21220,7 +21220,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G719" t="n">
-        <v>0.895088076591492</v>
+        <v>0.895087897777557</v>
       </c>
       <c r="H719" t="n">
         <v>114368</v>
@@ -21249,7 +21249,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G720" t="n">
-        <v>0.916399538516998</v>
+        <v>0.916399657726288</v>
       </c>
       <c r="H720" t="n">
         <v>256170</v>
@@ -21278,7 +21278,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G721" t="n">
-        <v>0.892043471336365</v>
+        <v>0.89204353094101</v>
       </c>
       <c r="H721" t="n">
         <v>159400</v>
@@ -21365,7 +21365,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G724" t="n">
-        <v>0.93162214756012</v>
+        <v>0.931622087955475</v>
       </c>
       <c r="H724" t="n">
         <v>83535</v>
@@ -21423,7 +21423,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G726" t="n">
-        <v>0.968156337738037</v>
+        <v>0.968156456947327</v>
       </c>
       <c r="H726" t="n">
         <v>102600</v>
@@ -21452,7 +21452,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G727" t="n">
-        <v>1.01991307735443</v>
+        <v>1.01991319656372</v>
       </c>
       <c r="H727" t="n">
         <v>568817</v>
@@ -21510,7 +21510,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G729" t="n">
-        <v>1.03513562679291</v>
+        <v>1.0351357460022</v>
       </c>
       <c r="H729" t="n">
         <v>179288</v>
@@ -21539,7 +21539,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G730" t="n">
-        <v>1.02752447128296</v>
+        <v>1.02752459049225</v>
       </c>
       <c r="H730" t="n">
         <v>238333</v>
@@ -21568,7 +21568,7 @@
         <v>1.34599995613098</v>
       </c>
       <c r="G731" t="n">
-        <v>1.02447998523712</v>
+        <v>1.02447986602783</v>
       </c>
       <c r="H731" t="n">
         <v>81887</v>
@@ -21626,7 +21626,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G733" t="n">
-        <v>1.03361368179321</v>
+        <v>1.03361344337463</v>
       </c>
       <c r="H733" t="n">
         <v>82427</v>
@@ -21800,7 +21800,7 @@
         <v>1.27600002288818</v>
       </c>
       <c r="G739" t="n">
-        <v>0.971201002597809</v>
+        <v>0.971200942993164</v>
       </c>
       <c r="H739" t="n">
         <v>239885</v>
@@ -21829,7 +21829,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G740" t="n">
-        <v>0.966634035110474</v>
+        <v>0.966634213924408</v>
       </c>
       <c r="H740" t="n">
         <v>100315</v>
@@ -21858,7 +21858,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G741" t="n">
-        <v>0.969678699970245</v>
+        <v>0.969678580760956</v>
       </c>
       <c r="H741" t="n">
         <v>84261</v>
@@ -21916,7 +21916,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G743" t="n">
-        <v>1.02904665470123</v>
+        <v>1.02904653549194</v>
       </c>
       <c r="H743" t="n">
         <v>123805</v>
@@ -21945,7 +21945,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G744" t="n">
-        <v>1.02904665470123</v>
+        <v>1.02904653549194</v>
       </c>
       <c r="H744" t="n">
         <v>19343</v>
@@ -21974,7 +21974,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G745" t="n">
-        <v>1.01991307735443</v>
+        <v>1.01991319656372</v>
       </c>
       <c r="H745" t="n">
         <v>115070</v>
@@ -22061,7 +22061,7 @@
         <v>1.30599999427795</v>
       </c>
       <c r="G748" t="n">
-        <v>0.994034826755524</v>
+        <v>0.994034647941589</v>
       </c>
       <c r="H748" t="n">
         <v>73371</v>
@@ -22090,7 +22090,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G749" t="n">
-        <v>0.969678699970245</v>
+        <v>0.969678580760956</v>
       </c>
       <c r="H749" t="n">
         <v>121821</v>
@@ -22119,7 +22119,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G750" t="n">
-        <v>0.954455971717834</v>
+        <v>0.954456090927124</v>
       </c>
       <c r="H750" t="n">
         <v>114490</v>
@@ -22264,7 +22264,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G755" t="n">
-        <v>0.948367118835449</v>
+        <v>0.94836699962616</v>
       </c>
       <c r="H755" t="n">
         <v>119423</v>
@@ -22293,7 +22293,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G756" t="n">
-        <v>0.948367118835449</v>
+        <v>0.94836699962616</v>
       </c>
       <c r="H756" t="n">
         <v>95259</v>
@@ -22322,7 +22322,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G757" t="n">
-        <v>0.965112030506134</v>
+        <v>0.965111911296844</v>
       </c>
       <c r="H757" t="n">
         <v>142192</v>
@@ -22380,7 +22380,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G759" t="n">
-        <v>0.966634035110474</v>
+        <v>0.966634213924408</v>
       </c>
       <c r="H759" t="n">
         <v>51502</v>
@@ -22409,7 +22409,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G760" t="n">
-        <v>0.969678699970245</v>
+        <v>0.969678580760956</v>
       </c>
       <c r="H760" t="n">
         <v>70204</v>
@@ -22438,7 +22438,7 @@
         <v>1.27799999713898</v>
       </c>
       <c r="G761" t="n">
-        <v>0.972723305225372</v>
+        <v>0.972723066806793</v>
       </c>
       <c r="H761" t="n">
         <v>106940</v>
@@ -22467,7 +22467,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G762" t="n">
-        <v>0.962067365646362</v>
+        <v>0.962067306041718</v>
       </c>
       <c r="H762" t="n">
         <v>59014</v>
@@ -22496,7 +22496,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G763" t="n">
-        <v>0.952933788299561</v>
+        <v>0.952933669090271</v>
       </c>
       <c r="H763" t="n">
         <v>123708</v>
@@ -22525,7 +22525,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G764" t="n">
-        <v>0.966634035110474</v>
+        <v>0.966634213924408</v>
       </c>
       <c r="H764" t="n">
         <v>135628</v>
@@ -22554,7 +22554,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G765" t="n">
-        <v>0.997079193592072</v>
+        <v>0.997079253196716</v>
       </c>
       <c r="H765" t="n">
         <v>128414</v>
@@ -22583,7 +22583,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G766" t="n">
-        <v>0.99251252412796</v>
+        <v>0.99251264333725</v>
       </c>
       <c r="H766" t="n">
         <v>347964</v>
@@ -22612,7 +22612,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G767" t="n">
-        <v>1.01686859130859</v>
+        <v>1.01686871051788</v>
       </c>
       <c r="H767" t="n">
         <v>245847</v>
@@ -22641,7 +22641,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G768" t="n">
-        <v>1.01077973842621</v>
+        <v>1.01077950000763</v>
       </c>
       <c r="H768" t="n">
         <v>228422</v>
@@ -22670,7 +22670,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G769" t="n">
-        <v>1.03361368179321</v>
+        <v>1.03361344337463</v>
       </c>
       <c r="H769" t="n">
         <v>130775</v>
@@ -22699,7 +22699,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G770" t="n">
-        <v>1.02295768260956</v>
+        <v>1.02295780181885</v>
       </c>
       <c r="H770" t="n">
         <v>112013</v>
@@ -22902,7 +22902,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G777" t="n">
-        <v>1.02752447128296</v>
+        <v>1.02752459049225</v>
       </c>
       <c r="H777" t="n">
         <v>237215</v>
@@ -22931,7 +22931,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G778" t="n">
-        <v>1.00469052791595</v>
+        <v>1.00469064712524</v>
       </c>
       <c r="H778" t="n">
         <v>233419</v>
@@ -22960,7 +22960,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G779" t="n">
-        <v>1.01991307735443</v>
+        <v>1.01991319656372</v>
       </c>
       <c r="H779" t="n">
         <v>99341</v>
@@ -22989,7 +22989,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G780" t="n">
-        <v>1.01991307735443</v>
+        <v>1.01991319656372</v>
       </c>
       <c r="H780" t="n">
         <v>57502</v>
@@ -23018,7 +23018,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G781" t="n">
-        <v>1.04731392860413</v>
+        <v>1.04731380939484</v>
       </c>
       <c r="H781" t="n">
         <v>185925</v>
@@ -23076,7 +23076,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G783" t="n">
-        <v>1.03361368179321</v>
+        <v>1.03361344337463</v>
       </c>
       <c r="H783" t="n">
         <v>56537</v>
@@ -23134,7 +23134,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G785" t="n">
-        <v>0.997079193592072</v>
+        <v>0.997079253196716</v>
       </c>
       <c r="H785" t="n">
         <v>393727</v>
@@ -23163,7 +23163,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G786" t="n">
-        <v>0.978812158107758</v>
+        <v>0.978812336921692</v>
       </c>
       <c r="H786" t="n">
         <v>130599</v>
@@ -23192,7 +23192,7 @@
         <v>1.27799999713898</v>
       </c>
       <c r="G787" t="n">
-        <v>0.972723305225372</v>
+        <v>0.972723066806793</v>
       </c>
       <c r="H787" t="n">
         <v>158003</v>
@@ -23221,7 +23221,7 @@
         <v>1.28199994564056</v>
       </c>
       <c r="G788" t="n">
-        <v>0.975767552852631</v>
+        <v>0.975767731666565</v>
       </c>
       <c r="H788" t="n">
         <v>165379</v>
@@ -23250,7 +23250,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G789" t="n">
-        <v>0.99251252412796</v>
+        <v>0.99251264333725</v>
       </c>
       <c r="H789" t="n">
         <v>149415</v>
@@ -23279,7 +23279,7 @@
         <v>1.28799998760223</v>
       </c>
       <c r="G790" t="n">
-        <v>0.980334579944611</v>
+        <v>0.980334341526031</v>
       </c>
       <c r="H790" t="n">
         <v>73244</v>
@@ -23337,7 +23337,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G792" t="n">
-        <v>0.974245250225067</v>
+        <v>0.974245488643646</v>
       </c>
       <c r="H792" t="n">
         <v>54402</v>
@@ -23366,7 +23366,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G793" t="n">
-        <v>0.983379065990448</v>
+        <v>0.983379125595093</v>
       </c>
       <c r="H793" t="n">
         <v>47634</v>
@@ -23395,7 +23395,7 @@
         <v>1.31200003623962</v>
       </c>
       <c r="G794" t="n">
-        <v>0.998601615428925</v>
+        <v>0.99860155582428</v>
       </c>
       <c r="H794" t="n">
         <v>32572</v>
@@ -23424,7 +23424,7 @@
         <v>1.30599999427795</v>
       </c>
       <c r="G795" t="n">
-        <v>0.994034826755524</v>
+        <v>0.994034647941589</v>
       </c>
       <c r="H795" t="n">
         <v>33337</v>
@@ -23453,7 +23453,7 @@
         <v>1.30599999427795</v>
       </c>
       <c r="G796" t="n">
-        <v>0.994034826755524</v>
+        <v>0.994034647941589</v>
       </c>
       <c r="H796" t="n">
         <v>53655</v>
@@ -23482,7 +23482,7 @@
         <v>1.30200004577637</v>
       </c>
       <c r="G797" t="n">
-        <v>0.990990340709686</v>
+        <v>0.990990400314331</v>
       </c>
       <c r="H797" t="n">
         <v>46038</v>
@@ -23511,7 +23511,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G798" t="n">
-        <v>0.989467918872833</v>
+        <v>0.989467859268188</v>
       </c>
       <c r="H798" t="n">
         <v>32262</v>
@@ -23540,7 +23540,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G799" t="n">
-        <v>0.981856644153595</v>
+        <v>0.98185658454895</v>
       </c>
       <c r="H799" t="n">
         <v>60962</v>
@@ -23627,7 +23627,7 @@
         <v>1.31200003623962</v>
       </c>
       <c r="G802" t="n">
-        <v>0.998601615428925</v>
+        <v>0.99860155582428</v>
       </c>
       <c r="H802" t="n">
         <v>81645</v>
@@ -23685,7 +23685,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G804" t="n">
-        <v>1.01839101314545</v>
+        <v>1.01839089393616</v>
       </c>
       <c r="H804" t="n">
         <v>55624</v>
@@ -23714,7 +23714,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G805" t="n">
-        <v>0.997079193592072</v>
+        <v>0.997079253196716</v>
       </c>
       <c r="H805" t="n">
         <v>50423</v>
@@ -23743,7 +23743,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G806" t="n">
-        <v>0.989467918872833</v>
+        <v>0.989467859268188</v>
       </c>
       <c r="H806" t="n">
         <v>64909</v>
@@ -23801,7 +23801,7 @@
         <v>1.33399999141693</v>
       </c>
       <c r="G808" t="n">
-        <v>1.01534628868103</v>
+        <v>1.01534652709961</v>
       </c>
       <c r="H808" t="n">
         <v>45551</v>
@@ -23859,7 +23859,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G810" t="n">
-        <v>0.99251252412796</v>
+        <v>0.99251264333725</v>
       </c>
       <c r="H810" t="n">
         <v>20233</v>
@@ -23888,7 +23888,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G811" t="n">
-        <v>0.986423552036285</v>
+        <v>0.986423492431641</v>
       </c>
       <c r="H811" t="n">
         <v>45296</v>
@@ -23917,7 +23917,7 @@
         <v>1.32400000095367</v>
       </c>
       <c r="G812" t="n">
-        <v>1.00773501396179</v>
+        <v>1.00773525238037</v>
       </c>
       <c r="H812" t="n">
         <v>36801</v>
@@ -23946,7 +23946,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G813" t="n">
-        <v>0.997079193592072</v>
+        <v>0.997079253196716</v>
       </c>
       <c r="H813" t="n">
         <v>53063</v>
@@ -23975,7 +23975,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G814" t="n">
-        <v>0.99251252412796</v>
+        <v>0.99251264333725</v>
       </c>
       <c r="H814" t="n">
         <v>67114</v>
@@ -24033,7 +24033,7 @@
         <v>1.30599999427795</v>
       </c>
       <c r="G816" t="n">
-        <v>0.994034826755524</v>
+        <v>0.994034647941589</v>
       </c>
       <c r="H816" t="n">
         <v>148678</v>
@@ -24062,7 +24062,7 @@
         <v>1.30599999427795</v>
       </c>
       <c r="G817" t="n">
-        <v>0.994034826755524</v>
+        <v>0.994034647941589</v>
       </c>
       <c r="H817" t="n">
         <v>79341</v>
@@ -24091,7 +24091,7 @@
         <v>1.32400000095367</v>
       </c>
       <c r="G818" t="n">
-        <v>1.00773501396179</v>
+        <v>1.00773525238037</v>
       </c>
       <c r="H818" t="n">
         <v>68280</v>
@@ -24149,7 +24149,7 @@
         <v>1.33399999141693</v>
       </c>
       <c r="G820" t="n">
-        <v>1.01534628868103</v>
+        <v>1.01534652709961</v>
       </c>
       <c r="H820" t="n">
         <v>153365</v>
@@ -24207,7 +24207,7 @@
         <v>1.30200004577637</v>
       </c>
       <c r="G822" t="n">
-        <v>0.990990340709686</v>
+        <v>0.990990400314331</v>
       </c>
       <c r="H822" t="n">
         <v>31883</v>
@@ -24236,7 +24236,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G823" t="n">
-        <v>0.989467918872833</v>
+        <v>0.989467859268188</v>
       </c>
       <c r="H823" t="n">
         <v>49842</v>
@@ -24265,7 +24265,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G824" t="n">
-        <v>0.989467918872833</v>
+        <v>0.989467859268188</v>
       </c>
       <c r="H824" t="n">
         <v>33780</v>
@@ -24294,7 +24294,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G825" t="n">
-        <v>0.989467918872833</v>
+        <v>0.989467859268188</v>
       </c>
       <c r="H825" t="n">
         <v>17713</v>
@@ -24323,7 +24323,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G826" t="n">
-        <v>0.986423552036285</v>
+        <v>0.986423492431641</v>
       </c>
       <c r="H826" t="n">
         <v>26160</v>
@@ -24352,7 +24352,7 @@
         <v>1.30599999427795</v>
       </c>
       <c r="G827" t="n">
-        <v>0.994034826755524</v>
+        <v>0.994034647941589</v>
       </c>
       <c r="H827" t="n">
         <v>38312</v>
@@ -24381,7 +24381,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G828" t="n">
-        <v>0.99251252412796</v>
+        <v>0.99251264333725</v>
       </c>
       <c r="H828" t="n">
         <v>54698</v>
@@ -24439,7 +24439,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G830" t="n">
-        <v>0.989467918872833</v>
+        <v>0.989467859268188</v>
       </c>
       <c r="H830" t="n">
         <v>110940</v>
@@ -24468,7 +24468,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G831" t="n">
-        <v>1.02600228786469</v>
+        <v>1.0260021686554</v>
       </c>
       <c r="H831" t="n">
         <v>268422</v>
@@ -24642,7 +24642,7 @@
         <v>1.40600001811981</v>
       </c>
       <c r="G837" t="n">
-        <v>1.07014775276184</v>
+        <v>1.07014763355255</v>
       </c>
       <c r="H837" t="n">
         <v>287078</v>
@@ -24700,7 +24700,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G839" t="n">
-        <v>1.05949187278748</v>
+        <v>1.05949175357819</v>
       </c>
       <c r="H839" t="n">
         <v>159165</v>
@@ -24787,7 +24787,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G842" t="n">
-        <v>1.05492520332336</v>
+        <v>1.05492532253265</v>
       </c>
       <c r="H842" t="n">
         <v>120282</v>
@@ -24845,7 +24845,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G844" t="n">
-        <v>1.04731392860413</v>
+        <v>1.04731380939484</v>
       </c>
       <c r="H844" t="n">
         <v>86271</v>
@@ -24903,7 +24903,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G846" t="n">
-        <v>1.03513562679291</v>
+        <v>1.0351357460022</v>
       </c>
       <c r="H846" t="n">
         <v>88142</v>
@@ -25048,7 +25048,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G851" t="n">
-        <v>1.01991307735443</v>
+        <v>1.01991319656372</v>
       </c>
       <c r="H851" t="n">
         <v>48493</v>
@@ -25077,7 +25077,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G852" t="n">
-        <v>0.974245250225067</v>
+        <v>0.974245488643646</v>
       </c>
       <c r="H852" t="n">
         <v>165749</v>
@@ -25106,7 +25106,7 @@
         <v>1.28199994564056</v>
       </c>
       <c r="G853" t="n">
-        <v>0.975767552852631</v>
+        <v>0.975767731666565</v>
       </c>
       <c r="H853" t="n">
         <v>45679</v>
@@ -25135,7 +25135,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G854" t="n">
-        <v>0.983379065990448</v>
+        <v>0.983379125595093</v>
       </c>
       <c r="H854" t="n">
         <v>113515</v>
@@ -25164,7 +25164,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G855" t="n">
-        <v>0.983379065990448</v>
+        <v>0.983379125595093</v>
       </c>
       <c r="H855" t="n">
         <v>48174</v>
@@ -25222,7 +25222,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G857" t="n">
-        <v>0.90878838300705</v>
+        <v>0.908788204193115</v>
       </c>
       <c r="H857" t="n">
         <v>253484</v>
@@ -25251,7 +25251,7 @@
         <v>1.13399994373322</v>
       </c>
       <c r="G858" t="n">
-        <v>0.863120436668396</v>
+        <v>0.863120496273041</v>
       </c>
       <c r="H858" t="n">
         <v>639100</v>
@@ -25280,7 +25280,7 @@
         <v>1.10199999809265</v>
       </c>
       <c r="G859" t="n">
-        <v>0.838764429092407</v>
+        <v>0.838764369487762</v>
       </c>
       <c r="H859" t="n">
         <v>379453</v>
@@ -25309,7 +25309,7 @@
         <v>1.13399994373322</v>
       </c>
       <c r="G860" t="n">
-        <v>0.863120436668396</v>
+        <v>0.863120496273041</v>
       </c>
       <c r="H860" t="n">
         <v>224329</v>
@@ -25367,7 +25367,7 @@
         <v>1.13199996948242</v>
       </c>
       <c r="G862" t="n">
-        <v>0.861598312854767</v>
+        <v>0.861598372459412</v>
       </c>
       <c r="H862" t="n">
         <v>120720</v>
@@ -25396,7 +25396,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G863" t="n">
-        <v>0.85246479511261</v>
+        <v>0.852464735507965</v>
       </c>
       <c r="H863" t="n">
         <v>141152</v>
@@ -25454,7 +25454,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G865" t="n">
-        <v>0.864642798900604</v>
+        <v>0.864642858505249</v>
       </c>
       <c r="H865" t="n">
         <v>177323</v>
@@ -25483,7 +25483,7 @@
         <v>1.12399995326996</v>
       </c>
       <c r="G866" t="n">
-        <v>0.855509161949158</v>
+        <v>0.855509102344513</v>
       </c>
       <c r="H866" t="n">
         <v>100876</v>
@@ -25512,7 +25512,7 @@
         <v>1.09599995613098</v>
       </c>
       <c r="G867" t="n">
-        <v>0.834197640419006</v>
+        <v>0.834197700023651</v>
       </c>
       <c r="H867" t="n">
         <v>166699</v>
@@ -25599,7 +25599,7 @@
         <v>1.04799997806549</v>
       </c>
       <c r="G870" t="n">
-        <v>0.831494510173798</v>
+        <v>0.831494569778442</v>
       </c>
       <c r="H870" t="n">
         <v>103768</v>
@@ -25628,7 +25628,7 @@
         <v>1.06400001049042</v>
       </c>
       <c r="G871" t="n">
-        <v>0.84418910741806</v>
+        <v>0.844189286231995</v>
       </c>
       <c r="H871" t="n">
         <v>75832</v>
@@ -25657,7 +25657,7 @@
         <v>1.09200000762939</v>
       </c>
       <c r="G872" t="n">
-        <v>0.866404712200165</v>
+        <v>0.86640465259552</v>
       </c>
       <c r="H872" t="n">
         <v>36722</v>
@@ -25686,7 +25686,7 @@
         <v>1.07599997520447</v>
       </c>
       <c r="G873" t="n">
-        <v>0.853710055351257</v>
+        <v>0.853710114955902</v>
       </c>
       <c r="H873" t="n">
         <v>59888</v>
@@ -25715,7 +25715,7 @@
         <v>1.06200003623962</v>
       </c>
       <c r="G874" t="n">
-        <v>0.842602372169495</v>
+        <v>0.84260231256485</v>
       </c>
       <c r="H874" t="n">
         <v>66658</v>
@@ -25744,7 +25744,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G875" t="n">
-        <v>0.841015517711639</v>
+        <v>0.84101539850235</v>
       </c>
       <c r="H875" t="n">
         <v>31151</v>
@@ -25773,7 +25773,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G876" t="n">
-        <v>0.828320980072021</v>
+        <v>0.828321039676666</v>
       </c>
       <c r="H876" t="n">
         <v>164700</v>
@@ -25802,7 +25802,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G877" t="n">
-        <v>0.828320980072021</v>
+        <v>0.828321039676666</v>
       </c>
       <c r="H877" t="n">
         <v>57915</v>
@@ -25947,7 +25947,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G882" t="n">
-        <v>0.788650393486023</v>
+        <v>0.788650453090668</v>
       </c>
       <c r="H882" t="n">
         <v>158047</v>
@@ -25976,7 +25976,7 @@
         <v>0.985000014305115</v>
       </c>
       <c r="G883" t="n">
-        <v>0.781509637832642</v>
+        <v>0.781509757041931</v>
       </c>
       <c r="H883" t="n">
         <v>253459</v>
@@ -26034,7 +26034,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G885" t="n">
-        <v>0.796584486961365</v>
+        <v>0.79658454656601</v>
       </c>
       <c r="H885" t="n">
         <v>50741</v>
@@ -26092,7 +26092,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G887" t="n">
-        <v>0.777542650699615</v>
+        <v>0.77754271030426</v>
       </c>
       <c r="H887" t="n">
         <v>103580</v>
@@ -26150,7 +26150,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G889" t="n">
-        <v>0.785476684570312</v>
+        <v>0.785476744174957</v>
       </c>
       <c r="H889" t="n">
         <v>73867</v>
@@ -26179,7 +26179,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G890" t="n">
-        <v>0.783889889717102</v>
+        <v>0.783890008926392</v>
       </c>
       <c r="H890" t="n">
         <v>79937</v>
@@ -26208,7 +26208,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G891" t="n">
-        <v>0.785476684570312</v>
+        <v>0.785476744174957</v>
       </c>
       <c r="H891" t="n">
         <v>127800</v>
@@ -26237,7 +26237,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G892" t="n">
-        <v>0.801344990730286</v>
+        <v>0.801344931125641</v>
       </c>
       <c r="H892" t="n">
         <v>403016</v>
@@ -26324,7 +26324,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G895" t="n">
-        <v>0.773575663566589</v>
+        <v>0.773575603961945</v>
       </c>
       <c r="H895" t="n">
         <v>113425</v>
@@ -26353,7 +26353,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G896" t="n">
-        <v>0.772782146930695</v>
+        <v>0.772782206535339</v>
       </c>
       <c r="H896" t="n">
         <v>161572</v>
@@ -26411,7 +26411,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G898" t="n">
-        <v>0.764848113059998</v>
+        <v>0.764848053455353</v>
       </c>
       <c r="H898" t="n">
         <v>183970</v>
@@ -26440,7 +26440,7 @@
         <v>0.967000007629395</v>
       </c>
       <c r="G899" t="n">
-        <v>0.767228305339813</v>
+        <v>0.767228364944458</v>
       </c>
       <c r="H899" t="n">
         <v>75290</v>
@@ -26469,7 +26469,7 @@
         <v>0.971000015735626</v>
       </c>
       <c r="G900" t="n">
-        <v>0.770401954650879</v>
+        <v>0.770401895046234</v>
       </c>
       <c r="H900" t="n">
         <v>79675</v>
@@ -26614,7 +26614,7 @@
         <v>0.962999999523163</v>
       </c>
       <c r="G905" t="n">
-        <v>0.764054656028748</v>
+        <v>0.764054596424103</v>
       </c>
       <c r="H905" t="n">
         <v>64900</v>
@@ -26643,7 +26643,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G906" t="n">
-        <v>0.763261258602142</v>
+        <v>0.763261318206787</v>
       </c>
       <c r="H906" t="n">
         <v>37877</v>
@@ -26672,7 +26672,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G907" t="n">
-        <v>0.768021643161774</v>
+        <v>0.768021702766418</v>
       </c>
       <c r="H907" t="n">
         <v>34764</v>
@@ -26701,7 +26701,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G908" t="n">
-        <v>0.780716359615326</v>
+        <v>0.780716240406036</v>
       </c>
       <c r="H908" t="n">
         <v>97681</v>
@@ -26730,7 +26730,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G909" t="n">
-        <v>0.789443790912628</v>
+        <v>0.789443850517273</v>
       </c>
       <c r="H909" t="n">
         <v>108139</v>
@@ -26759,7 +26759,7 @@
         <v>1</v>
       </c>
       <c r="G910" t="n">
-        <v>0.793410897254944</v>
+        <v>0.793410837650299</v>
       </c>
       <c r="H910" t="n">
         <v>98352</v>
@@ -26788,7 +26788,7 @@
         <v>0.985000014305115</v>
       </c>
       <c r="G911" t="n">
-        <v>0.781509637832642</v>
+        <v>0.781509757041931</v>
       </c>
       <c r="H911" t="n">
         <v>54545</v>
@@ -26817,7 +26817,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G912" t="n">
-        <v>0.777542650699615</v>
+        <v>0.77754271030426</v>
       </c>
       <c r="H912" t="n">
         <v>63057</v>
@@ -26875,7 +26875,7 @@
         <v>0.944999992847443</v>
       </c>
       <c r="G914" t="n">
-        <v>0.74977320432663</v>
+        <v>0.749773323535919</v>
       </c>
       <c r="H914" t="n">
         <v>160552</v>
@@ -26991,7 +26991,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G918" t="n">
-        <v>0.664878249168396</v>
+        <v>0.664878368377686</v>
       </c>
       <c r="H918" t="n">
         <v>387079</v>
@@ -27020,7 +27020,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G919" t="n">
-        <v>0.669638812541962</v>
+        <v>0.669638752937317</v>
       </c>
       <c r="H919" t="n">
         <v>232045</v>
@@ -27078,7 +27078,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G921" t="n">
-        <v>0.656944155693054</v>
+        <v>0.656944274902344</v>
       </c>
       <c r="H921" t="n">
         <v>25922</v>
@@ -27107,7 +27107,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G922" t="n">
-        <v>0.650596857070923</v>
+        <v>0.650596916675568</v>
       </c>
       <c r="H922" t="n">
         <v>83450</v>
@@ -27165,7 +27165,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G924" t="n">
-        <v>0.647423267364502</v>
+        <v>0.647423207759857</v>
       </c>
       <c r="H924" t="n">
         <v>96346</v>
@@ -27194,7 +27194,7 @@
         <v>0.814999997615814</v>
       </c>
       <c r="G925" t="n">
-        <v>0.646629810333252</v>
+        <v>0.646629869937897</v>
       </c>
       <c r="H925" t="n">
         <v>241713</v>
@@ -27223,7 +27223,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G926" t="n">
-        <v>0.656944155693054</v>
+        <v>0.656944274902344</v>
       </c>
       <c r="H926" t="n">
         <v>61278</v>
@@ -27252,7 +27252,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G927" t="n">
-        <v>0.658530950546265</v>
+        <v>0.658531010150909</v>
       </c>
       <c r="H927" t="n">
         <v>98178</v>
@@ -27281,7 +27281,7 @@
         <v>0.861000001430511</v>
       </c>
       <c r="G928" t="n">
-        <v>0.68312680721283</v>
+        <v>0.683126747608185</v>
       </c>
       <c r="H928" t="n">
         <v>57209</v>
@@ -27339,7 +27339,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G930" t="n">
-        <v>0.672812342643738</v>
+        <v>0.672812402248383</v>
       </c>
       <c r="H930" t="n">
         <v>162189</v>
@@ -27426,7 +27426,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G933" t="n">
-        <v>0.656944155693054</v>
+        <v>0.656944274902344</v>
       </c>
       <c r="H933" t="n">
         <v>100640</v>
@@ -27600,7 +27600,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G939" t="n">
-        <v>0.68233335018158</v>
+        <v>0.682333409786224</v>
       </c>
       <c r="H939" t="n">
         <v>328275</v>
@@ -27687,7 +27687,7 @@
         <v>0.954999983310699</v>
       </c>
       <c r="G942" t="n">
-        <v>0.757707357406616</v>
+        <v>0.757707297801971</v>
       </c>
       <c r="H942" t="n">
         <v>429655</v>
@@ -27716,7 +27716,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G943" t="n">
-        <v>0.748979866504669</v>
+        <v>0.748979806900024</v>
       </c>
       <c r="H943" t="n">
         <v>400265</v>
@@ -27832,7 +27832,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G947" t="n">
-        <v>0.728351175785065</v>
+        <v>0.72835111618042</v>
       </c>
       <c r="H947" t="n">
         <v>83293</v>
@@ -27861,7 +27861,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G948" t="n">
-        <v>0.717243373394012</v>
+        <v>0.717243432998657</v>
       </c>
       <c r="H948" t="n">
         <v>191730</v>
@@ -28064,7 +28064,7 @@
         <v>0.852999985218048</v>
       </c>
       <c r="G955" t="n">
-        <v>0.676779448986053</v>
+        <v>0.676779508590698</v>
       </c>
       <c r="H955" t="n">
         <v>116687</v>
@@ -28180,7 +28180,7 @@
         <v>0.837000012397766</v>
       </c>
       <c r="G959" t="n">
-        <v>0.664084911346436</v>
+        <v>0.664084851741791</v>
       </c>
       <c r="H959" t="n">
         <v>17625</v>
@@ -28238,7 +28238,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G961" t="n">
-        <v>0.68233335018158</v>
+        <v>0.682333409786224</v>
       </c>
       <c r="H961" t="n">
         <v>113842</v>
@@ -28267,7 +28267,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G962" t="n">
-        <v>0.683920204639435</v>
+        <v>0.68392014503479</v>
       </c>
       <c r="H962" t="n">
         <v>114547</v>
@@ -28325,7 +28325,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G964" t="n">
-        <v>0.675986111164093</v>
+        <v>0.675986051559448</v>
       </c>
       <c r="H964" t="n">
         <v>126456</v>
@@ -28354,7 +28354,7 @@
         <v>0.852999985218048</v>
       </c>
       <c r="G965" t="n">
-        <v>0.676779448986053</v>
+        <v>0.676779508590698</v>
       </c>
       <c r="H965" t="n">
         <v>127885</v>
@@ -28441,7 +28441,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G968" t="n">
-        <v>0.672812342643738</v>
+        <v>0.672812402248383</v>
       </c>
       <c r="H968" t="n">
         <v>77294</v>
@@ -28615,7 +28615,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G974" t="n">
-        <v>0.669638812541962</v>
+        <v>0.669638752937317</v>
       </c>
       <c r="H974" t="n">
         <v>103164</v>
@@ -28644,7 +28644,7 @@
         <v>0.842999994754791</v>
       </c>
       <c r="G975" t="n">
-        <v>0.668845355510712</v>
+        <v>0.668845295906067</v>
       </c>
       <c r="H975" t="n">
         <v>34346</v>
@@ -28673,7 +28673,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G976" t="n">
-        <v>0.672812342643738</v>
+        <v>0.672812402248383</v>
       </c>
       <c r="H976" t="n">
         <v>169984</v>
@@ -28702,7 +28702,7 @@
         <v>0.852999985218048</v>
       </c>
       <c r="G977" t="n">
-        <v>0.676779448986053</v>
+        <v>0.676779508590698</v>
       </c>
       <c r="H977" t="n">
         <v>73828</v>
@@ -28760,7 +28760,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G979" t="n">
-        <v>0.741045713424683</v>
+        <v>0.741045653820038</v>
       </c>
       <c r="H979" t="n">
         <v>353968</v>
@@ -28847,7 +28847,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G982" t="n">
-        <v>0.720417082309723</v>
+        <v>0.720417022705078</v>
       </c>
       <c r="H982" t="n">
         <v>66773</v>
@@ -28876,7 +28876,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G983" t="n">
-        <v>0.745806157588959</v>
+        <v>0.745806217193604</v>
       </c>
       <c r="H983" t="n">
         <v>196678</v>
@@ -28963,7 +28963,7 @@
         <v>0.894999980926514</v>
       </c>
       <c r="G986" t="n">
-        <v>0.710102736949921</v>
+        <v>0.710102796554565</v>
       </c>
       <c r="H986" t="n">
         <v>535759</v>
@@ -29021,7 +29021,7 @@
         <v>0.861000001430511</v>
       </c>
       <c r="G988" t="n">
-        <v>0.68312680721283</v>
+        <v>0.683126747608185</v>
       </c>
       <c r="H988" t="n">
         <v>120380</v>
@@ -29050,7 +29050,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G989" t="n">
-        <v>0.68233335018158</v>
+        <v>0.682333409786224</v>
       </c>
       <c r="H989" t="n">
         <v>171445</v>
@@ -29137,7 +29137,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G992" t="n">
-        <v>0.68233335018158</v>
+        <v>0.682333409786224</v>
       </c>
       <c r="H992" t="n">
         <v>254052</v>
@@ -29166,7 +29166,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G993" t="n">
-        <v>0.686300337314606</v>
+        <v>0.686300456523895</v>
       </c>
       <c r="H993" t="n">
         <v>45175</v>
@@ -29253,7 +29253,7 @@
         <v>0.90200001001358</v>
       </c>
       <c r="G996" t="n">
-        <v>0.715656638145447</v>
+        <v>0.715656578540802</v>
       </c>
       <c r="H996" t="n">
         <v>212834</v>
@@ -29311,7 +29311,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G998" t="n">
-        <v>0.733111679553986</v>
+        <v>0.73311173915863</v>
       </c>
       <c r="H998" t="n">
         <v>243560</v>
@@ -29340,7 +29340,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G999" t="n">
-        <v>0.733111679553986</v>
+        <v>0.73311173915863</v>
       </c>
       <c r="H999" t="n">
         <v>170267</v>
@@ -29485,7 +29485,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G1004" t="n">
-        <v>0.740252315998077</v>
+        <v>0.740252375602722</v>
       </c>
       <c r="H1004" t="n">
         <v>136295</v>
@@ -29514,7 +29514,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G1005" t="n">
-        <v>0.731524765491486</v>
+        <v>0.73152482509613</v>
       </c>
       <c r="H1005" t="n">
         <v>49510</v>
@@ -29543,7 +29543,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G1006" t="n">
-        <v>0.734698534011841</v>
+        <v>0.734698414802551</v>
       </c>
       <c r="H1006" t="n">
         <v>38044</v>
@@ -29717,7 +29717,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G1012" t="n">
-        <v>0.728351175785065</v>
+        <v>0.72835111618042</v>
       </c>
       <c r="H1012" t="n">
         <v>117560</v>
@@ -29746,7 +29746,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G1013" t="n">
-        <v>0.733905076980591</v>
+        <v>0.733905017375946</v>
       </c>
       <c r="H1013" t="n">
         <v>53493</v>
@@ -29775,7 +29775,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G1014" t="n">
-        <v>0.731524765491486</v>
+        <v>0.73152482509613</v>
       </c>
       <c r="H1014" t="n">
         <v>57936</v>
@@ -29804,7 +29804,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G1015" t="n">
-        <v>0.723590731620789</v>
+        <v>0.723590672016144</v>
       </c>
       <c r="H1015" t="n">
         <v>43065</v>
@@ -29891,7 +29891,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G1018" t="n">
-        <v>0.718036711215973</v>
+        <v>0.718036830425262</v>
       </c>
       <c r="H1018" t="n">
         <v>80867</v>
@@ -29920,7 +29920,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G1019" t="n">
-        <v>0.733905076980591</v>
+        <v>0.733905017375946</v>
       </c>
       <c r="H1019" t="n">
         <v>45124</v>
@@ -29949,7 +29949,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G1020" t="n">
-        <v>0.728351175785065</v>
+        <v>0.72835111618042</v>
       </c>
       <c r="H1020" t="n">
         <v>62906</v>
@@ -30065,7 +30065,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G1024" t="n">
-        <v>0.733905076980591</v>
+        <v>0.733905017375946</v>
       </c>
       <c r="H1024" t="n">
         <v>57504</v>
@@ -30094,7 +30094,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G1025" t="n">
-        <v>0.733111679553986</v>
+        <v>0.73311173915863</v>
       </c>
       <c r="H1025" t="n">
         <v>215483</v>
@@ -30152,7 +30152,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G1027" t="n">
-        <v>0.728351175785065</v>
+        <v>0.72835111618042</v>
       </c>
       <c r="H1027" t="n">
         <v>129217</v>
@@ -30181,7 +30181,7 @@
         <v>0.91100001335144</v>
       </c>
       <c r="G1028" t="n">
-        <v>0.722797274589539</v>
+        <v>0.722797393798828</v>
       </c>
       <c r="H1028" t="n">
         <v>57541</v>
@@ -30210,7 +30210,7 @@
         <v>0.916999995708466</v>
       </c>
       <c r="G1029" t="n">
-        <v>0.727557837963104</v>
+        <v>0.727557778358459</v>
       </c>
       <c r="H1029" t="n">
         <v>170288</v>
@@ -30297,7 +30297,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G1032" t="n">
-        <v>0.731524765491486</v>
+        <v>0.73152482509613</v>
       </c>
       <c r="H1032" t="n">
         <v>86634</v>
@@ -30442,7 +30442,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1037" t="n">
-        <v>0.656944155693054</v>
+        <v>0.656944274902344</v>
       </c>
       <c r="H1037" t="n">
         <v>190423</v>
@@ -30471,7 +30471,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1038" t="n">
-        <v>0.669638812541962</v>
+        <v>0.669638752937317</v>
       </c>
       <c r="H1038" t="n">
         <v>191682</v>
@@ -30558,7 +30558,7 @@
         <v>0.880999982357025</v>
       </c>
       <c r="G1041" t="n">
-        <v>0.698994994163513</v>
+        <v>0.698994934558868</v>
       </c>
       <c r="H1041" t="n">
         <v>187083</v>
@@ -30645,7 +30645,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G1044" t="n">
-        <v>0.698201596736908</v>
+        <v>0.698201537132263</v>
       </c>
       <c r="H1044" t="n">
         <v>47189</v>
@@ -30819,7 +30819,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1050" t="n">
-        <v>0.675986111164093</v>
+        <v>0.675986051559448</v>
       </c>
       <c r="H1050" t="n">
         <v>160496</v>
@@ -30906,7 +30906,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1053" t="n">
-        <v>0.634728729724884</v>
+        <v>0.634728610515594</v>
       </c>
       <c r="H1053" t="n">
         <v>374777</v>
@@ -30935,7 +30935,7 @@
         <v>0.828999996185303</v>
       </c>
       <c r="G1054" t="n">
-        <v>0.657737612724304</v>
+        <v>0.657737553119659</v>
       </c>
       <c r="H1054" t="n">
         <v>80976</v>
@@ -30964,7 +30964,7 @@
         <v>0.833000004291534</v>
       </c>
       <c r="G1055" t="n">
-        <v>0.66091126203537</v>
+        <v>0.660911321640015</v>
       </c>
       <c r="H1055" t="n">
         <v>84157</v>
@@ -31022,7 +31022,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1057" t="n">
-        <v>0.626794576644897</v>
+        <v>0.626794636249542</v>
       </c>
       <c r="H1057" t="n">
         <v>153385</v>
@@ -31051,7 +31051,7 @@
         <v>0.823000013828278</v>
       </c>
       <c r="G1058" t="n">
-        <v>0.652977168560028</v>
+        <v>0.652977108955383</v>
       </c>
       <c r="H1058" t="n">
         <v>537944</v>
@@ -31080,7 +31080,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G1059" t="n">
-        <v>0.686300337314606</v>
+        <v>0.686300456523895</v>
       </c>
       <c r="H1059" t="n">
         <v>248429</v>
@@ -31138,7 +31138,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1061" t="n">
-        <v>0.658530950546265</v>
+        <v>0.658531010150909</v>
       </c>
       <c r="H1061" t="n">
         <v>134876</v>
@@ -31167,7 +31167,7 @@
         <v>0.816999971866608</v>
       </c>
       <c r="G1062" t="n">
-        <v>0.648216724395752</v>
+        <v>0.648216664791107</v>
       </c>
       <c r="H1062" t="n">
         <v>152842</v>
@@ -31254,7 +31254,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.533172070980072</v>
+        <v>0.533172130584717</v>
       </c>
       <c r="H1065" t="n">
         <v>203062</v>
@@ -31283,7 +31283,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.491914719343185</v>
+        <v>0.491914749145508</v>
       </c>
       <c r="H1066" t="n">
         <v>239543</v>
@@ -31312,7 +31312,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.507782936096191</v>
+        <v>0.507782995700836</v>
       </c>
       <c r="H1067" t="n">
         <v>236446</v>
@@ -31341,7 +31341,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1068" t="n">
-        <v>0.490327894687653</v>
+        <v>0.490327835083008</v>
       </c>
       <c r="H1068" t="n">
         <v>77522</v>
@@ -31370,7 +31370,7 @@
         <v>0.633000016212463</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.502229034900665</v>
+        <v>0.50222909450531</v>
       </c>
       <c r="H1069" t="n">
         <v>70512</v>
@@ -31399,7 +31399,7 @@
         <v>0.620999991893768</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.492708146572113</v>
+        <v>0.492708116769791</v>
       </c>
       <c r="H1070" t="n">
         <v>69896</v>
@@ -31428,7 +31428,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.507782936096191</v>
+        <v>0.507782995700836</v>
       </c>
       <c r="H1071" t="n">
         <v>40007</v>
@@ -31544,7 +31544,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1075" t="n">
-        <v>0.556974411010742</v>
+        <v>0.556974470615387</v>
       </c>
       <c r="H1075" t="n">
         <v>137932</v>
@@ -31573,7 +31573,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.57125586271286</v>
+        <v>0.571255803108215</v>
       </c>
       <c r="H1076" t="n">
         <v>52985</v>
@@ -31631,7 +31631,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1078" t="n">
-        <v>0.537932515144348</v>
+        <v>0.537932574748993</v>
       </c>
       <c r="H1078" t="n">
         <v>57490</v>
@@ -31660,7 +31660,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.537932515144348</v>
+        <v>0.537932574748993</v>
       </c>
       <c r="H1079" t="n">
         <v>77913</v>
@@ -31747,7 +31747,7 @@
         <v>0.616999983787537</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.489534467458725</v>
+        <v>0.48953452706337</v>
       </c>
       <c r="H1082" t="n">
         <v>93756</v>
@@ -31776,7 +31776,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1083" t="n">
-        <v>0.496675193309784</v>
+        <v>0.496675133705139</v>
       </c>
       <c r="H1083" t="n">
         <v>99961</v>
@@ -31805,7 +31805,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1084" t="n">
-        <v>0.483980596065521</v>
+        <v>0.483980655670166</v>
       </c>
       <c r="H1084" t="n">
         <v>996137</v>
@@ -31834,7 +31834,7 @@
         <v>0.601000010967255</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.476839959621429</v>
+        <v>0.476839929819107</v>
       </c>
       <c r="H1085" t="n">
         <v>406984</v>
@@ -31863,7 +31863,7 @@
         <v>0.598999977111816</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.475253105163574</v>
+        <v>0.475253134965897</v>
       </c>
       <c r="H1086" t="n">
         <v>494891</v>
@@ -31892,7 +31892,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1087" t="n">
-        <v>0.491914719343185</v>
+        <v>0.491914749145508</v>
       </c>
       <c r="H1087" t="n">
         <v>456929</v>
@@ -31921,7 +31921,7 @@
         <v>0.619000017642975</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.491121381521225</v>
+        <v>0.49112132191658</v>
       </c>
       <c r="H1088" t="n">
         <v>194353</v>
@@ -31950,7 +31950,7 @@
         <v>0.601000010967255</v>
       </c>
       <c r="G1089" t="n">
-        <v>0.476839959621429</v>
+        <v>0.476839929819107</v>
       </c>
       <c r="H1089" t="n">
         <v>145596</v>
@@ -32008,7 +32008,7 @@
         <v>0.601000010967255</v>
       </c>
       <c r="G1091" t="n">
-        <v>0.476839959621429</v>
+        <v>0.476839929819107</v>
       </c>
       <c r="H1091" t="n">
         <v>275243</v>
@@ -32037,7 +32037,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1092" t="n">
-        <v>0.476046502590179</v>
+        <v>0.476046532392502</v>
       </c>
       <c r="H1092" t="n">
         <v>183467</v>
@@ -32124,7 +32124,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G1095" t="n">
-        <v>0.471286058425903</v>
+        <v>0.471285998821259</v>
       </c>
       <c r="H1095" t="n">
         <v>112411</v>
@@ -32153,7 +32153,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1096" t="n">
-        <v>0.476046502590179</v>
+        <v>0.476046532392502</v>
       </c>
       <c r="H1096" t="n">
         <v>254873</v>
@@ -32182,7 +32182,7 @@
         <v>0.605000019073486</v>
       </c>
       <c r="G1097" t="n">
-        <v>0.480013519525528</v>
+        <v>0.480013579130173</v>
       </c>
       <c r="H1097" t="n">
         <v>559928</v>
@@ -32211,7 +32211,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1098" t="n">
-        <v>0.485567450523376</v>
+        <v>0.485567390918732</v>
       </c>
       <c r="H1098" t="n">
         <v>540633</v>
@@ -32240,7 +32240,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1099" t="n">
-        <v>0.476046502590179</v>
+        <v>0.476046532392502</v>
       </c>
       <c r="H1099" t="n">
         <v>267291</v>
@@ -32269,7 +32269,7 @@
         <v>0.597000002861023</v>
       </c>
       <c r="G1100" t="n">
-        <v>0.473666280508041</v>
+        <v>0.473666220903397</v>
       </c>
       <c r="H1100" t="n">
         <v>209203</v>
@@ -32298,7 +32298,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1101" t="n">
-        <v>0.476046502590179</v>
+        <v>0.476046532392502</v>
       </c>
       <c r="H1101" t="n">
         <v>68223</v>
@@ -32327,7 +32327,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G1102" t="n">
-        <v>0.471286058425903</v>
+        <v>0.471285998821259</v>
       </c>
       <c r="H1102" t="n">
         <v>87998</v>
@@ -32385,7 +32385,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G1104" t="n">
-        <v>0.471286058425903</v>
+        <v>0.471285998821259</v>
       </c>
       <c r="H1104" t="n">
         <v>95168</v>
@@ -32414,7 +32414,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1105" t="n">
-        <v>0.476046502590179</v>
+        <v>0.476046532392502</v>
       </c>
       <c r="H1105" t="n">
         <v>43205</v>
@@ -32443,7 +32443,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1106" t="n">
-        <v>0.480807065963745</v>
+        <v>0.4808070063591</v>
       </c>
       <c r="H1106" t="n">
         <v>59051</v>
@@ -32472,7 +32472,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1107" t="n">
-        <v>0.476046502590179</v>
+        <v>0.476046532392502</v>
       </c>
       <c r="H1107" t="n">
         <v>50016</v>
@@ -32530,7 +32530,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G1109" t="n">
-        <v>0.450657367706299</v>
+        <v>0.450657397508621</v>
       </c>
       <c r="H1109" t="n">
         <v>166261</v>
@@ -32559,7 +32559,7 @@
         <v>0.58899998664856</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.467319041490555</v>
+        <v>0.467318952083588</v>
       </c>
       <c r="H1110" t="n">
         <v>67719</v>
@@ -32617,7 +32617,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.452244192361832</v>
+        <v>0.452244222164154</v>
       </c>
       <c r="H1112" t="n">
         <v>53538</v>
@@ -32646,7 +32646,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.447483718395233</v>
+        <v>0.447483748197556</v>
       </c>
       <c r="H1113" t="n">
         <v>27552</v>
@@ -32675,7 +32675,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.449070543050766</v>
+        <v>0.449070572853088</v>
       </c>
       <c r="H1114" t="n">
         <v>118310</v>
@@ -32704,7 +32704,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.455417841672897</v>
+        <v>0.45541787147522</v>
       </c>
       <c r="H1115" t="n">
         <v>123928</v>
@@ -32733,7 +32733,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1116" t="n">
-        <v>0.469699203968048</v>
+        <v>0.46969923377037</v>
       </c>
       <c r="H1116" t="n">
         <v>34439</v>
@@ -32762,7 +32762,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1117" t="n">
-        <v>0.476046502590179</v>
+        <v>0.476046532392502</v>
       </c>
       <c r="H1117" t="n">
         <v>402801</v>
@@ -32791,7 +32791,7 @@
         <v>0.609000027179718</v>
       </c>
       <c r="G1118" t="n">
-        <v>0.483187258243561</v>
+        <v>0.483187288045883</v>
       </c>
       <c r="H1118" t="n">
         <v>308791</v>
@@ -32820,7 +32820,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1119" t="n">
-        <v>0.476046502590179</v>
+        <v>0.476046532392502</v>
       </c>
       <c r="H1119" t="n">
         <v>87032</v>
@@ -32849,7 +32849,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1120" t="n">
-        <v>0.476046502590179</v>
+        <v>0.476046532392502</v>
       </c>
       <c r="H1120" t="n">
         <v>99119</v>
@@ -32878,7 +32878,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1121" t="n">
-        <v>0.474459707736969</v>
+        <v>0.474459648132324</v>
       </c>
       <c r="H1121" t="n">
         <v>155730</v>
@@ -32907,7 +32907,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1122" t="n">
-        <v>0.4792200922966</v>
+        <v>0.479220181703568</v>
       </c>
       <c r="H1122" t="n">
         <v>724571</v>
@@ -32936,7 +32936,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1123" t="n">
-        <v>0.476046502590179</v>
+        <v>0.476046532392502</v>
       </c>
       <c r="H1123" t="n">
         <v>224551</v>
@@ -32965,7 +32965,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1124" t="n">
-        <v>0.491914719343185</v>
+        <v>0.491914749145508</v>
       </c>
       <c r="H1124" t="n">
         <v>673286</v>
@@ -33023,7 +33023,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1126" t="n">
-        <v>0.553800761699677</v>
+        <v>0.553800821304321</v>
       </c>
       <c r="H1126" t="n">
         <v>1169063</v>
@@ -33052,7 +33052,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1127" t="n">
-        <v>0.566495418548584</v>
+        <v>0.566495299339294</v>
       </c>
       <c r="H1127" t="n">
         <v>338100</v>
@@ -33139,7 +33139,7 @@
         <v>0.725000023841858</v>
       </c>
       <c r="G1130" t="n">
-        <v>0.575222849845886</v>
+        <v>0.575222909450531</v>
       </c>
       <c r="H1130" t="n">
         <v>1158362</v>
@@ -33168,7 +33168,7 @@
         <v>0.75900000333786</v>
       </c>
       <c r="G1131" t="n">
-        <v>0.602198898792267</v>
+        <v>0.602198839187622</v>
       </c>
       <c r="H1131" t="n">
         <v>1052612</v>
@@ -33197,7 +33197,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G1132" t="n">
-        <v>0.583156943321228</v>
+        <v>0.583157002925873</v>
       </c>
       <c r="H1132" t="n">
         <v>432413</v>
@@ -33255,7 +33255,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1134" t="n">
-        <v>0.56966894865036</v>
+        <v>0.56966906785965</v>
       </c>
       <c r="H1134" t="n">
         <v>200198</v>
@@ -33284,7 +33284,7 @@
         <v>0.707000017166138</v>
       </c>
       <c r="G1135" t="n">
-        <v>0.560941398143768</v>
+        <v>0.560941457748413</v>
       </c>
       <c r="H1135" t="n">
         <v>96464</v>
@@ -33313,7 +33313,7 @@
         <v>0.712999999523163</v>
       </c>
       <c r="G1136" t="n">
-        <v>0.565701901912689</v>
+        <v>0.565701961517334</v>
       </c>
       <c r="H1136" t="n">
         <v>129766</v>
@@ -33342,7 +33342,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1137" t="n">
-        <v>0.566495418548584</v>
+        <v>0.566495299339294</v>
       </c>
       <c r="H1137" t="n">
         <v>122578</v>
@@ -33371,7 +33371,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G1138" t="n">
-        <v>0.559354603290558</v>
+        <v>0.559354662895203</v>
       </c>
       <c r="H1138" t="n">
         <v>70962</v>
@@ -33400,7 +33400,7 @@
         <v>0.690999984741211</v>
       </c>
       <c r="G1139" t="n">
-        <v>0.54824697971344</v>
+        <v>0.548246920108795</v>
       </c>
       <c r="H1139" t="n">
         <v>64977</v>
@@ -33487,7 +33487,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1142" t="n">
-        <v>0.533172070980072</v>
+        <v>0.533172130584717</v>
       </c>
       <c r="H1142" t="n">
         <v>60009</v>
@@ -33632,7 +33632,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G1147" t="n">
-        <v>0.572842597961426</v>
+        <v>0.572842657566071</v>
       </c>
       <c r="H1147" t="n">
         <v>124138</v>
@@ -33719,7 +33719,7 @@
         <v>0.726999998092651</v>
       </c>
       <c r="G1150" t="n">
-        <v>0.576809644699097</v>
+        <v>0.576809704303741</v>
       </c>
       <c r="H1150" t="n">
         <v>49042</v>
@@ -33748,7 +33748,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1151" t="n">
-        <v>0.610926330089569</v>
+        <v>0.610926389694214</v>
       </c>
       <c r="H1151" t="n">
         <v>842178</v>
@@ -33777,7 +33777,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1152" t="n">
-        <v>0.626794576644897</v>
+        <v>0.626794636249542</v>
       </c>
       <c r="H1152" t="n">
         <v>599215</v>
@@ -33864,7 +33864,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G1155" t="n">
-        <v>0.599818587303162</v>
+        <v>0.599818646907806</v>
       </c>
       <c r="H1155" t="n">
         <v>154701</v>
@@ -33922,7 +33922,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G1157" t="n">
-        <v>0.61489337682724</v>
+        <v>0.614893436431885</v>
       </c>
       <c r="H1157" t="n">
         <v>112455</v>
@@ -33951,7 +33951,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1158" t="n">
-        <v>0.626794576644897</v>
+        <v>0.626794636249542</v>
       </c>
       <c r="H1158" t="n">
         <v>228165</v>
@@ -34009,7 +34009,7 @@
         <v>0.788999974727631</v>
       </c>
       <c r="G1160" t="n">
-        <v>0.626001179218292</v>
+        <v>0.626001119613647</v>
       </c>
       <c r="H1160" t="n">
         <v>83116</v>
@@ -34038,7 +34038,7 @@
         <v>0.799000024795532</v>
       </c>
       <c r="G1161" t="n">
-        <v>0.633935332298279</v>
+        <v>0.633935272693634</v>
       </c>
       <c r="H1161" t="n">
         <v>110117</v>
@@ -34096,7 +34096,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.617273688316345</v>
+        <v>0.6172736287117</v>
       </c>
       <c r="H1163" t="n">
         <v>287392</v>
@@ -34183,7 +34183,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G1166" t="n">
-        <v>0.683920204639435</v>
+        <v>0.68392014503479</v>
       </c>
       <c r="H1166" t="n">
         <v>600766</v>
@@ -34386,7 +34386,7 @@
         <v>0.876999974250793</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.695821285247803</v>
+        <v>0.695821344852448</v>
       </c>
       <c r="H1173" t="n">
         <v>232967</v>
@@ -34618,7 +34618,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.674399256706238</v>
+        <v>0.674399197101593</v>
       </c>
       <c r="H1181" t="n">
         <v>13990</v>
@@ -34647,7 +34647,7 @@
         <v>0.842999994754791</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.668845355510712</v>
+        <v>0.668845295906067</v>
       </c>
       <c r="H1182" t="n">
         <v>38982</v>
@@ -34676,7 +34676,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.650596857070923</v>
+        <v>0.650596916675568</v>
       </c>
       <c r="H1183" t="n">
         <v>278764</v>
@@ -34705,7 +34705,7 @@
         <v>0.824999988079071</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.654563903808594</v>
+        <v>0.654563963413239</v>
       </c>
       <c r="H1184" t="n">
         <v>245205</v>
@@ -34879,7 +34879,7 @@
         <v>0.824999988079071</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.654563903808594</v>
+        <v>0.654563963413239</v>
       </c>
       <c r="H1190" t="n">
         <v>185901</v>
@@ -34908,7 +34908,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.655357360839844</v>
+        <v>0.655357301235199</v>
       </c>
       <c r="H1191" t="n">
         <v>178474</v>
@@ -34937,7 +34937,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.664878249168396</v>
+        <v>0.664878368377686</v>
       </c>
       <c r="H1192" t="n">
         <v>117700</v>
@@ -34995,7 +34995,7 @@
         <v>0.852999985218048</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.676779448986053</v>
+        <v>0.676779508590698</v>
       </c>
       <c r="H1194" t="n">
         <v>46882</v>
@@ -35024,7 +35024,7 @@
         <v>0.842999994754791</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.668845355510712</v>
+        <v>0.668845295906067</v>
       </c>
       <c r="H1195" t="n">
         <v>151652</v>
@@ -35053,7 +35053,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.669638812541962</v>
+        <v>0.669638752937317</v>
       </c>
       <c r="H1196" t="n">
         <v>36452</v>
@@ -35082,7 +35082,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.664878249168396</v>
+        <v>0.664878368377686</v>
       </c>
       <c r="H1197" t="n">
         <v>47928</v>
@@ -35169,7 +35169,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.664878249168396</v>
+        <v>0.664878368377686</v>
       </c>
       <c r="H1200" t="n">
         <v>167351</v>
@@ -35198,7 +35198,7 @@
         <v>0.833000004291534</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.66091126203537</v>
+        <v>0.660911321640015</v>
       </c>
       <c r="H1201" t="n">
         <v>27578</v>
@@ -35227,7 +35227,7 @@
         <v>0.833000004291534</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.66091126203537</v>
+        <v>0.660911321640015</v>
       </c>
       <c r="H1202" t="n">
         <v>91968</v>
@@ -35285,7 +35285,7 @@
         <v>0.833000004291534</v>
       </c>
       <c r="G1204" t="n">
-        <v>0.66091126203537</v>
+        <v>0.660911321640015</v>
       </c>
       <c r="H1204" t="n">
         <v>20833</v>
@@ -35372,7 +35372,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G1207" t="n">
-        <v>0.66170471906662</v>
+        <v>0.661704659461975</v>
       </c>
       <c r="H1207" t="n">
         <v>9345</v>
@@ -35430,7 +35430,7 @@
         <v>0.85699999332428</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.679953157901764</v>
+        <v>0.679953098297119</v>
       </c>
       <c r="H1209" t="n">
         <v>53560</v>
@@ -35546,7 +35546,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1213" t="n">
-        <v>0.701375246047974</v>
+        <v>0.701375186443329</v>
       </c>
       <c r="H1213" t="n">
         <v>183522</v>
@@ -35633,7 +35633,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.723590731620789</v>
+        <v>0.723590672016144</v>
       </c>
       <c r="H1216" t="n">
         <v>821505</v>
@@ -35923,7 +35923,7 @@
         <v>0.866999983787537</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.687887251377106</v>
+        <v>0.687887191772461</v>
       </c>
       <c r="H1226" t="n">
         <v>59033</v>
@@ -36010,7 +36010,7 @@
         <v>0.814999997615814</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.646629810333252</v>
+        <v>0.646629869937897</v>
       </c>
       <c r="H1229" t="n">
         <v>31879</v>
@@ -36155,7 +36155,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.701375246047974</v>
+        <v>0.701375186443329</v>
       </c>
       <c r="H1234" t="n">
         <v>58034</v>
@@ -36184,7 +36184,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.722003877162933</v>
+        <v>0.722003936767578</v>
       </c>
       <c r="H1235" t="n">
         <v>334369</v>
@@ -36213,7 +36213,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.722003877162933</v>
+        <v>0.722003936767578</v>
       </c>
       <c r="H1236" t="n">
         <v>116928</v>
@@ -36242,7 +36242,7 @@
         <v>1</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.793410897254944</v>
+        <v>0.793410837650299</v>
       </c>
       <c r="H1237" t="n">
         <v>1515347</v>
@@ -36358,7 +36358,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.785476684570312</v>
+        <v>0.785476744174957</v>
       </c>
       <c r="H1241" t="n">
         <v>198010</v>
@@ -36387,7 +36387,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.773575663566589</v>
+        <v>0.773575603961945</v>
       </c>
       <c r="H1242" t="n">
         <v>163606</v>
@@ -36474,7 +36474,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1245" t="n">
-        <v>0.785476684570312</v>
+        <v>0.785476744174957</v>
       </c>
       <c r="H1245" t="n">
         <v>194176</v>
@@ -36532,7 +36532,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G1247" t="n">
-        <v>0.777542650699615</v>
+        <v>0.77754271030426</v>
       </c>
       <c r="H1247" t="n">
         <v>85062</v>
@@ -36561,7 +36561,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.77436900138855</v>
+        <v>0.774368941783905</v>
       </c>
       <c r="H1248" t="n">
         <v>68898</v>
@@ -36590,7 +36590,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G1249" t="n">
-        <v>0.755327224731445</v>
+        <v>0.755327105522156</v>
       </c>
       <c r="H1249" t="n">
         <v>138708</v>
@@ -36677,7 +36677,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G1252" t="n">
-        <v>0.773575663566589</v>
+        <v>0.773575603961945</v>
       </c>
       <c r="H1252" t="n">
         <v>85577</v>
@@ -36706,7 +36706,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1253" t="n">
-        <v>0.785476684570312</v>
+        <v>0.785476744174957</v>
       </c>
       <c r="H1253" t="n">
         <v>248010</v>
@@ -36793,7 +36793,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G1256" t="n">
-        <v>0.828320980072021</v>
+        <v>0.828321039676666</v>
       </c>
       <c r="H1256" t="n">
         <v>467727</v>
@@ -36822,7 +36822,7 @@
         <v>1.07799994945526</v>
       </c>
       <c r="G1257" t="n">
-        <v>0.855296969413757</v>
+        <v>0.855296790599823</v>
       </c>
       <c r="H1257" t="n">
         <v>290124</v>
@@ -36851,7 +36851,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1258" t="n">
-        <v>0.86481785774231</v>
+        <v>0.864817917346954</v>
       </c>
       <c r="H1258" t="n">
         <v>283081</v>
@@ -36880,7 +36880,7 @@
         <v>1.09200000762939</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.866404712200165</v>
+        <v>0.86640465259552</v>
       </c>
       <c r="H1259" t="n">
         <v>172850</v>
@@ -36938,7 +36938,7 @@
         <v>1.1139999628067</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.883859634399414</v>
+        <v>0.883859813213348</v>
       </c>
       <c r="H1261" t="n">
         <v>160546</v>
@@ -36967,7 +36967,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1262" t="n">
-        <v>0.86481785774231</v>
+        <v>0.864817917346954</v>
       </c>
       <c r="H1262" t="n">
         <v>200755</v>
@@ -37025,7 +37025,7 @@
         <v>1.10800004005432</v>
       </c>
       <c r="G1264" t="n">
-        <v>0.879099309444427</v>
+        <v>0.879099369049072</v>
       </c>
       <c r="H1264" t="n">
         <v>107652</v>
@@ -37054,7 +37054,7 @@
         <v>1.06400001049042</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.84418910741806</v>
+        <v>0.844189286231995</v>
       </c>
       <c r="H1265" t="n">
         <v>142945</v>
@@ -37112,7 +37112,7 @@
         <v>1.09599995613098</v>
       </c>
       <c r="G1267" t="n">
-        <v>0.869578301906586</v>
+        <v>0.86957836151123</v>
       </c>
       <c r="H1267" t="n">
         <v>144700</v>
@@ -37170,7 +37170,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.871165215969086</v>
+        <v>0.871165156364441</v>
       </c>
       <c r="H1269" t="n">
         <v>118985</v>
@@ -37199,7 +37199,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1270" t="n">
-        <v>0.871165215969086</v>
+        <v>0.871165156364441</v>
       </c>
       <c r="H1270" t="n">
         <v>75834</v>
@@ -37228,7 +37228,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.860057294368744</v>
+        <v>0.860057413578033</v>
       </c>
       <c r="H1271" t="n">
         <v>165587</v>
@@ -37257,7 +37257,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1272" t="n">
-        <v>0.86481785774231</v>
+        <v>0.864817917346954</v>
       </c>
       <c r="H1272" t="n">
         <v>89255</v>
@@ -37286,7 +37286,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1273" t="n">
-        <v>0.88862019777298</v>
+        <v>0.888620138168335</v>
       </c>
       <c r="H1273" t="n">
         <v>393656</v>
@@ -37344,7 +37344,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1275" t="n">
-        <v>0.936224758625031</v>
+        <v>0.93622487783432</v>
       </c>
       <c r="H1275" t="n">
         <v>280760</v>
@@ -37373,7 +37373,7 @@
         <v>1.15799999237061</v>
       </c>
       <c r="G1276" t="n">
-        <v>0.918769896030426</v>
+        <v>0.918769836425781</v>
       </c>
       <c r="H1276" t="n">
         <v>150351</v>
@@ -37460,7 +37460,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1279" t="n">
-        <v>0.91242241859436</v>
+        <v>0.91242253780365</v>
       </c>
       <c r="H1279" t="n">
         <v>58233</v>
@@ -37489,7 +37489,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1280" t="n">
-        <v>0.904488384723663</v>
+        <v>0.904488444328308</v>
       </c>
       <c r="H1280" t="n">
         <v>149342</v>
@@ -37518,7 +37518,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1281" t="n">
-        <v>0.91242241859436</v>
+        <v>0.91242253780365</v>
       </c>
       <c r="H1281" t="n">
         <v>32653</v>
@@ -37547,7 +37547,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G1282" t="n">
-        <v>0.875925540924072</v>
+        <v>0.875925600528717</v>
       </c>
       <c r="H1282" t="n">
         <v>164232</v>
@@ -37576,7 +37576,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1283" t="n">
-        <v>0.871165215969086</v>
+        <v>0.871165156364441</v>
       </c>
       <c r="H1283" t="n">
         <v>108628</v>
@@ -37750,7 +37750,7 @@
         <v>1.15799999237061</v>
       </c>
       <c r="G1289" t="n">
-        <v>0.918769896030426</v>
+        <v>0.918769836425781</v>
       </c>
       <c r="H1289" t="n">
         <v>270975</v>
@@ -37779,7 +37779,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1290" t="n">
-        <v>0.947332561016083</v>
+        <v>0.947332441806793</v>
       </c>
       <c r="H1290" t="n">
         <v>477589</v>
@@ -37808,7 +37808,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1291" t="n">
-        <v>0.95685350894928</v>
+        <v>0.956853449344635</v>
       </c>
       <c r="H1291" t="n">
         <v>267320</v>
@@ -37866,7 +37866,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1293" t="n">
-        <v>0.96161413192749</v>
+        <v>0.961614012718201</v>
       </c>
       <c r="H1293" t="n">
         <v>618316</v>
@@ -37895,7 +37895,7 @@
         <v>1.21800005435944</v>
       </c>
       <c r="G1294" t="n">
-        <v>0.966374516487122</v>
+        <v>0.966374576091766</v>
       </c>
       <c r="H1294" t="n">
         <v>107834</v>
@@ -37924,7 +37924,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1295" t="n">
-        <v>0.967961192131042</v>
+        <v>0.967961311340332</v>
       </c>
       <c r="H1295" t="n">
         <v>195812</v>
@@ -37982,7 +37982,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1297" t="n">
-        <v>0.944158852100372</v>
+        <v>0.944159090518951</v>
       </c>
       <c r="H1297" t="n">
         <v>104018</v>
@@ -38011,7 +38011,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1298" t="n">
-        <v>0.967961192131042</v>
+        <v>0.967961311340332</v>
       </c>
       <c r="H1298" t="n">
         <v>184822</v>
@@ -38040,7 +38040,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1299" t="n">
-        <v>0.944158852100372</v>
+        <v>0.944159090518951</v>
       </c>
       <c r="H1299" t="n">
         <v>72893</v>
@@ -38098,7 +38098,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1301" t="n">
-        <v>0.960027039051056</v>
+        <v>0.960027158260345</v>
       </c>
       <c r="H1301" t="n">
         <v>135794</v>
@@ -38127,7 +38127,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G1302" t="n">
-        <v>0.942572116851807</v>
+        <v>0.942571997642517</v>
       </c>
       <c r="H1302" t="n">
         <v>166744</v>
@@ -38214,7 +38214,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1305" t="n">
-        <v>0.95685350894928</v>
+        <v>0.956853449344635</v>
       </c>
       <c r="H1305" t="n">
         <v>453038</v>
@@ -38272,7 +38272,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G1307" t="n">
-        <v>0.950506210327148</v>
+        <v>0.950506269931793</v>
       </c>
       <c r="H1307" t="n">
         <v>134352</v>
@@ -38301,7 +38301,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G1308" t="n">
-        <v>0.971134901046753</v>
+        <v>0.971134781837463</v>
       </c>
       <c r="H1308" t="n">
         <v>184888</v>
@@ -38359,7 +38359,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1310" t="n">
-        <v>0.939398407936096</v>
+        <v>0.939398467540741</v>
       </c>
       <c r="H1310" t="n">
         <v>154101</v>
@@ -38388,7 +38388,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G1311" t="n">
-        <v>0.971134901046753</v>
+        <v>0.971134781837463</v>
       </c>
       <c r="H1311" t="n">
         <v>164514</v>
@@ -38417,7 +38417,7 @@
         <v>1.21800005435944</v>
       </c>
       <c r="G1312" t="n">
-        <v>0.966374516487122</v>
+        <v>0.966374576091766</v>
       </c>
       <c r="H1312" t="n">
         <v>93369</v>
@@ -38446,7 +38446,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1313" t="n">
-        <v>0.95685350894928</v>
+        <v>0.956853449344635</v>
       </c>
       <c r="H1313" t="n">
         <v>77384</v>
@@ -38475,7 +38475,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1314" t="n">
-        <v>0.944158852100372</v>
+        <v>0.944159090518951</v>
       </c>
       <c r="H1314" t="n">
         <v>53655</v>
@@ -38533,7 +38533,7 @@
         <v>1.25</v>
       </c>
       <c r="G1316" t="n">
-        <v>0.991763651371002</v>
+        <v>0.991763710975647</v>
       </c>
       <c r="H1316" t="n">
         <v>315112</v>
@@ -38562,7 +38562,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1317" t="n">
-        <v>0.983829438686371</v>
+        <v>0.983829498291016</v>
       </c>
       <c r="H1317" t="n">
         <v>49846</v>
@@ -38591,7 +38591,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G1318" t="n">
-        <v>0.980655789375305</v>
+        <v>0.980655670166016</v>
       </c>
       <c r="H1318" t="n">
         <v>32873</v>
@@ -38620,7 +38620,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G1319" t="n">
-        <v>1.00921857357025</v>
+        <v>1.00921869277954</v>
       </c>
       <c r="H1319" t="n">
         <v>159846</v>
@@ -38649,7 +38649,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1320" t="n">
-        <v>1.00763177871704</v>
+        <v>1.00763189792633</v>
       </c>
       <c r="H1320" t="n">
         <v>120143</v>
@@ -38678,7 +38678,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1321" t="n">
-        <v>1.01080548763275</v>
+        <v>1.01080536842346</v>
       </c>
       <c r="H1321" t="n">
         <v>96132</v>
@@ -38707,7 +38707,7 @@
         <v>1.27799999713898</v>
       </c>
       <c r="G1322" t="n">
-        <v>1.01397907733917</v>
+        <v>1.01397895812988</v>
       </c>
       <c r="H1322" t="n">
         <v>809025</v>
@@ -38736,7 +38736,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G1323" t="n">
-        <v>1.00921857357025</v>
+        <v>1.00921869277954</v>
       </c>
       <c r="H1323" t="n">
         <v>148270</v>
@@ -38823,7 +38823,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.05206286907196</v>
+        <v>1.05206274986267</v>
       </c>
       <c r="H1326" t="n">
         <v>373415</v>
@@ -38881,7 +38881,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G1328" t="n">
-        <v>1.07269144058228</v>
+        <v>1.07269132137299</v>
       </c>
       <c r="H1328" t="n">
         <v>371431</v>
@@ -38910,7 +38910,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.07269144058228</v>
+        <v>1.07269132137299</v>
       </c>
       <c r="H1329" t="n">
         <v>170365</v>
@@ -38939,7 +38939,7 @@
         <v>1.33399999141693</v>
       </c>
       <c r="G1330" t="n">
-        <v>1.05840992927551</v>
+        <v>1.05841016769409</v>
       </c>
       <c r="H1330" t="n">
         <v>150485</v>
@@ -39026,7 +39026,7 @@
         <v>1.317999958992</v>
       </c>
       <c r="G1333" t="n">
-        <v>1.04571545124054</v>
+        <v>1.04571557044983</v>
       </c>
       <c r="H1333" t="n">
         <v>261617</v>
@@ -39055,7 +39055,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.05206286907196</v>
+        <v>1.05206274986267</v>
       </c>
       <c r="H1334" t="n">
         <v>79861</v>
@@ -39084,7 +39084,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1335" t="n">
-        <v>1.0615838766098</v>
+        <v>1.06158375740051</v>
       </c>
       <c r="H1335" t="n">
         <v>281911</v>
@@ -39113,7 +39113,7 @@
         <v>1.35399997234344</v>
       </c>
       <c r="G1336" t="n">
-        <v>1.07427823543549</v>
+        <v>1.07427835464478</v>
       </c>
       <c r="H1336" t="n">
         <v>187249</v>
@@ -39171,7 +39171,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G1338" t="n">
-        <v>1.06951808929443</v>
+        <v>1.06951785087585</v>
       </c>
       <c r="H1338" t="n">
         <v>54081</v>
@@ -39200,7 +39200,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.05206286907196</v>
+        <v>1.05206274986267</v>
       </c>
       <c r="H1339" t="n">
         <v>142972</v>
@@ -39229,7 +39229,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.05206286907196</v>
+        <v>1.05206274986267</v>
       </c>
       <c r="H1340" t="n">
         <v>84943</v>
@@ -39287,7 +39287,7 @@
         <v>1.33399999141693</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.05840992927551</v>
+        <v>1.05841016769409</v>
       </c>
       <c r="H1342" t="n">
         <v>47784</v>
@@ -39316,7 +39316,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.0615838766098</v>
+        <v>1.06158375740051</v>
       </c>
       <c r="H1343" t="n">
         <v>129344</v>
@@ -39461,7 +39461,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G1348" t="n">
-        <v>1.06951808929443</v>
+        <v>1.06951785087585</v>
       </c>
       <c r="H1348" t="n">
         <v>70742</v>
@@ -39519,7 +39519,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1350" t="n">
-        <v>1.09490692615509</v>
+        <v>1.09490704536438</v>
       </c>
       <c r="H1350" t="n">
         <v>147863</v>
@@ -39548,7 +39548,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1351" t="n">
-        <v>1.09490692615509</v>
+        <v>1.09490704536438</v>
       </c>
       <c r="H1351" t="n">
         <v>59529</v>
@@ -39635,7 +39635,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G1354" t="n">
-        <v>1.10918831825256</v>
+        <v>1.10918855667114</v>
       </c>
       <c r="H1354" t="n">
         <v>208935</v>
@@ -39722,7 +39722,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.11236202716827</v>
+        <v>1.11236190795898</v>
       </c>
       <c r="H1357" t="n">
         <v>86296</v>
@@ -39751,7 +39751,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G1358" t="n">
-        <v>1.10918831825256</v>
+        <v>1.10918855667114</v>
       </c>
       <c r="H1358" t="n">
         <v>33629</v>
@@ -39780,7 +39780,7 @@
         <v>1.38199996948242</v>
       </c>
       <c r="G1359" t="n">
-        <v>1.09649395942688</v>
+        <v>1.09649384021759</v>
       </c>
       <c r="H1359" t="n">
         <v>64376</v>
@@ -39838,7 +39838,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1361" t="n">
-        <v>1.19805037975311</v>
+        <v>1.19805026054382</v>
       </c>
       <c r="H1361" t="n">
         <v>1517956</v>
@@ -39896,7 +39896,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1363" t="n">
-        <v>1.25358915328979</v>
+        <v>1.25358927249908</v>
       </c>
       <c r="H1363" t="n">
         <v>642269</v>
@@ -39925,7 +39925,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G1364" t="n">
-        <v>1.24406826496124</v>
+        <v>1.24406814575195</v>
       </c>
       <c r="H1364" t="n">
         <v>363856</v>
@@ -39954,7 +39954,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G1365" t="n">
-        <v>1.2964334487915</v>
+        <v>1.29643332958221</v>
       </c>
       <c r="H1365" t="n">
         <v>321961</v>
@@ -39983,7 +39983,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G1366" t="n">
-        <v>1.32975649833679</v>
+        <v>1.32975673675537</v>
       </c>
       <c r="H1366" t="n">
         <v>734473</v>
@@ -40157,7 +40157,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G1372" t="n">
-        <v>1.45511567592621</v>
+        <v>1.45511555671692</v>
       </c>
       <c r="H1372" t="n">
         <v>376994</v>
@@ -40215,7 +40215,7 @@
         <v>1.92400002479553</v>
       </c>
       <c r="G1374" t="n">
-        <v>1.52652251720428</v>
+        <v>1.52652263641357</v>
       </c>
       <c r="H1374" t="n">
         <v>374251</v>
@@ -40244,7 +40244,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.51382791996002</v>
+        <v>1.51382803916931</v>
       </c>
       <c r="H1375" t="n">
         <v>389589</v>
@@ -40273,7 +40273,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.53286993503571</v>
+        <v>1.53286969661713</v>
       </c>
       <c r="H1376" t="n">
         <v>229126</v>
@@ -40331,7 +40331,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G1378" t="n">
-        <v>1.52493572235107</v>
+        <v>1.52493584156036</v>
       </c>
       <c r="H1378" t="n">
         <v>217063</v>
@@ -40389,7 +40389,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1380" t="n">
-        <v>1.54362154006958</v>
+        <v>1.54362165927887</v>
       </c>
       <c r="H1380" t="n">
         <v>208199</v>
@@ -40476,7 +40476,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.52249836921692</v>
+        <v>1.52249825000763</v>
       </c>
       <c r="H1383" t="n">
         <v>93831</v>
@@ -40505,7 +40505,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.52249836921692</v>
+        <v>1.52249825000763</v>
       </c>
       <c r="H1384" t="n">
         <v>159743</v>
@@ -40621,7 +40621,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.41363251209259</v>
+        <v>1.4136323928833</v>
       </c>
       <c r="H1388" t="n">
         <v>458449</v>
@@ -40650,7 +40650,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1389" t="n">
-        <v>1.47212755680084</v>
+        <v>1.47212767601013</v>
       </c>
       <c r="H1389" t="n">
         <v>215457</v>
@@ -40679,7 +40679,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.4315060377121</v>
+        <v>1.43150591850281</v>
       </c>
       <c r="H1390" t="n">
         <v>172737</v>
@@ -40708,7 +40708,7 @@
         <v>1.74600005149841</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.41850709915161</v>
+        <v>1.4185072183609</v>
       </c>
       <c r="H1391" t="n">
         <v>93193</v>
@@ -40737,7 +40737,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1392" t="n">
-        <v>1.40875792503357</v>
+        <v>1.40875780582428</v>
       </c>
       <c r="H1392" t="n">
         <v>93834</v>
@@ -40882,7 +40882,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G1397" t="n">
-        <v>1.35188770294189</v>
+        <v>1.3518875837326</v>
       </c>
       <c r="H1397" t="n">
         <v>240612</v>
@@ -40998,7 +40998,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G1401" t="n">
-        <v>1.39575886726379</v>
+        <v>1.39575898647308</v>
       </c>
       <c r="H1401" t="n">
         <v>142165</v>
@@ -41085,7 +41085,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1404" t="n">
-        <v>1.37788534164429</v>
+        <v>1.37788546085358</v>
       </c>
       <c r="H1404" t="n">
         <v>131204</v>
@@ -41143,7 +41143,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G1406" t="n">
-        <v>1.35351240634918</v>
+        <v>1.35351252555847</v>
       </c>
       <c r="H1406" t="n">
         <v>323384</v>
@@ -41172,7 +41172,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1407" t="n">
-        <v>1.3161404132843</v>
+        <v>1.31614053249359</v>
       </c>
       <c r="H1407" t="n">
         <v>184770</v>
@@ -41375,7 +41375,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1414" t="n">
-        <v>1.43800532817841</v>
+        <v>1.4380054473877</v>
       </c>
       <c r="H1414" t="n">
         <v>259665</v>
@@ -41433,7 +41433,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G1416" t="n">
-        <v>1.42013192176819</v>
+        <v>1.42013204097748</v>
       </c>
       <c r="H1416" t="n">
         <v>135961</v>
@@ -41520,7 +41520,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G1419" t="n">
-        <v>1.4315060377121</v>
+        <v>1.43150591850281</v>
       </c>
       <c r="H1419" t="n">
         <v>176317</v>
@@ -41549,7 +41549,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G1420" t="n">
-        <v>1.4315060377121</v>
+        <v>1.43150591850281</v>
       </c>
       <c r="H1420" t="n">
         <v>119553</v>
@@ -41636,7 +41636,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1423" t="n">
-        <v>1.48675131797791</v>
+        <v>1.48675143718719</v>
       </c>
       <c r="H1423" t="n">
         <v>839179</v>
@@ -41694,7 +41694,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.49000120162964</v>
+        <v>1.49000108242035</v>
       </c>
       <c r="H1425" t="n">
         <v>187044</v>
@@ -41723,7 +41723,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1426" t="n">
-        <v>1.51924872398376</v>
+        <v>1.51924860477448</v>
       </c>
       <c r="H1426" t="n">
         <v>266509</v>
@@ -41752,7 +41752,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G1427" t="n">
-        <v>1.49812543392181</v>
+        <v>1.49812531471252</v>
       </c>
       <c r="H1427" t="n">
         <v>108196</v>
@@ -41839,7 +41839,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1430" t="n">
-        <v>1.48350155353546</v>
+        <v>1.48350167274475</v>
       </c>
       <c r="H1430" t="n">
         <v>123040</v>
@@ -41926,7 +41926,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G1433" t="n">
-        <v>1.43638062477112</v>
+        <v>1.43638050556183</v>
       </c>
       <c r="H1433" t="n">
         <v>92372</v>
@@ -41984,7 +41984,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1435" t="n">
-        <v>1.47212755680084</v>
+        <v>1.47212767601013</v>
       </c>
       <c r="H1435" t="n">
         <v>207722</v>
@@ -42013,7 +42013,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1436" t="n">
-        <v>1.48675131797791</v>
+        <v>1.48675143718719</v>
       </c>
       <c r="H1436" t="n">
         <v>150831</v>
@@ -42042,7 +42042,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G1437" t="n">
-        <v>1.49000120162964</v>
+        <v>1.49000108242035</v>
       </c>
       <c r="H1437" t="n">
         <v>106074</v>
@@ -42100,7 +42100,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G1439" t="n">
-        <v>1.53224754333496</v>
+        <v>1.53224766254425</v>
       </c>
       <c r="H1439" t="n">
         <v>424476</v>
@@ -42158,7 +42158,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1441" t="n">
-        <v>1.5354973077774</v>
+        <v>1.53549742698669</v>
       </c>
       <c r="H1441" t="n">
         <v>380338</v>
@@ -42303,7 +42303,7 @@
         <v>1.98800003528595</v>
       </c>
       <c r="G1446" t="n">
-        <v>1.6151157617569</v>
+        <v>1.61511564254761</v>
       </c>
       <c r="H1446" t="n">
         <v>247250</v>
@@ -42419,7 +42419,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G1450" t="n">
-        <v>1.52574825286865</v>
+        <v>1.52574813365936</v>
       </c>
       <c r="H1450" t="n">
         <v>194235</v>
@@ -42477,7 +42477,7 @@
         <v>1.81400001049042</v>
       </c>
       <c r="G1452" t="n">
-        <v>1.473752617836</v>
+        <v>1.47375249862671</v>
       </c>
       <c r="H1452" t="n">
         <v>146775</v>
@@ -42535,7 +42535,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G1454" t="n">
-        <v>1.4315060377121</v>
+        <v>1.43150591850281</v>
       </c>
       <c r="H1454" t="n">
         <v>224881</v>
@@ -42651,7 +42651,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G1458" t="n">
-        <v>1.48837637901306</v>
+        <v>1.48837625980377</v>
       </c>
       <c r="H1458" t="n">
         <v>141066</v>
@@ -42738,7 +42738,7 @@
         <v>1.74600005149841</v>
       </c>
       <c r="G1461" t="n">
-        <v>1.41850709915161</v>
+        <v>1.4185072183609</v>
       </c>
       <c r="H1461" t="n">
         <v>117908</v>
@@ -42796,7 +42796,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G1463" t="n">
-        <v>1.44775450229645</v>
+        <v>1.44775462150574</v>
       </c>
       <c r="H1463" t="n">
         <v>92420</v>
@@ -42825,7 +42825,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G1464" t="n">
-        <v>1.4006335735321</v>
+        <v>1.40063345432281</v>
       </c>
       <c r="H1464" t="n">
         <v>139889</v>
@@ -42941,7 +42941,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1468" t="n">
-        <v>1.43800532817841</v>
+        <v>1.4380054473877</v>
       </c>
       <c r="H1468" t="n">
         <v>67369</v>
@@ -43318,7 +43318,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1481" t="n">
-        <v>1.68173515796661</v>
+        <v>1.6817352771759</v>
       </c>
       <c r="H1481" t="n">
         <v>359067</v>
@@ -43376,7 +43376,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1483" t="n">
-        <v>1.63298916816711</v>
+        <v>1.6329892873764</v>
       </c>
       <c r="H1483" t="n">
         <v>259727</v>
@@ -43521,7 +43521,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1488" t="n">
-        <v>1.72235667705536</v>
+        <v>1.72235679626465</v>
       </c>
       <c r="H1488" t="n">
         <v>809400</v>
@@ -43579,7 +43579,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G1490" t="n">
-        <v>1.67767286300659</v>
+        <v>1.67767298221588</v>
       </c>
       <c r="H1490" t="n">
         <v>229813</v>
@@ -43608,7 +43608,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G1491" t="n">
-        <v>1.67767286300659</v>
+        <v>1.67767298221588</v>
       </c>
       <c r="H1491" t="n">
         <v>341679</v>
@@ -43666,7 +43666,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1493" t="n">
-        <v>1.76297831535339</v>
+        <v>1.76297843456268</v>
       </c>
       <c r="H1493" t="n">
         <v>714024</v>
@@ -43695,7 +43695,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1494" t="n">
-        <v>1.68985939025879</v>
+        <v>1.68985950946808</v>
       </c>
       <c r="H1494" t="n">
         <v>378268</v>
@@ -43724,7 +43724,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G1495" t="n">
-        <v>1.67767286300659</v>
+        <v>1.67767298221588</v>
       </c>
       <c r="H1495" t="n">
         <v>192202</v>
@@ -43753,7 +43753,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1496" t="n">
-        <v>1.63298916816711</v>
+        <v>1.6329892873764</v>
       </c>
       <c r="H1496" t="n">
         <v>243963</v>
@@ -43811,7 +43811,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G1498" t="n">
-        <v>1.59561741352081</v>
+        <v>1.59561729431152</v>
       </c>
       <c r="H1498" t="n">
         <v>353204</v>
@@ -43840,7 +43840,7 @@
         <v>1.98199999332428</v>
       </c>
       <c r="G1499" t="n">
-        <v>1.61024117469788</v>
+        <v>1.61024105548859</v>
       </c>
       <c r="H1499" t="n">
         <v>194433</v>
@@ -43898,7 +43898,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G1501" t="n">
-        <v>1.64517569541931</v>
+        <v>1.6451758146286</v>
       </c>
       <c r="H1501" t="n">
         <v>383780</v>
@@ -43985,7 +43985,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1504" t="n">
-        <v>1.8117241859436</v>
+        <v>1.81172430515289</v>
       </c>
       <c r="H1504" t="n">
         <v>780332</v>
@@ -44043,7 +44043,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1506" t="n">
-        <v>1.78735136985779</v>
+        <v>1.78735148906708</v>
       </c>
       <c r="H1506" t="n">
         <v>502772</v>
@@ -44072,7 +44072,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G1507" t="n">
-        <v>1.74266743659973</v>
+        <v>1.74266767501831</v>
       </c>
       <c r="H1507" t="n">
         <v>256619</v>
@@ -44159,7 +44159,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G1510" t="n">
-        <v>1.81578648090363</v>
+        <v>1.81578660011292</v>
       </c>
       <c r="H1510" t="n">
         <v>322801</v>
@@ -44188,7 +44188,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1511" t="n">
-        <v>1.77922701835632</v>
+        <v>1.77922689914703</v>
       </c>
       <c r="H1511" t="n">
         <v>106127</v>
@@ -44246,7 +44246,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1513" t="n">
-        <v>1.77110278606415</v>
+        <v>1.77110290527344</v>
       </c>
       <c r="H1513" t="n">
         <v>142968</v>
@@ -44304,7 +44304,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G1515" t="n">
-        <v>1.69392156600952</v>
+        <v>1.69392168521881</v>
       </c>
       <c r="H1515" t="n">
         <v>140700</v>
@@ -44333,7 +44333,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1516" t="n">
-        <v>1.68985939025879</v>
+        <v>1.68985950946808</v>
       </c>
       <c r="H1516" t="n">
         <v>113177</v>
@@ -44362,7 +44362,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G1517" t="n">
-        <v>1.69392156600952</v>
+        <v>1.69392168521881</v>
       </c>
       <c r="H1517" t="n">
         <v>170599</v>
@@ -44391,7 +44391,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1518" t="n">
-        <v>1.68173515796661</v>
+        <v>1.6817352771759</v>
       </c>
       <c r="H1518" t="n">
         <v>138706</v>
@@ -44449,7 +44449,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1520" t="n">
-        <v>1.68173515796661</v>
+        <v>1.6817352771759</v>
       </c>
       <c r="H1520" t="n">
         <v>131491</v>
@@ -44565,7 +44565,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G1524" t="n">
-        <v>1.71829473972321</v>
+        <v>1.71829462051392</v>
       </c>
       <c r="H1524" t="n">
         <v>63606</v>
@@ -44594,7 +44594,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G1525" t="n">
-        <v>1.71829473972321</v>
+        <v>1.71829462051392</v>
       </c>
       <c r="H1525" t="n">
         <v>150154</v>
@@ -44623,7 +44623,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G1526" t="n">
-        <v>1.71829473972321</v>
+        <v>1.71829462051392</v>
       </c>
       <c r="H1526" t="n">
         <v>128866</v>
@@ -44681,7 +44681,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1528" t="n">
-        <v>1.72235667705536</v>
+        <v>1.72235679626465</v>
       </c>
       <c r="H1528" t="n">
         <v>89066</v>
@@ -44739,7 +44739,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G1530" t="n">
-        <v>1.67767286300659</v>
+        <v>1.67767298221588</v>
       </c>
       <c r="H1530" t="n">
         <v>160683</v>
@@ -44768,7 +44768,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1531" t="n">
-        <v>1.66954851150513</v>
+        <v>1.66954874992371</v>
       </c>
       <c r="H1531" t="n">
         <v>158008</v>
@@ -44826,7 +44826,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G1533" t="n">
-        <v>1.60536646842957</v>
+        <v>1.60536658763885</v>
       </c>
       <c r="H1533" t="n">
         <v>150409</v>
@@ -44942,7 +44942,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1537" t="n">
-        <v>1.63298916816711</v>
+        <v>1.6329892873764</v>
       </c>
       <c r="H1537" t="n">
         <v>160339</v>
@@ -45029,7 +45029,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1540" t="n">
-        <v>1.60861611366272</v>
+        <v>1.60861623287201</v>
       </c>
       <c r="H1540" t="n">
         <v>183079</v>
@@ -45058,7 +45058,7 @@
         <v>1.91600000858307</v>
       </c>
       <c r="G1541" t="n">
-        <v>1.55662047863007</v>
+        <v>1.55662059783936</v>
       </c>
       <c r="H1541" t="n">
         <v>208561</v>
@@ -45087,7 +45087,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1542" t="n">
-        <v>1.48350155353546</v>
+        <v>1.48350167274475</v>
       </c>
       <c r="H1542" t="n">
         <v>274605</v>
@@ -45116,7 +45116,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1543" t="n">
-        <v>1.50300014019012</v>
+        <v>1.50300002098083</v>
       </c>
       <c r="H1543" t="n">
         <v>168123</v>
@@ -45145,7 +45145,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1544" t="n">
-        <v>1.51924872398376</v>
+        <v>1.51924860477448</v>
       </c>
       <c r="H1544" t="n">
         <v>158636</v>
@@ -45203,7 +45203,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1546" t="n">
-        <v>1.52737283706665</v>
+        <v>1.52737307548523</v>
       </c>
       <c r="H1546" t="n">
         <v>506923</v>
@@ -45261,7 +45261,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1548" t="n">
-        <v>1.54362154006958</v>
+        <v>1.54362165927887</v>
       </c>
       <c r="H1548" t="n">
         <v>460093</v>
@@ -45290,7 +45290,7 @@
         <v>1.89600002765656</v>
       </c>
       <c r="G1549" t="n">
-        <v>1.54037201404572</v>
+        <v>1.54037189483643</v>
       </c>
       <c r="H1549" t="n">
         <v>214698</v>
@@ -45319,7 +45319,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G1550" t="n">
-        <v>1.52249836921692</v>
+        <v>1.52249825000763</v>
       </c>
       <c r="H1550" t="n">
         <v>112041</v>
@@ -45348,7 +45348,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1551" t="n">
-        <v>1.48675131797791</v>
+        <v>1.48675143718719</v>
       </c>
       <c r="H1551" t="n">
         <v>163561</v>
@@ -45406,7 +45406,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G1553" t="n">
-        <v>1.4558789730072</v>
+        <v>1.45587885379791</v>
       </c>
       <c r="H1553" t="n">
         <v>165152</v>
@@ -45435,7 +45435,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G1554" t="n">
-        <v>1.49812543392181</v>
+        <v>1.49812531471252</v>
       </c>
       <c r="H1554" t="n">
         <v>231892</v>
@@ -45464,7 +45464,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1555" t="n">
-        <v>1.45912873744965</v>
+        <v>1.45912861824036</v>
       </c>
       <c r="H1555" t="n">
         <v>132516</v>
@@ -45493,7 +45493,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G1556" t="n">
-        <v>1.44775450229645</v>
+        <v>1.44775462150574</v>
       </c>
       <c r="H1556" t="n">
         <v>67002</v>
@@ -45609,7 +45609,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1560" t="n">
-        <v>1.3892594575882</v>
+        <v>1.38925957679749</v>
       </c>
       <c r="H1560" t="n">
         <v>224727</v>
@@ -45638,7 +45638,7 @@
         <v>1.68799996376038</v>
       </c>
       <c r="G1561" t="n">
-        <v>1.37138605117798</v>
+        <v>1.37138593196869</v>
       </c>
       <c r="H1561" t="n">
         <v>153681</v>
@@ -45667,7 +45667,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G1562" t="n">
-        <v>1.35188770294189</v>
+        <v>1.3518875837326</v>
       </c>
       <c r="H1562" t="n">
         <v>124267</v>
@@ -45696,7 +45696,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1563" t="n">
-        <v>1.35676217079163</v>
+        <v>1.35676229000092</v>
       </c>
       <c r="H1563" t="n">
         <v>161596</v>
@@ -45754,7 +45754,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1565" t="n">
-        <v>1.3161404132843</v>
+        <v>1.31614053249359</v>
       </c>
       <c r="H1565" t="n">
         <v>568059</v>
@@ -45812,7 +45812,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.35351240634918</v>
+        <v>1.35351252555847</v>
       </c>
       <c r="H1567" t="n">
         <v>147398</v>
@@ -45899,7 +45899,7 @@
         <v>1.56400001049042</v>
       </c>
       <c r="G1570" t="n">
-        <v>1.27064442634583</v>
+        <v>1.27064418792725</v>
       </c>
       <c r="H1570" t="n">
         <v>136397</v>
@@ -45957,7 +45957,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G1572" t="n">
-        <v>1.21539902687073</v>
+        <v>1.21539890766144</v>
       </c>
       <c r="H1572" t="n">
         <v>350390</v>
@@ -46073,7 +46073,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1576" t="n">
-        <v>1.22677290439606</v>
+        <v>1.22677302360535</v>
       </c>
       <c r="H1576" t="n">
         <v>139661</v>
@@ -46102,7 +46102,7 @@
         <v>1.58800005912781</v>
       </c>
       <c r="G1577" t="n">
-        <v>1.2901428937912</v>
+        <v>1.29014277458191</v>
       </c>
       <c r="H1577" t="n">
         <v>276513</v>
@@ -46189,7 +46189,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1580" t="n">
-        <v>1.25114583969116</v>
+        <v>1.25114595890045</v>
       </c>
       <c r="H1580" t="n">
         <v>498622</v>
@@ -46247,7 +46247,7 @@
         <v>1.49399995803833</v>
       </c>
       <c r="G1582" t="n">
-        <v>1.21377408504486</v>
+        <v>1.21377396583557</v>
       </c>
       <c r="H1582" t="n">
         <v>421007</v>
@@ -46276,7 +46276,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1583" t="n">
-        <v>1.18290174007416</v>
+        <v>1.18290162086487</v>
       </c>
       <c r="H1583" t="n">
         <v>470371</v>
@@ -46334,7 +46334,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G1585" t="n">
-        <v>1.15202927589417</v>
+        <v>1.15202915668488</v>
       </c>
       <c r="H1585" t="n">
         <v>253286</v>
@@ -46392,7 +46392,7 @@
         <v>1.40600001811981</v>
       </c>
       <c r="G1587" t="n">
-        <v>1.14227998256683</v>
+        <v>1.14228010177612</v>
       </c>
       <c r="H1587" t="n">
         <v>324496</v>
@@ -46450,7 +46450,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1589" t="n">
-        <v>1.18290174007416</v>
+        <v>1.18290162086487</v>
       </c>
       <c r="H1589" t="n">
         <v>172152</v>
@@ -46537,7 +46537,7 @@
         <v>1.42400002479553</v>
       </c>
       <c r="G1592" t="n">
-        <v>1.1569037437439</v>
+        <v>1.15690386295319</v>
       </c>
       <c r="H1592" t="n">
         <v>146118</v>
@@ -46566,7 +46566,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G1593" t="n">
-        <v>1.16015350818634</v>
+        <v>1.16015362739563</v>
       </c>
       <c r="H1593" t="n">
         <v>135352</v>
@@ -46624,7 +46624,7 @@
         <v>1.3639999628067</v>
       </c>
       <c r="G1595" t="n">
-        <v>1.10815787315369</v>
+        <v>1.1081577539444</v>
       </c>
       <c r="H1595" t="n">
         <v>127559</v>
@@ -46653,7 +46653,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1596" t="n">
-        <v>1.13903033733368</v>
+        <v>1.13903021812439</v>
       </c>
       <c r="H1596" t="n">
         <v>129641</v>
@@ -46682,7 +46682,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G1597" t="n">
-        <v>1.16015350818634</v>
+        <v>1.16015362739563</v>
       </c>
       <c r="H1597" t="n">
         <v>131997</v>
@@ -46740,7 +46740,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1599" t="n">
-        <v>1.19427561759949</v>
+        <v>1.19427573680878</v>
       </c>
       <c r="H1599" t="n">
         <v>341752</v>
@@ -46769,7 +46769,7 @@
         <v>1.46200001239777</v>
       </c>
       <c r="G1600" t="n">
-        <v>1.18777632713318</v>
+        <v>1.18777620792389</v>
       </c>
       <c r="H1600" t="n">
         <v>283692</v>
@@ -46798,7 +46798,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G1601" t="n">
-        <v>1.20727443695068</v>
+        <v>1.20727455615997</v>
       </c>
       <c r="H1601" t="n">
         <v>165882</v>
@@ -46856,7 +46856,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G1603" t="n">
-        <v>1.23977196216583</v>
+        <v>1.23977184295654</v>
       </c>
       <c r="H1603" t="n">
         <v>108098</v>
@@ -46885,7 +46885,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G1604" t="n">
-        <v>1.22027361392975</v>
+        <v>1.22027349472046</v>
       </c>
       <c r="H1604" t="n">
         <v>172641</v>
@@ -46914,7 +46914,7 @@
         <v>1.432000041008</v>
       </c>
       <c r="G1605" t="n">
-        <v>1.16340327262878</v>
+        <v>1.16340339183807</v>
       </c>
       <c r="H1605" t="n">
         <v>245214</v>
@@ -46943,7 +46943,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G1606" t="n">
-        <v>1.1504043340683</v>
+        <v>1.15040421485901</v>
       </c>
       <c r="H1606" t="n">
         <v>246735</v>
@@ -46972,7 +46972,7 @@
         <v>1.432000041008</v>
       </c>
       <c r="G1607" t="n">
-        <v>1.16340327262878</v>
+        <v>1.16340339183807</v>
       </c>
       <c r="H1607" t="n">
         <v>156800</v>
@@ -47117,7 +47117,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1612" t="n">
-        <v>1.13903033733368</v>
+        <v>1.13903021812439</v>
       </c>
       <c r="H1612" t="n">
         <v>147777</v>
@@ -47146,7 +47146,7 @@
         <v>1.38199996948242</v>
       </c>
       <c r="G1613" t="n">
-        <v>1.12278163433075</v>
+        <v>1.12278151512146</v>
       </c>
       <c r="H1613" t="n">
         <v>79104</v>
@@ -47291,7 +47291,7 @@
         <v>1.40600001811981</v>
       </c>
       <c r="G1618" t="n">
-        <v>1.14227998256683</v>
+        <v>1.14228010177612</v>
       </c>
       <c r="H1618" t="n">
         <v>77664</v>
@@ -47320,7 +47320,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G1619" t="n">
-        <v>1.15527892112732</v>
+        <v>1.15527904033661</v>
       </c>
       <c r="H1619" t="n">
         <v>243429</v>
@@ -47378,7 +47378,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G1621" t="n">
-        <v>1.16015350818634</v>
+        <v>1.16015362739563</v>
       </c>
       <c r="H1621" t="n">
         <v>99673</v>
@@ -47407,7 +47407,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1622" t="n">
-        <v>1.18290174007416</v>
+        <v>1.18290162086487</v>
       </c>
       <c r="H1622" t="n">
         <v>86677</v>
@@ -47436,7 +47436,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1623" t="n">
-        <v>1.20239996910095</v>
+        <v>1.20240020751953</v>
       </c>
       <c r="H1623" t="n">
         <v>232276</v>
@@ -47581,7 +47581,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1628" t="n">
-        <v>1.23489737510681</v>
+        <v>1.23489725589752</v>
       </c>
       <c r="H1628" t="n">
         <v>171807</v>
@@ -47610,7 +47610,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G1629" t="n">
-        <v>1.2365220785141</v>
+        <v>1.23652231693268</v>
       </c>
       <c r="H1629" t="n">
         <v>130601</v>
@@ -47668,7 +47668,7 @@
         <v>1.58599996566772</v>
       </c>
       <c r="G1631" t="n">
-        <v>1.28851771354675</v>
+        <v>1.28851783275604</v>
       </c>
       <c r="H1631" t="n">
         <v>263238</v>
@@ -47697,7 +47697,7 @@
         <v>1.567999958992</v>
       </c>
       <c r="G1632" t="n">
-        <v>1.27389407157898</v>
+        <v>1.27389395236969</v>
       </c>
       <c r="H1632" t="n">
         <v>259885</v>
@@ -47784,7 +47784,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G1635" t="n">
-        <v>1.32461130619049</v>
+        <v>1.3246111869812</v>
       </c>
       <c r="H1635" t="n">
         <v>250360</v>
@@ -47842,7 +47842,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1637" t="n">
-        <v>1.24448668956757</v>
+        <v>1.24448680877686</v>
       </c>
       <c r="H1637" t="n">
         <v>119554</v>
@@ -47900,7 +47900,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G1639" t="n">
-        <v>1.18140995502472</v>
+        <v>1.18141007423401</v>
       </c>
       <c r="H1639" t="n">
         <v>189144</v>
@@ -47958,7 +47958,7 @@
         <v>1.317999958992</v>
       </c>
       <c r="G1641" t="n">
-        <v>1.12344753742218</v>
+        <v>1.12344765663147</v>
       </c>
       <c r="H1641" t="n">
         <v>226152</v>
@@ -47987,7 +47987,7 @@
         <v>1.317999958992</v>
       </c>
       <c r="G1642" t="n">
-        <v>1.12344753742218</v>
+        <v>1.12344765663147</v>
       </c>
       <c r="H1642" t="n">
         <v>104159</v>
@@ -48016,7 +48016,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1643" t="n">
-        <v>1.09105670452118</v>
+        <v>1.09105682373047</v>
       </c>
       <c r="H1643" t="n">
         <v>76333</v>
@@ -48045,7 +48045,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1644" t="n">
-        <v>1.09105670452118</v>
+        <v>1.09105682373047</v>
       </c>
       <c r="H1644" t="n">
         <v>83196</v>
@@ -48132,7 +48132,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1647" t="n">
-        <v>1.06037068367004</v>
+        <v>1.06037080287933</v>
       </c>
       <c r="H1647" t="n">
         <v>90460</v>
@@ -48219,7 +48219,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1650" t="n">
-        <v>1.00922751426697</v>
+        <v>1.00922763347626</v>
       </c>
       <c r="H1650" t="n">
         <v>247035</v>
@@ -48306,7 +48306,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1653" t="n">
-        <v>1.01434183120728</v>
+        <v>1.01434206962585</v>
       </c>
       <c r="H1653" t="n">
         <v>150566</v>
@@ -48364,7 +48364,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G1655" t="n">
-        <v>1.00411331653595</v>
+        <v>1.00411319732666</v>
       </c>
       <c r="H1655" t="n">
         <v>57672</v>
@@ -48422,7 +48422,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1657" t="n">
-        <v>1.00922751426697</v>
+        <v>1.00922763347626</v>
       </c>
       <c r="H1657" t="n">
         <v>32212</v>
@@ -48509,7 +48509,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1660" t="n">
-        <v>1.05696129798889</v>
+        <v>1.0569611787796</v>
       </c>
       <c r="H1660" t="n">
         <v>51321</v>
@@ -48596,7 +48596,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1663" t="n">
-        <v>0.997294008731842</v>
+        <v>0.997294127941132</v>
       </c>
       <c r="H1663" t="n">
         <v>54748</v>
@@ -48654,7 +48654,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G1665" t="n">
-        <v>1.00411331653595</v>
+        <v>1.00411319732666</v>
       </c>
       <c r="H1665" t="n">
         <v>61997</v>
@@ -48712,7 +48712,7 @@
         <v>1.25</v>
       </c>
       <c r="G1667" t="n">
-        <v>1.06548523902893</v>
+        <v>1.06548511981964</v>
       </c>
       <c r="H1667" t="n">
         <v>81818</v>
@@ -48741,7 +48741,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1668" t="n">
-        <v>1.07400906085968</v>
+        <v>1.07400918006897</v>
       </c>
       <c r="H1668" t="n">
         <v>80447</v>
@@ -48770,7 +48770,7 @@
         <v>1.27799999713898</v>
       </c>
       <c r="G1669" t="n">
-        <v>1.08935213088989</v>
+        <v>1.0893520116806</v>
       </c>
       <c r="H1669" t="n">
         <v>63893</v>
@@ -48828,7 +48828,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1671" t="n">
-        <v>1.09105670452118</v>
+        <v>1.09105682373047</v>
       </c>
       <c r="H1671" t="n">
         <v>42630</v>
@@ -48944,7 +48944,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1675" t="n">
-        <v>1.15072405338287</v>
+        <v>1.15072393417358</v>
       </c>
       <c r="H1675" t="n">
         <v>115027</v>
@@ -49002,7 +49002,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1677" t="n">
-        <v>1.15072405338287</v>
+        <v>1.15072393417358</v>
       </c>
       <c r="H1677" t="n">
         <v>26173</v>
@@ -49089,7 +49089,7 @@
         <v>1.28799998760223</v>
       </c>
       <c r="G1680" t="n">
-        <v>1.09787595272064</v>
+        <v>1.09787583351135</v>
       </c>
       <c r="H1680" t="n">
         <v>83661</v>
@@ -49234,7 +49234,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1685" t="n">
-        <v>1.09105670452118</v>
+        <v>1.09105682373047</v>
       </c>
       <c r="H1685" t="n">
         <v>48966</v>
@@ -49321,7 +49321,7 @@
         <v>1.25</v>
       </c>
       <c r="G1688" t="n">
-        <v>1.06548523902893</v>
+        <v>1.06548511981964</v>
       </c>
       <c r="H1688" t="n">
         <v>46579</v>
@@ -49350,7 +49350,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G1689" t="n">
-        <v>1.02798008918762</v>
+        <v>1.02797996997833</v>
       </c>
       <c r="H1689" t="n">
         <v>62623</v>
@@ -49379,7 +49379,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1690" t="n">
-        <v>1.04843747615814</v>
+        <v>1.04843735694885</v>
       </c>
       <c r="H1690" t="n">
         <v>50229</v>
@@ -49437,7 +49437,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1692" t="n">
-        <v>1.04502773284912</v>
+        <v>1.04502785205841</v>
       </c>
       <c r="H1692" t="n">
         <v>13935</v>
@@ -49524,7 +49524,7 @@
         <v>1.13199996948242</v>
       </c>
       <c r="G1695" t="n">
-        <v>0.964903354644775</v>
+        <v>0.96490341424942</v>
       </c>
       <c r="H1695" t="n">
         <v>72471</v>
@@ -49553,7 +49553,7 @@
         <v>1.11600005626678</v>
       </c>
       <c r="G1696" t="n">
-        <v>0.951265156269073</v>
+        <v>0.951265275478363</v>
       </c>
       <c r="H1696" t="n">
         <v>149678</v>
@@ -49582,7 +49582,7 @@
         <v>1.11800003051758</v>
       </c>
       <c r="G1697" t="n">
-        <v>0.952970087528229</v>
+        <v>0.952969908714294</v>
       </c>
       <c r="H1697" t="n">
         <v>50805</v>
@@ -49669,7 +49669,7 @@
         <v>1.04200005531311</v>
       </c>
       <c r="G1700" t="n">
-        <v>0.888188540935516</v>
+        <v>0.888188421726227</v>
       </c>
       <c r="H1700" t="n">
         <v>227830</v>
@@ -49814,7 +49814,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1705" t="n">
-        <v>0.912055313587189</v>
+        <v>0.912055373191833</v>
       </c>
       <c r="H1705" t="n">
         <v>48966</v>
@@ -49872,7 +49872,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G1707" t="n">
-        <v>0.879664540290833</v>
+        <v>0.879664480686188</v>
       </c>
       <c r="H1707" t="n">
         <v>43441</v>
@@ -49959,7 +49959,7 @@
         <v>0.981000006198883</v>
       </c>
       <c r="G1710" t="n">
-        <v>0.836192727088928</v>
+        <v>0.836192786693573</v>
       </c>
       <c r="H1710" t="n">
         <v>95879</v>
@@ -49988,7 +49988,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G1711" t="n">
-        <v>0.828521311283112</v>
+        <v>0.828521251678467</v>
       </c>
       <c r="H1711" t="n">
         <v>121333</v>
@@ -50017,7 +50017,7 @@
         <v>0.940999984741211</v>
       </c>
       <c r="G1712" t="n">
-        <v>0.802097201347351</v>
+        <v>0.802097260951996</v>
       </c>
       <c r="H1712" t="n">
         <v>138220</v>
@@ -50046,7 +50046,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G1713" t="n">
-        <v>0.772263646125793</v>
+        <v>0.772263705730438</v>
       </c>
       <c r="H1713" t="n">
         <v>137783</v>
@@ -50249,7 +50249,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G1720" t="n">
-        <v>0.789311468601227</v>
+        <v>0.789311408996582</v>
       </c>
       <c r="H1720" t="n">
         <v>129382</v>
@@ -50278,7 +50278,7 @@
         <v>0.898999989032745</v>
       </c>
       <c r="G1721" t="n">
-        <v>0.766296982765198</v>
+        <v>0.766296923160553</v>
       </c>
       <c r="H1721" t="n">
         <v>97158</v>
@@ -50307,7 +50307,7 @@
         <v>0.901000022888184</v>
       </c>
       <c r="G1722" t="n">
-        <v>0.768001735210419</v>
+        <v>0.768001675605774</v>
       </c>
       <c r="H1722" t="n">
         <v>67176</v>
@@ -50365,7 +50365,7 @@
         <v>0.936999976634979</v>
       </c>
       <c r="G1724" t="n">
-        <v>0.798687696456909</v>
+        <v>0.798687636852264</v>
       </c>
       <c r="H1724" t="n">
         <v>39470</v>
@@ -50394,7 +50394,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G1725" t="n">
-        <v>0.788459062576294</v>
+        <v>0.788459002971649</v>
       </c>
       <c r="H1725" t="n">
         <v>42349</v>
@@ -50423,7 +50423,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G1726" t="n">
-        <v>0.808063983917236</v>
+        <v>0.808063924312592</v>
       </c>
       <c r="H1726" t="n">
         <v>46174</v>
@@ -50568,7 +50568,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G1731" t="n">
-        <v>0.838750004768372</v>
+        <v>0.838749945163727</v>
       </c>
       <c r="H1731" t="n">
         <v>58567</v>
@@ -50684,7 +50684,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G1735" t="n">
-        <v>0.874550223350525</v>
+        <v>0.87455028295517</v>
       </c>
       <c r="H1735" t="n">
         <v>54424</v>
@@ -50713,7 +50713,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1736" t="n">
-        <v>0.886483609676361</v>
+        <v>0.886483669281006</v>
       </c>
       <c r="H1736" t="n">
         <v>50773</v>
@@ -50742,7 +50742,7 @@
         <v>1.067999958992</v>
       </c>
       <c r="G1737" t="n">
-        <v>0.910350561141968</v>
+        <v>0.910350501537323</v>
       </c>
       <c r="H1737" t="n">
         <v>131430</v>
@@ -50771,7 +50771,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1738" t="n">
-        <v>0.912055313587189</v>
+        <v>0.912055373191833</v>
       </c>
       <c r="H1738" t="n">
         <v>24387</v>
@@ -50829,7 +50829,7 @@
         <v>1.07200002670288</v>
       </c>
       <c r="G1740" t="n">
-        <v>0.913760125637054</v>
+        <v>0.91376006603241</v>
       </c>
       <c r="H1740" t="n">
         <v>121974</v>
@@ -50858,7 +50858,7 @@
         <v>1.01600003242493</v>
       </c>
       <c r="G1741" t="n">
-        <v>0.866026341915131</v>
+        <v>0.866026401519775</v>
       </c>
       <c r="H1741" t="n">
         <v>223979</v>
@@ -50887,7 +50887,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G1742" t="n">
-        <v>0.879664540290833</v>
+        <v>0.879664480686188</v>
       </c>
       <c r="H1742" t="n">
         <v>89715</v>
@@ -50974,7 +50974,7 @@
         <v>1.12399995326996</v>
       </c>
       <c r="G1745" t="n">
-        <v>0.958084166049957</v>
+        <v>0.958084225654602</v>
       </c>
       <c r="H1745" t="n">
         <v>98956</v>
@@ -51003,7 +51003,7 @@
         <v>1.13399994373322</v>
       </c>
       <c r="G1746" t="n">
-        <v>0.966607987880707</v>
+        <v>0.966608107089996</v>
       </c>
       <c r="H1746" t="n">
         <v>104301</v>
@@ -51032,7 +51032,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1747" t="n">
-        <v>0.988770186901093</v>
+        <v>0.988770246505737</v>
       </c>
       <c r="H1747" t="n">
         <v>113438</v>
@@ -51148,7 +51148,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1751" t="n">
-        <v>1.04502773284912</v>
+        <v>1.04502785205841</v>
       </c>
       <c r="H1751" t="n">
         <v>218805</v>
@@ -51206,7 +51206,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1753" t="n">
-        <v>1.01434183120728</v>
+        <v>1.01434206962585</v>
       </c>
       <c r="H1753" t="n">
         <v>77128</v>
@@ -51235,7 +51235,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1754" t="n">
-        <v>1.03138959407806</v>
+        <v>1.03138971328735</v>
       </c>
       <c r="H1754" t="n">
         <v>230138</v>
@@ -51293,7 +51293,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G1756" t="n">
-        <v>1.04332304000854</v>
+        <v>1.04332315921783</v>
       </c>
       <c r="H1756" t="n">
         <v>36363</v>
@@ -51351,7 +51351,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1758" t="n">
-        <v>1.08253288269043</v>
+        <v>1.08253300189972</v>
       </c>
       <c r="H1758" t="n">
         <v>89488</v>
@@ -51380,7 +51380,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1759" t="n">
-        <v>1.09105670452118</v>
+        <v>1.09105682373047</v>
       </c>
       <c r="H1759" t="n">
         <v>111708</v>
@@ -51496,7 +51496,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1763" t="n">
-        <v>1.05525660514832</v>
+        <v>1.05525648593903</v>
       </c>
       <c r="H1763" t="n">
         <v>18697</v>
@@ -51525,7 +51525,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1764" t="n">
-        <v>1.05525660514832</v>
+        <v>1.05525648593903</v>
       </c>
       <c r="H1764" t="n">
         <v>6490</v>
@@ -51612,7 +51612,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1767" t="n">
-        <v>1.02286577224731</v>
+        <v>1.0228658914566</v>
       </c>
       <c r="H1767" t="n">
         <v>6818</v>
@@ -51728,7 +51728,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G1771" t="n">
-        <v>1.00411331653595</v>
+        <v>1.00411319732666</v>
       </c>
       <c r="H1771" t="n">
         <v>57385</v>
@@ -51757,7 +51757,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1772" t="n">
-        <v>0.988770186901093</v>
+        <v>0.988770246505737</v>
       </c>
       <c r="H1772" t="n">
         <v>23526</v>
@@ -51902,7 +51902,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G1777" t="n">
-        <v>0.992179811000824</v>
+        <v>0.992179870605469</v>
       </c>
       <c r="H1777" t="n">
         <v>11254</v>
@@ -51931,7 +51931,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1778" t="n">
-        <v>1.01434183120728</v>
+        <v>1.01434206962585</v>
       </c>
       <c r="H1778" t="n">
         <v>43914</v>
@@ -51960,7 +51960,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G1779" t="n">
-        <v>0.998998939990997</v>
+        <v>0.998998880386353</v>
       </c>
       <c r="H1779" t="n">
         <v>27915</v>
@@ -52018,7 +52018,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G1781" t="n">
-        <v>0.992179811000824</v>
+        <v>0.992179870605469</v>
       </c>
       <c r="H1781" t="n">
         <v>16217</v>
@@ -52047,7 +52047,7 @@
         <v>1.16600000858307</v>
       </c>
       <c r="G1782" t="n">
-        <v>0.993884563446045</v>
+        <v>0.99388462305069</v>
       </c>
       <c r="H1782" t="n">
         <v>33221</v>
@@ -52163,7 +52163,7 @@
         <v>1.25</v>
       </c>
       <c r="G1786" t="n">
-        <v>1.06548523902893</v>
+        <v>1.06548511981964</v>
       </c>
       <c r="H1786" t="n">
         <v>53889</v>
@@ -52221,7 +52221,7 @@
         <v>1.27799999713898</v>
       </c>
       <c r="G1788" t="n">
-        <v>1.08935213088989</v>
+        <v>1.0893520116806</v>
       </c>
       <c r="H1788" t="n">
         <v>146432</v>
@@ -52250,7 +52250,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1789" t="n">
-        <v>1.08594250679016</v>
+        <v>1.08594238758087</v>
       </c>
       <c r="H1789" t="n">
         <v>122538</v>
@@ -52279,7 +52279,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1790" t="n">
-        <v>1.07400906085968</v>
+        <v>1.07400918006897</v>
       </c>
       <c r="H1790" t="n">
         <v>86337</v>
@@ -52366,7 +52366,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1793" t="n">
-        <v>1.04843747615814</v>
+        <v>1.04843735694885</v>
       </c>
       <c r="H1793" t="n">
         <v>111796</v>
@@ -52453,7 +52453,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G1796" t="n">
-        <v>1.05184686183929</v>
+        <v>1.05184698104858</v>
       </c>
       <c r="H1796" t="n">
         <v>53899</v>
@@ -52482,7 +52482,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1797" t="n">
-        <v>1.05696129798889</v>
+        <v>1.0569611787796</v>
       </c>
       <c r="H1797" t="n">
         <v>53170</v>
@@ -52569,7 +52569,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G1800" t="n">
-        <v>1.1115140914917</v>
+        <v>1.11151421070099</v>
       </c>
       <c r="H1800" t="n">
         <v>169020</v>
@@ -52656,7 +52656,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1803" t="n">
-        <v>1.04843747615814</v>
+        <v>1.04843735694885</v>
       </c>
       <c r="H1803" t="n">
         <v>296942</v>
@@ -52685,7 +52685,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G1804" t="n">
-        <v>1.02116096019745</v>
+        <v>1.02116107940674</v>
       </c>
       <c r="H1804" t="n">
         <v>124141</v>
@@ -52772,7 +52772,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1807" t="n">
-        <v>1.08594250679016</v>
+        <v>1.08594238758087</v>
       </c>
       <c r="H1807" t="n">
         <v>160848</v>
@@ -52830,7 +52830,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1809" t="n">
-        <v>1.05696129798889</v>
+        <v>1.0569611787796</v>
       </c>
       <c r="H1809" t="n">
         <v>129914</v>
@@ -52917,7 +52917,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1812" t="n">
-        <v>1.01434183120728</v>
+        <v>1.01434206962585</v>
       </c>
       <c r="H1812" t="n">
         <v>202135</v>
@@ -52946,7 +52946,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G1813" t="n">
-        <v>1.0296847820282</v>
+        <v>1.02968490123749</v>
       </c>
       <c r="H1813" t="n">
         <v>79006</v>
@@ -53004,7 +53004,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G1815" t="n">
-        <v>0.992179811000824</v>
+        <v>0.992179870605469</v>
       </c>
       <c r="H1815" t="n">
         <v>240969</v>
@@ -53062,7 +53062,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1817" t="n">
-        <v>0.96319854259491</v>
+        <v>0.963198602199554</v>
       </c>
       <c r="H1817" t="n">
         <v>223409</v>
@@ -53091,7 +53091,7 @@
         <v>1.11800003051758</v>
       </c>
       <c r="G1818" t="n">
-        <v>0.952970087528229</v>
+        <v>0.952969908714294</v>
       </c>
       <c r="H1818" t="n">
         <v>286619</v>
@@ -53120,7 +53120,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1819" t="n">
-        <v>0.96319854259491</v>
+        <v>0.963198602199554</v>
       </c>
       <c r="H1819" t="n">
         <v>262571</v>
@@ -53236,7 +53236,7 @@
         <v>1.11199998855591</v>
       </c>
       <c r="G1823" t="n">
-        <v>0.947855591773987</v>
+        <v>0.947855532169342</v>
       </c>
       <c r="H1823" t="n">
         <v>175134</v>
@@ -53381,7 +53381,7 @@
         <v>1.07200002670288</v>
       </c>
       <c r="G1828" t="n">
-        <v>0.913760125637054</v>
+        <v>0.91376006603241</v>
       </c>
       <c r="H1828" t="n">
         <v>520878</v>
@@ -53410,7 +53410,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1829" t="n">
-        <v>0.929103076457977</v>
+        <v>0.929103136062622</v>
       </c>
       <c r="H1829" t="n">
         <v>298669</v>
@@ -53439,7 +53439,7 @@
         <v>1.11600005626678</v>
       </c>
       <c r="G1830" t="n">
-        <v>0.951265156269073</v>
+        <v>0.951265275478363</v>
       </c>
       <c r="H1830" t="n">
         <v>496069</v>
@@ -53468,7 +53468,7 @@
         <v>1.11800003051758</v>
       </c>
       <c r="G1831" t="n">
-        <v>0.952970087528229</v>
+        <v>0.952969908714294</v>
       </c>
       <c r="H1831" t="n">
         <v>126905</v>
@@ -53555,7 +53555,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1834" t="n">
-        <v>0.929103076457977</v>
+        <v>0.929103136062622</v>
       </c>
       <c r="H1834" t="n">
         <v>103566</v>
@@ -53613,7 +53613,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1836" t="n">
-        <v>0.912055313587189</v>
+        <v>0.912055373191833</v>
       </c>
       <c r="H1836" t="n">
         <v>149800</v>
@@ -53671,7 +53671,7 @@
         <v>1.067999958992</v>
       </c>
       <c r="G1838" t="n">
-        <v>0.910350561141968</v>
+        <v>0.910350501537323</v>
       </c>
       <c r="H1838" t="n">
         <v>105246</v>
@@ -53700,7 +53700,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1839" t="n">
-        <v>0.912055313587189</v>
+        <v>0.912055373191833</v>
       </c>
       <c r="H1839" t="n">
         <v>72792</v>
@@ -53729,7 +53729,7 @@
         <v>1.14600002765656</v>
       </c>
       <c r="G1840" t="n">
-        <v>0.976836800575256</v>
+        <v>0.976836860179901</v>
       </c>
       <c r="H1840" t="n">
         <v>372452</v>
@@ -53758,7 +53758,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G1841" t="n">
-        <v>0.970017790794373</v>
+        <v>0.970017671585083</v>
       </c>
       <c r="H1841" t="n">
         <v>476174</v>
@@ -53816,7 +53816,7 @@
         <v>1.13199996948242</v>
       </c>
       <c r="G1843" t="n">
-        <v>0.964903354644775</v>
+        <v>0.96490341424942</v>
       </c>
       <c r="H1843" t="n">
         <v>68209</v>
@@ -53845,7 +53845,7 @@
         <v>1.12399995326996</v>
       </c>
       <c r="G1844" t="n">
-        <v>0.958084166049957</v>
+        <v>0.958084225654602</v>
       </c>
       <c r="H1844" t="n">
         <v>72951</v>
@@ -53874,7 +53874,7 @@
         <v>1.11800003051758</v>
       </c>
       <c r="G1845" t="n">
-        <v>0.952970087528229</v>
+        <v>0.952969908714294</v>
       </c>
       <c r="H1845" t="n">
         <v>62856</v>
@@ -53903,7 +53903,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1846" t="n">
-        <v>0.96319854259491</v>
+        <v>0.963198602199554</v>
       </c>
       <c r="H1846" t="n">
         <v>98252</v>
@@ -53990,7 +53990,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G1849" t="n">
-        <v>0.995589375495911</v>
+        <v>0.995589315891266</v>
       </c>
       <c r="H1849" t="n">
         <v>200494</v>
@@ -54077,7 +54077,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G1852" t="n">
-        <v>1.02116096019745</v>
+        <v>1.02116107940674</v>
       </c>
       <c r="H1852" t="n">
         <v>72016</v>
@@ -54106,7 +54106,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G1853" t="n">
-        <v>1.01945626735687</v>
+        <v>1.01945614814758</v>
       </c>
       <c r="H1853" t="n">
         <v>181935</v>
@@ -54135,7 +54135,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G1854" t="n">
-        <v>1.0296847820282</v>
+        <v>1.02968490123749</v>
       </c>
       <c r="H1854" t="n">
         <v>83325</v>
@@ -54222,7 +54222,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G1857" t="n">
-        <v>1.0296847820282</v>
+        <v>1.02968490123749</v>
       </c>
       <c r="H1857" t="n">
         <v>327862</v>
@@ -54309,7 +54309,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1860" t="n">
-        <v>1.02286577224731</v>
+        <v>1.0228658914566</v>
       </c>
       <c r="H1860" t="n">
         <v>76153</v>
@@ -54338,7 +54338,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1861" t="n">
-        <v>0.997294008731842</v>
+        <v>0.997294127941132</v>
       </c>
       <c r="H1861" t="n">
         <v>89518</v>
@@ -54367,7 +54367,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1862" t="n">
-        <v>0.988770186901093</v>
+        <v>0.988770246505737</v>
       </c>
       <c r="H1862" t="n">
         <v>26123</v>
@@ -54541,7 +54541,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1868" t="n">
-        <v>0.95467472076416</v>
+        <v>0.954674661159515</v>
       </c>
       <c r="H1868" t="n">
         <v>30468</v>
@@ -54570,7 +54570,7 @@
         <v>1.12399995326996</v>
       </c>
       <c r="G1869" t="n">
-        <v>0.958084166049957</v>
+        <v>0.958084225654602</v>
       </c>
       <c r="H1869" t="n">
         <v>44505</v>
@@ -54599,7 +54599,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G1870" t="n">
-        <v>0.968312919139862</v>
+        <v>0.968312859535217</v>
       </c>
       <c r="H1870" t="n">
         <v>37333</v>
@@ -54628,7 +54628,7 @@
         <v>1.10800004005432</v>
       </c>
       <c r="G1871" t="n">
-        <v>0.94444614648819</v>
+        <v>0.944446086883545</v>
       </c>
       <c r="H1871" t="n">
         <v>130290</v>
@@ -54657,7 +54657,7 @@
         <v>1.11600005626678</v>
       </c>
       <c r="G1872" t="n">
-        <v>0.951265156269073</v>
+        <v>0.951265275478363</v>
       </c>
       <c r="H1872" t="n">
         <v>49675</v>
@@ -54831,7 +54831,7 @@
         <v>1.07799994945526</v>
       </c>
       <c r="G1878" t="n">
-        <v>0.918874442577362</v>
+        <v>0.918874382972717</v>
       </c>
       <c r="H1878" t="n">
         <v>85938</v>
@@ -54860,7 +54860,7 @@
         <v>1.11199998855591</v>
       </c>
       <c r="G1879" t="n">
-        <v>0.947855591773987</v>
+        <v>0.947855532169342</v>
       </c>
       <c r="H1879" t="n">
         <v>49798</v>
@@ -54889,7 +54889,7 @@
         <v>1.12399995326996</v>
       </c>
       <c r="G1880" t="n">
-        <v>0.958084166049957</v>
+        <v>0.958084225654602</v>
       </c>
       <c r="H1880" t="n">
         <v>63545</v>
@@ -54918,7 +54918,7 @@
         <v>1.11800003051758</v>
       </c>
       <c r="G1881" t="n">
-        <v>0.952970087528229</v>
+        <v>0.952969908714294</v>
       </c>
       <c r="H1881" t="n">
         <v>91035</v>
@@ -54947,7 +54947,7 @@
         <v>1.08800005912781</v>
       </c>
       <c r="G1882" t="n">
-        <v>0.927398383617401</v>
+        <v>0.927398324012756</v>
       </c>
       <c r="H1882" t="n">
         <v>287269</v>
@@ -55005,7 +55005,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.92398864030838</v>
+        <v>0.923988699913025</v>
       </c>
       <c r="H1884" t="n">
         <v>53637</v>
@@ -55034,7 +55034,7 @@
         <v>1.11600005626678</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.951265156269073</v>
+        <v>0.951265275478363</v>
       </c>
       <c r="H1885" t="n">
         <v>123740</v>
@@ -55092,7 +55092,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.912055313587189</v>
+        <v>0.912055373191833</v>
       </c>
       <c r="H1887" t="n">
         <v>165852</v>
@@ -55150,7 +55150,7 @@
         <v>1.10800004005432</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.94444614648819</v>
+        <v>0.944446086883545</v>
       </c>
       <c r="H1889" t="n">
         <v>320207</v>
@@ -79980,6 +79980,35 @@
         <v>47887</v>
       </c>
       <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>0.771000027656555</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>0.785000026226044</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>0.76800000667572</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>0.785000026226044</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>0.785000026226044</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>21722</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>
